--- a/data/KLYPV (TRY).xlsx
+++ b/data/KLYPV (TRY).xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J108"/>
+  <dimension ref="A1:L108"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -415,6 +415,8 @@
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
     <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
+    <col min="12" max="12" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -422,30 +424,36 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="C1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="D1" t="str">
+      <c r="F1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="E1" t="str">
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>2021/12</v>
       </c>
     </row>
@@ -459,30 +467,36 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B3">
+        <v>53901645</v>
+      </c>
+      <c r="C3">
+        <v>1089008586</v>
+      </c>
+      <c r="D3">
         <v>2049524230</v>
       </c>
-      <c r="C3">
+      <c r="E3">
         <v>2539337751</v>
       </c>
-      <c r="D3">
+      <c r="F3">
         <v>4490771362</v>
       </c>
-      <c r="E3">
+      <c r="G3">
         <v>849724943</v>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>119454439</v>
       </c>
-      <c r="G3">
+      <c r="I3">
         <v>79754221</v>
       </c>
-      <c r="H3">
+      <c r="J3">
         <v>33729725</v>
       </c>
-      <c r="I3">
+      <c r="K3">
         <v>56602558</v>
       </c>
-      <c r="J3">
+      <c r="L3">
         <v>7621735</v>
       </c>
     </row>
@@ -506,30 +520,36 @@
         <v xml:space="preserve">    Ticari Alacaklar</v>
       </c>
       <c r="B7">
+        <v>703552342</v>
+      </c>
+      <c r="C7">
+        <v>998582209</v>
+      </c>
+      <c r="D7">
         <v>1226184293</v>
       </c>
-      <c r="C7">
+      <c r="E7">
         <v>1557166286</v>
       </c>
-      <c r="D7">
+      <c r="F7">
         <v>3868255814</v>
       </c>
-      <c r="E7">
+      <c r="G7">
         <v>1744766414</v>
       </c>
-      <c r="F7">
+      <c r="H7">
         <v>1192904913</v>
       </c>
-      <c r="G7">
+      <c r="I7">
         <v>1309519246</v>
       </c>
-      <c r="H7">
+      <c r="J7">
         <v>820206001</v>
       </c>
-      <c r="I7">
+      <c r="K7">
         <v>890653538</v>
       </c>
-      <c r="J7">
+      <c r="L7">
         <v>273048120</v>
       </c>
     </row>
@@ -548,30 +568,36 @@
         <v xml:space="preserve">    Diğer Alacaklar</v>
       </c>
       <c r="B10">
+        <v>483366628</v>
+      </c>
+      <c r="C10">
+        <v>285381149</v>
+      </c>
+      <c r="D10">
         <v>179715689</v>
       </c>
-      <c r="C10">
+      <c r="E10">
         <v>104414963</v>
       </c>
-      <c r="D10">
+      <c r="F10">
         <v>143525807</v>
       </c>
-      <c r="E10">
+      <c r="G10">
         <v>107213102</v>
       </c>
-      <c r="F10">
+      <c r="H10">
         <v>138693845</v>
       </c>
-      <c r="G10">
+      <c r="I10">
         <v>56210286</v>
       </c>
-      <c r="H10">
+      <c r="J10">
         <v>228543243</v>
       </c>
-      <c r="I10">
+      <c r="K10">
         <v>99439122</v>
       </c>
-      <c r="J10">
+      <c r="L10">
         <v>48952059</v>
       </c>
     </row>
@@ -580,21 +606,27 @@
         <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Varlıklar</v>
       </c>
       <c r="B11">
+        <v>116410901</v>
+      </c>
+      <c r="C11">
+        <v>30839085</v>
+      </c>
+      <c r="D11">
         <v>22825790</v>
       </c>
-      <c r="C11">
+      <c r="E11">
         <v>22825793</v>
       </c>
-      <c r="D11">
+      <c r="F11">
         <v>22825764</v>
       </c>
-      <c r="E11">
+      <c r="G11">
         <v>22588625</v>
       </c>
-      <c r="F11">
+      <c r="H11">
         <v>22580662</v>
       </c>
-      <c r="H11">
+      <c r="J11">
         <v>65563672</v>
       </c>
     </row>
@@ -613,30 +645,36 @@
         <v xml:space="preserve">    Stoklar</v>
       </c>
       <c r="B14">
+        <v>5376974177</v>
+      </c>
+      <c r="C14">
+        <v>5880341005</v>
+      </c>
+      <c r="D14">
         <v>4822953085</v>
       </c>
-      <c r="C14">
+      <c r="E14">
         <v>5133479048</v>
       </c>
-      <c r="D14">
+      <c r="F14">
         <v>4078867230</v>
       </c>
-      <c r="E14">
+      <c r="G14">
         <v>4625456743</v>
       </c>
-      <c r="F14">
+      <c r="H14">
         <v>4905318404</v>
       </c>
-      <c r="G14">
+      <c r="I14">
         <v>5388475635</v>
       </c>
-      <c r="H14">
+      <c r="J14">
         <v>3084454625</v>
       </c>
-      <c r="I14">
+      <c r="K14">
         <v>2340702587</v>
       </c>
-      <c r="J14">
+      <c r="L14">
         <v>821979726</v>
       </c>
     </row>
@@ -655,30 +693,36 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderler</v>
       </c>
       <c r="B17">
+        <v>576122611</v>
+      </c>
+      <c r="C17">
+        <v>1188271739</v>
+      </c>
+      <c r="D17">
         <v>1975138868</v>
       </c>
-      <c r="C17">
+      <c r="E17">
         <v>2853224335</v>
       </c>
-      <c r="D17">
+      <c r="F17">
         <v>3475723135</v>
       </c>
-      <c r="E17">
+      <c r="G17">
         <v>2054786265</v>
       </c>
-      <c r="F17">
+      <c r="H17">
         <v>972259976</v>
       </c>
-      <c r="G17">
+      <c r="I17">
         <v>1443055296</v>
       </c>
-      <c r="H17">
+      <c r="J17">
         <v>668457530</v>
       </c>
-      <c r="I17">
+      <c r="K17">
         <v>682288383</v>
       </c>
-      <c r="J17">
+      <c r="L17">
         <v>221189326</v>
       </c>
     </row>
@@ -702,30 +746,36 @@
         <v xml:space="preserve">    Diğer Dönen Varlıklar</v>
       </c>
       <c r="B21">
+        <v>1333765832</v>
+      </c>
+      <c r="C21">
+        <v>1220912152</v>
+      </c>
+      <c r="D21">
         <v>834471424</v>
       </c>
-      <c r="C21">
+      <c r="E21">
         <v>602066677</v>
       </c>
-      <c r="D21">
+      <c r="F21">
         <v>15573903</v>
       </c>
-      <c r="E21">
+      <c r="G21">
         <v>331221835</v>
       </c>
-      <c r="F21">
+      <c r="H21">
         <v>323656921</v>
       </c>
-      <c r="G21">
+      <c r="I21">
         <v>634082211</v>
       </c>
-      <c r="H21">
+      <c r="J21">
         <v>130946169</v>
       </c>
-      <c r="I21">
+      <c r="K21">
         <v>173072854</v>
       </c>
-      <c r="J21">
+      <c r="L21">
         <v>84542447</v>
       </c>
     </row>
@@ -744,30 +794,36 @@
         <v xml:space="preserve">    Toplam Dönen Varlıklar</v>
       </c>
       <c r="B24">
+        <v>8644094136</v>
+      </c>
+      <c r="C24">
+        <v>10693335925</v>
+      </c>
+      <c r="D24">
         <v>11110813379</v>
       </c>
-      <c r="C24">
+      <c r="E24">
         <v>12812514853</v>
       </c>
-      <c r="D24">
+      <c r="F24">
         <v>16095543015</v>
       </c>
-      <c r="E24">
+      <c r="G24">
         <v>9735757927</v>
       </c>
-      <c r="F24">
+      <c r="H24">
         <v>7674869160</v>
       </c>
-      <c r="G24">
+      <c r="I24">
         <v>8911096895</v>
       </c>
-      <c r="H24">
+      <c r="J24">
         <v>5031900965</v>
       </c>
-      <c r="I24">
+      <c r="K24">
         <v>4242759041</v>
       </c>
-      <c r="J24">
+      <c r="L24">
         <v>1457333413</v>
       </c>
     </row>
@@ -801,30 +857,36 @@
         <v xml:space="preserve">    Diğer Alacaklar</v>
       </c>
       <c r="B30">
+        <v>1827358</v>
+      </c>
+      <c r="C30">
+        <v>16923971</v>
+      </c>
+      <c r="D30">
         <v>16344906</v>
       </c>
-      <c r="C30">
+      <c r="E30">
         <v>15820068</v>
       </c>
-      <c r="D30">
+      <c r="F30">
         <v>8203534</v>
       </c>
-      <c r="E30">
+      <c r="G30">
         <v>7797237</v>
       </c>
-      <c r="F30">
+      <c r="H30">
         <v>7274657</v>
       </c>
-      <c r="G30">
+      <c r="I30">
         <v>1347302</v>
       </c>
-      <c r="H30">
+      <c r="J30">
         <v>1153145</v>
       </c>
-      <c r="I30">
+      <c r="K30">
         <v>722297</v>
       </c>
-      <c r="J30">
+      <c r="L30">
         <v>531147</v>
       </c>
     </row>
@@ -873,30 +935,36 @@
         <v xml:space="preserve">    Maddi Duran Varlıklar</v>
       </c>
       <c r="B39">
+        <v>21754314873</v>
+      </c>
+      <c r="C39">
+        <v>20539170588</v>
+      </c>
+      <c r="D39">
         <v>19217307823</v>
       </c>
-      <c r="C39">
+      <c r="E39">
         <v>16161913178</v>
       </c>
-      <c r="D39">
+      <c r="F39">
         <v>12560334340</v>
       </c>
-      <c r="E39">
+      <c r="G39">
         <v>11977249726</v>
       </c>
-      <c r="F39">
+      <c r="H39">
         <v>11185648575</v>
       </c>
-      <c r="G39">
+      <c r="I39">
         <v>10342072508</v>
       </c>
-      <c r="H39">
+      <c r="J39">
         <v>8825751643</v>
       </c>
-      <c r="I39">
+      <c r="K39">
         <v>5282982648</v>
       </c>
-      <c r="J39">
+      <c r="L39">
         <v>3921632499</v>
       </c>
     </row>
@@ -910,30 +978,36 @@
         <v xml:space="preserve">    Maddi Olmayan Duran Varlıklar</v>
       </c>
       <c r="B41">
+        <v>2093656560</v>
+      </c>
+      <c r="C41">
+        <v>1974771380</v>
+      </c>
+      <c r="D41">
         <v>1882019267</v>
       </c>
-      <c r="C41">
+      <c r="E41">
         <v>1682112547</v>
       </c>
-      <c r="D41">
+      <c r="F41">
         <v>1578053438</v>
       </c>
-      <c r="E41">
+      <c r="G41">
         <v>1388012013</v>
       </c>
-      <c r="F41">
+      <c r="H41">
         <v>1267594507</v>
       </c>
-      <c r="G41">
+      <c r="I41">
         <v>1066439912</v>
       </c>
-      <c r="H41">
+      <c r="J41">
         <v>733437677</v>
       </c>
-      <c r="I41">
+      <c r="K41">
         <v>290117525</v>
       </c>
-      <c r="J41">
+      <c r="L41">
         <v>54641424</v>
       </c>
     </row>
@@ -942,27 +1016,33 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderler</v>
       </c>
       <c r="B42">
+        <v>221780850</v>
+      </c>
+      <c r="C42">
+        <v>269773212</v>
+      </c>
+      <c r="D42">
         <v>368793077</v>
       </c>
-      <c r="C42">
+      <c r="E42">
         <v>0</v>
       </c>
-      <c r="D42">
+      <c r="F42">
         <v>4545394</v>
       </c>
-      <c r="E42">
+      <c r="G42">
         <v>4545392</v>
       </c>
-      <c r="F42">
+      <c r="H42">
         <v>636608141</v>
       </c>
-      <c r="H42">
+      <c r="J42">
         <v>4545388</v>
       </c>
-      <c r="I42">
+      <c r="K42">
         <v>4545388</v>
       </c>
-      <c r="J42">
+      <c r="L42">
         <v>2439</v>
       </c>
     </row>
@@ -971,30 +1051,36 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Varlığı</v>
       </c>
       <c r="B43">
+        <v>7123247655</v>
+      </c>
+      <c r="C43">
+        <v>3753550940</v>
+      </c>
+      <c r="D43">
         <v>3892039976</v>
       </c>
-      <c r="C43">
+      <c r="E43">
         <v>4739933984</v>
       </c>
-      <c r="D43">
+      <c r="F43">
         <v>3310052086</v>
       </c>
-      <c r="E43">
+      <c r="G43">
         <v>3366697987</v>
       </c>
-      <c r="F43">
+      <c r="H43">
         <v>3459720389</v>
       </c>
-      <c r="G43">
+      <c r="I43">
         <v>3446498608</v>
       </c>
-      <c r="H43">
+      <c r="J43">
         <v>2901852868</v>
       </c>
-      <c r="I43">
+      <c r="K43">
         <v>600699703</v>
       </c>
-      <c r="J43">
+      <c r="L43">
         <v>446420901</v>
       </c>
     </row>
@@ -1013,27 +1099,33 @@
         <v xml:space="preserve">    Diğer Duran Varlıklar</v>
       </c>
       <c r="B46">
+        <v>15335046</v>
+      </c>
+      <c r="C46">
+        <v>14910475</v>
+      </c>
+      <c r="D46">
         <v>14477905</v>
       </c>
-      <c r="C46">
+      <c r="E46">
         <v>5432576</v>
       </c>
-      <c r="D46">
+      <c r="F46">
         <v>13032598</v>
       </c>
-      <c r="E46">
+      <c r="G46">
         <v>13032569</v>
       </c>
-      <c r="F46">
+      <c r="H46">
         <v>13032613</v>
       </c>
-      <c r="G46">
+      <c r="I46">
         <v>7431008</v>
       </c>
-      <c r="H46">
+      <c r="J46">
         <v>5432586</v>
       </c>
-      <c r="I46">
+      <c r="K46">
         <v>1262247</v>
       </c>
     </row>
@@ -1042,30 +1134,36 @@
         <v xml:space="preserve">    Toplam Duran Varlıklar</v>
       </c>
       <c r="B47">
+        <v>31210162342</v>
+      </c>
+      <c r="C47">
+        <v>26569100566</v>
+      </c>
+      <c r="D47">
         <v>25390982954</v>
       </c>
-      <c r="C47">
+      <c r="E47">
         <v>22605212353</v>
       </c>
-      <c r="D47">
+      <c r="F47">
         <v>17474221390</v>
       </c>
-      <c r="E47">
+      <c r="G47">
         <v>16757334924</v>
       </c>
-      <c r="F47">
+      <c r="H47">
         <v>16569878882</v>
       </c>
-      <c r="G47">
+      <c r="I47">
         <v>14863789338</v>
       </c>
-      <c r="H47">
+      <c r="J47">
         <v>12472173307</v>
       </c>
-      <c r="I47">
+      <c r="K47">
         <v>6180329808</v>
       </c>
-      <c r="J47">
+      <c r="L47">
         <v>4423228410</v>
       </c>
     </row>
@@ -1074,30 +1172,36 @@
         <v xml:space="preserve">    Toplam Varlıklar</v>
       </c>
       <c r="B48">
+        <v>39854256478</v>
+      </c>
+      <c r="C48">
+        <v>37262436491</v>
+      </c>
+      <c r="D48">
         <v>36501796333</v>
       </c>
-      <c r="C48">
+      <c r="E48">
         <v>35417727206</v>
       </c>
-      <c r="D48">
+      <c r="F48">
         <v>33569764405</v>
       </c>
-      <c r="E48">
+      <c r="G48">
         <v>26493092851</v>
       </c>
-      <c r="F48">
+      <c r="H48">
         <v>24244748042</v>
       </c>
-      <c r="G48">
+      <c r="I48">
         <v>23774886233</v>
       </c>
-      <c r="H48">
+      <c r="J48">
         <v>17504074272</v>
       </c>
-      <c r="I48">
+      <c r="K48">
         <v>10423088849</v>
       </c>
-      <c r="J48">
+      <c r="L48">
         <v>5880561823</v>
       </c>
     </row>
@@ -1111,30 +1215,36 @@
         <v xml:space="preserve">    Finansal Borçlar</v>
       </c>
       <c r="B50">
+        <v>2708371831</v>
+      </c>
+      <c r="C50">
+        <v>2176146902</v>
+      </c>
+      <c r="D50">
         <v>2234735634</v>
       </c>
-      <c r="C50">
+      <c r="E50">
         <v>1616812986</v>
       </c>
-      <c r="D50">
+      <c r="F50">
         <v>1848677806</v>
       </c>
-      <c r="E50">
+      <c r="G50">
         <v>4142702641</v>
       </c>
-      <c r="F50">
+      <c r="H50">
         <v>5242786792</v>
       </c>
-      <c r="G50">
+      <c r="I50">
         <v>4549983933</v>
       </c>
-      <c r="H50">
+      <c r="J50">
         <v>993373488</v>
       </c>
-      <c r="I50">
+      <c r="K50">
         <v>913990851</v>
       </c>
-      <c r="J50">
+      <c r="L50">
         <v>2632486382</v>
       </c>
     </row>
@@ -1148,30 +1258,36 @@
         <v xml:space="preserve">    Ticari Borçlar</v>
       </c>
       <c r="B52">
+        <v>2426270949</v>
+      </c>
+      <c r="C52">
+        <v>1748699869</v>
+      </c>
+      <c r="D52">
         <v>2991237110</v>
       </c>
-      <c r="C52">
+      <c r="E52">
         <v>3071694915</v>
       </c>
-      <c r="D52">
+      <c r="F52">
         <v>3043416835</v>
       </c>
-      <c r="E52">
+      <c r="G52">
         <v>2373673776</v>
       </c>
-      <c r="F52">
+      <c r="H52">
         <v>2384725781</v>
       </c>
-      <c r="G52">
+      <c r="I52">
         <v>1763719203</v>
       </c>
-      <c r="H52">
+      <c r="J52">
         <v>1791625348</v>
       </c>
-      <c r="I52">
+      <c r="K52">
         <v>1232488813</v>
       </c>
-      <c r="J52">
+      <c r="L52">
         <v>847089609</v>
       </c>
     </row>
@@ -1185,30 +1301,36 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlar</v>
       </c>
       <c r="B54">
+        <v>113415065</v>
+      </c>
+      <c r="C54">
+        <v>152583534</v>
+      </c>
+      <c r="D54">
         <v>96817194</v>
       </c>
-      <c r="C54">
+      <c r="E54">
         <v>91358393</v>
       </c>
-      <c r="D54">
+      <c r="F54">
         <v>89373742</v>
       </c>
-      <c r="E54">
+      <c r="G54">
         <v>26970131</v>
       </c>
-      <c r="F54">
+      <c r="H54">
         <v>63593463</v>
       </c>
-      <c r="G54">
+      <c r="I54">
         <v>68521966</v>
       </c>
-      <c r="H54">
+      <c r="J54">
         <v>75041531</v>
       </c>
-      <c r="I54">
+      <c r="K54">
         <v>26088941</v>
       </c>
-      <c r="J54">
+      <c r="L54">
         <v>11371229</v>
       </c>
     </row>
@@ -1217,30 +1339,36 @@
         <v xml:space="preserve">    Diğer Borçlar</v>
       </c>
       <c r="B55">
+        <v>2674232153</v>
+      </c>
+      <c r="C55">
+        <v>777395217</v>
+      </c>
+      <c r="D55">
         <v>1735963810</v>
       </c>
-      <c r="C55">
+      <c r="E55">
         <v>36053576</v>
       </c>
-      <c r="D55">
+      <c r="F55">
         <v>1213654817</v>
       </c>
-      <c r="E55">
+      <c r="G55">
         <v>898293938</v>
       </c>
-      <c r="F55">
+      <c r="H55">
         <v>952494487</v>
       </c>
-      <c r="G55">
+      <c r="I55">
         <v>646483538</v>
       </c>
-      <c r="H55">
+      <c r="J55">
         <v>24980564</v>
       </c>
-      <c r="I55">
+      <c r="K55">
         <v>16886316</v>
       </c>
-      <c r="J55">
+      <c r="L55">
         <v>608534</v>
       </c>
     </row>
@@ -1269,30 +1397,36 @@
         <v xml:space="preserve">    Ertelenmiş Gelirler</v>
       </c>
       <c r="B60">
+        <v>2526025170</v>
+      </c>
+      <c r="C60">
+        <v>3620205100</v>
+      </c>
+      <c r="D60">
         <v>2149586086</v>
       </c>
-      <c r="C60">
+      <c r="E60">
         <v>1870035949</v>
       </c>
-      <c r="D60">
+      <c r="F60">
         <v>2002007302</v>
       </c>
-      <c r="E60">
+      <c r="G60">
         <v>1372388714</v>
       </c>
-      <c r="F60">
+      <c r="H60">
         <v>1775323280</v>
       </c>
-      <c r="G60">
+      <c r="I60">
         <v>1630303983</v>
       </c>
-      <c r="H60">
+      <c r="J60">
         <v>1555425798</v>
       </c>
-      <c r="I60">
+      <c r="K60">
         <v>1711664683</v>
       </c>
-      <c r="J60">
+      <c r="L60">
         <v>51012108</v>
       </c>
     </row>
@@ -1306,30 +1440,36 @@
         <v xml:space="preserve">    Kısa Vadeli Karşılıklar</v>
       </c>
       <c r="B62">
+        <v>48655495</v>
+      </c>
+      <c r="C62">
+        <v>43761636</v>
+      </c>
+      <c r="D62">
         <v>41919491</v>
       </c>
-      <c r="C62">
+      <c r="E62">
         <v>45980892</v>
       </c>
-      <c r="D62">
+      <c r="F62">
         <v>43629653</v>
       </c>
-      <c r="E62">
+      <c r="G62">
         <v>37605147</v>
       </c>
-      <c r="F62">
+      <c r="H62">
         <v>31009307</v>
       </c>
-      <c r="G62">
+      <c r="I62">
         <v>28825248</v>
       </c>
-      <c r="H62">
+      <c r="J62">
         <v>22722036</v>
       </c>
-      <c r="I62">
+      <c r="K62">
         <v>8039924</v>
       </c>
-      <c r="J62">
+      <c r="L62">
         <v>1484600</v>
       </c>
     </row>
@@ -1338,30 +1478,36 @@
         <v xml:space="preserve">    Diğer Kısa Vadeli Yükümlülükler</v>
       </c>
       <c r="B63">
+        <v>34214798</v>
+      </c>
+      <c r="C63">
+        <v>22449712</v>
+      </c>
+      <c r="D63">
         <v>31037076</v>
       </c>
-      <c r="C63">
+      <c r="E63">
         <v>74865384</v>
       </c>
-      <c r="D63">
+      <c r="F63">
         <v>18672334</v>
       </c>
-      <c r="E63">
+      <c r="G63">
         <v>9625877</v>
       </c>
-      <c r="F63">
+      <c r="H63">
         <v>16463672</v>
       </c>
-      <c r="G63">
+      <c r="I63">
         <v>45062585</v>
       </c>
-      <c r="H63">
+      <c r="J63">
         <v>14386813</v>
       </c>
-      <c r="I63">
+      <c r="K63">
         <v>6272222</v>
       </c>
-      <c r="J63">
+      <c r="L63">
         <v>3975771</v>
       </c>
     </row>
@@ -1380,30 +1526,36 @@
         <v xml:space="preserve">    Toplam Kısa Vadeli Yükümlülükler</v>
       </c>
       <c r="B66">
+        <v>10531185461</v>
+      </c>
+      <c r="C66">
+        <v>8541241970</v>
+      </c>
+      <c r="D66">
         <v>9281296401</v>
       </c>
-      <c r="C66">
+      <c r="E66">
         <v>6806802095</v>
       </c>
-      <c r="D66">
+      <c r="F66">
         <v>8259432489</v>
       </c>
-      <c r="E66">
+      <c r="G66">
         <v>8861260224</v>
       </c>
-      <c r="F66">
+      <c r="H66">
         <v>10466396782</v>
       </c>
-      <c r="G66">
+      <c r="I66">
         <v>8732900456</v>
       </c>
-      <c r="H66">
+      <c r="J66">
         <v>4477555578</v>
       </c>
-      <c r="I66">
+      <c r="K66">
         <v>3915431750</v>
       </c>
-      <c r="J66">
+      <c r="L66">
         <v>3548028233</v>
       </c>
     </row>
@@ -1417,30 +1569,36 @@
         <v xml:space="preserve">    Finansal Borçlar</v>
       </c>
       <c r="B68">
+        <v>11079576398</v>
+      </c>
+      <c r="C68">
+        <v>12469597861</v>
+      </c>
+      <c r="D68">
         <v>13886565593</v>
       </c>
-      <c r="C68">
+      <c r="E68">
         <v>14428305867</v>
       </c>
-      <c r="D68">
+      <c r="F68">
         <v>13442163465</v>
       </c>
-      <c r="E68">
+      <c r="G68">
         <v>5720615477</v>
       </c>
-      <c r="F68">
+      <c r="H68">
         <v>4569629414</v>
       </c>
-      <c r="G68">
+      <c r="I68">
         <v>5362059876</v>
       </c>
-      <c r="H68">
+      <c r="J68">
         <v>4976073513</v>
       </c>
-      <c r="I68">
+      <c r="K68">
         <v>3547189874</v>
       </c>
-      <c r="J68">
+      <c r="L68">
         <v>428716743</v>
       </c>
     </row>
@@ -1504,30 +1662,36 @@
         <v xml:space="preserve">    Uzun vadeli Karşılıklar</v>
       </c>
       <c r="B80">
+        <v>57458386</v>
+      </c>
+      <c r="C80">
+        <v>49839918</v>
+      </c>
+      <c r="D80">
         <v>37764683</v>
       </c>
-      <c r="C80">
+      <c r="E80">
         <v>38242722</v>
       </c>
-      <c r="D80">
+      <c r="F80">
         <v>31240193</v>
       </c>
-      <c r="E80">
+      <c r="G80">
         <v>34371273</v>
       </c>
-      <c r="F80">
+      <c r="H80">
         <v>36064849</v>
       </c>
-      <c r="G80">
+      <c r="I80">
         <v>28012012</v>
       </c>
-      <c r="H80">
+      <c r="J80">
         <v>8784188</v>
       </c>
-      <c r="I80">
+      <c r="K80">
         <v>8274119</v>
       </c>
-      <c r="J80">
+      <c r="L80">
         <v>1392085</v>
       </c>
     </row>
@@ -1551,30 +1715,36 @@
         <v xml:space="preserve">    Toplam Uzun Vadeli Yükümlülükler</v>
       </c>
       <c r="B84">
+        <v>11137034784</v>
+      </c>
+      <c r="C84">
+        <v>12519437779</v>
+      </c>
+      <c r="D84">
         <v>13924330276</v>
       </c>
-      <c r="C84">
+      <c r="E84">
         <v>14466548589</v>
       </c>
-      <c r="D84">
+      <c r="F84">
         <v>13473403658</v>
       </c>
-      <c r="E84">
+      <c r="G84">
         <v>5754986750</v>
       </c>
-      <c r="F84">
+      <c r="H84">
         <v>4605694263</v>
       </c>
-      <c r="G84">
+      <c r="I84">
         <v>5390071888</v>
       </c>
-      <c r="H84">
+      <c r="J84">
         <v>4984857701</v>
       </c>
-      <c r="I84">
+      <c r="K84">
         <v>3555463993</v>
       </c>
-      <c r="J84">
+      <c r="L84">
         <v>430108828</v>
       </c>
     </row>
@@ -1588,30 +1758,36 @@
         <v xml:space="preserve">    Ana Ortaklığa Ait Özkaynaklar</v>
       </c>
       <c r="B86">
+        <v>18186036233</v>
+      </c>
+      <c r="C86">
+        <v>16201756742</v>
+      </c>
+      <c r="D86">
         <v>13296169656</v>
       </c>
-      <c r="C86">
+      <c r="E86">
         <v>14144376522</v>
       </c>
-      <c r="D86">
+      <c r="F86">
         <v>11836928258</v>
       </c>
-      <c r="E86">
+      <c r="G86">
         <v>11876845877</v>
       </c>
-      <c r="F86">
+      <c r="H86">
         <v>9172656997</v>
       </c>
-      <c r="G86">
+      <c r="I86">
         <v>9651913889</v>
       </c>
-      <c r="H86">
+      <c r="J86">
         <v>8041660993</v>
       </c>
-      <c r="I86">
+      <c r="K86">
         <v>2952193106</v>
       </c>
-      <c r="J86">
+      <c r="L86">
         <v>1902424762</v>
       </c>
     </row>
@@ -1632,10 +1808,10 @@
         <v>411441018</v>
       </c>
       <c r="F87">
-        <v>375300000</v>
+        <v>411441018</v>
       </c>
       <c r="G87">
-        <v>375300000</v>
+        <v>411441018</v>
       </c>
       <c r="H87">
         <v>375300000</v>
@@ -1644,6 +1820,12 @@
         <v>375300000</v>
       </c>
       <c r="J87">
+        <v>375300000</v>
+      </c>
+      <c r="K87">
+        <v>375300000</v>
+      </c>
+      <c r="L87">
         <v>375300000</v>
       </c>
     </row>
@@ -1672,9 +1854,15 @@
         <v xml:space="preserve">    Geri Alınmış Paylar (-)</v>
       </c>
       <c r="B92">
+        <v>-224928641</v>
+      </c>
+      <c r="C92">
+        <v>-224928641</v>
+      </c>
+      <c r="D92">
         <v>-80382359</v>
       </c>
-      <c r="F92">
+      <c r="H92">
         <v>0</v>
       </c>
     </row>
@@ -1691,15 +1879,21 @@
         <v>2408368625</v>
       </c>
       <c r="C94">
-        <v>2449618562</v>
+        <v>2408368625</v>
       </c>
       <c r="D94">
-        <v>2449618562</v>
+        <v>2408368625</v>
       </c>
       <c r="E94">
         <v>2449618562</v>
       </c>
       <c r="F94">
+        <v>2449618562</v>
+      </c>
+      <c r="G94">
+        <v>2449618562</v>
+      </c>
+      <c r="H94">
         <v>0</v>
       </c>
     </row>
@@ -1718,30 +1912,36 @@
         <v xml:space="preserve">    Kar veya Zararda Yeniden Sınıflandırılmayacak Birikmiş Diğer Kapsamlı Gelirler (Giderler)</v>
       </c>
       <c r="B97">
+        <v>4977236969</v>
+      </c>
+      <c r="C97">
+        <v>4435824191</v>
+      </c>
+      <c r="D97">
         <v>4092408150</v>
       </c>
-      <c r="C97">
+      <c r="E97">
         <v>3928380096</v>
       </c>
-      <c r="D97">
+      <c r="F97">
         <v>3600056097</v>
       </c>
-      <c r="E97">
+      <c r="G97">
         <v>3291542532</v>
       </c>
-      <c r="F97">
+      <c r="H97">
         <v>2854821813</v>
       </c>
-      <c r="G97">
+      <c r="I97">
         <v>3021703048</v>
       </c>
-      <c r="H97">
+      <c r="J97">
         <v>3073951240</v>
       </c>
-      <c r="I97">
+      <c r="K97">
         <v>1428858905</v>
       </c>
-      <c r="J97">
+      <c r="L97">
         <v>1213624580</v>
       </c>
     </row>
@@ -1755,27 +1955,33 @@
         <v xml:space="preserve">    Kardan Ayrılan Kısıtlanmış Yedekler</v>
       </c>
       <c r="B99">
+        <v>314018493</v>
+      </c>
+      <c r="C99">
+        <v>313021228</v>
+      </c>
+      <c r="D99">
         <v>168330389</v>
-      </c>
-      <c r="C99">
-        <v>88092587</v>
-      </c>
-      <c r="D99">
-        <v>88092587</v>
       </c>
       <c r="E99">
         <v>88092587</v>
       </c>
       <c r="F99">
+        <v>88092587</v>
+      </c>
+      <c r="G99">
+        <v>88092587</v>
+      </c>
+      <c r="H99">
         <v>151727187</v>
       </c>
-      <c r="G99">
+      <c r="I99">
         <v>5432591</v>
       </c>
-      <c r="H99">
+      <c r="J99">
         <v>1262249</v>
       </c>
-      <c r="I99">
+      <c r="K99">
         <v>1262249</v>
       </c>
     </row>
@@ -1788,6 +1994,15 @@
       <c r="A101" t="str">
         <v xml:space="preserve">    Diğer Yedekler</v>
       </c>
+      <c r="B101">
+        <v>3419205837</v>
+      </c>
+      <c r="C101">
+        <v>3419205837</v>
+      </c>
+      <c r="D101">
+        <v>0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
@@ -1799,30 +2014,36 @@
         <v xml:space="preserve">    Geçmiş Yıllar Kar/Zararları</v>
       </c>
       <c r="B103">
+        <v>6779460426</v>
+      </c>
+      <c r="C103">
+        <v>6462344773</v>
+      </c>
+      <c r="D103">
         <v>6987394253</v>
       </c>
-      <c r="C103">
+      <c r="E103">
         <v>6846915282</v>
       </c>
-      <c r="D103">
+      <c r="F103">
         <v>6555595022</v>
       </c>
-      <c r="E103">
+      <c r="G103">
         <v>6232940752</v>
       </c>
-      <c r="F103">
+      <c r="H103">
         <v>6142962453</v>
       </c>
-      <c r="G103">
+      <c r="I103">
         <v>6082609372</v>
       </c>
-      <c r="H103">
+      <c r="J103">
         <v>1858345787</v>
       </c>
-      <c r="I103">
+      <c r="K103">
         <v>889849940</v>
       </c>
-      <c r="J103">
+      <c r="L103">
         <v>-324774578</v>
       </c>
     </row>
@@ -1831,30 +2052,36 @@
         <v xml:space="preserve">    Dönem Net Kar/Zararı</v>
       </c>
       <c r="B104">
+        <v>101233506</v>
+      </c>
+      <c r="C104">
+        <v>-1023520289</v>
+      </c>
+      <c r="D104">
         <v>-691390420</v>
       </c>
-      <c r="C104">
+      <c r="E104">
         <v>419928977</v>
       </c>
-      <c r="D104">
+      <c r="F104">
         <v>-1267875028</v>
       </c>
-      <c r="E104">
+      <c r="G104">
         <v>-596789574</v>
       </c>
-      <c r="F104">
+      <c r="H104">
         <v>-352154456</v>
       </c>
-      <c r="G104">
+      <c r="I104">
         <v>166868878</v>
       </c>
-      <c r="H104">
+      <c r="J104">
         <v>2732801717</v>
       </c>
-      <c r="I104">
+      <c r="K104">
         <v>256922012</v>
       </c>
-      <c r="J104">
+      <c r="L104">
         <v>638274760</v>
       </c>
     </row>
@@ -1868,30 +2095,36 @@
         <v xml:space="preserve">    Toplam Özkaynaklar</v>
       </c>
       <c r="B106">
+        <v>18186036233</v>
+      </c>
+      <c r="C106">
+        <v>16201756742</v>
+      </c>
+      <c r="D106">
         <v>13296169656</v>
       </c>
-      <c r="C106">
+      <c r="E106">
         <v>14144376522</v>
       </c>
-      <c r="D106">
+      <c r="F106">
         <v>11836928258</v>
       </c>
-      <c r="E106">
+      <c r="G106">
         <v>11876845877</v>
       </c>
-      <c r="F106">
+      <c r="H106">
         <v>9172656997</v>
       </c>
-      <c r="G106">
+      <c r="I106">
         <v>9651913889</v>
       </c>
-      <c r="H106">
+      <c r="J106">
         <v>8041660993</v>
       </c>
-      <c r="I106">
+      <c r="K106">
         <v>2952193106</v>
       </c>
-      <c r="J106">
+      <c r="L106">
         <v>1902424762</v>
       </c>
     </row>
@@ -1900,30 +2133,36 @@
         <v xml:space="preserve">    Toplam Kaynaklar</v>
       </c>
       <c r="B107">
+        <v>39854256478</v>
+      </c>
+      <c r="C107">
+        <v>37262436491</v>
+      </c>
+      <c r="D107">
         <v>36501796333</v>
       </c>
-      <c r="C107">
+      <c r="E107">
         <v>35417727206</v>
       </c>
-      <c r="D107">
+      <c r="F107">
         <v>33569764405</v>
       </c>
-      <c r="E107">
+      <c r="G107">
         <v>26493092851</v>
       </c>
-      <c r="F107">
+      <c r="H107">
         <v>24244748042</v>
       </c>
-      <c r="G107">
+      <c r="I107">
         <v>23774886233</v>
       </c>
-      <c r="H107">
+      <c r="J107">
         <v>17504074272</v>
       </c>
-      <c r="I107">
+      <c r="K107">
         <v>10423088849</v>
       </c>
-      <c r="J107">
+      <c r="L107">
         <v>5880561823</v>
       </c>
     </row>
@@ -1932,28 +2171,31 @@
         <v xml:space="preserve">    Hedge Dahil Net Yabancı Para Pozisyonu</v>
       </c>
       <c r="C108">
+        <v>-6663307453</v>
+      </c>
+      <c r="E108">
         <v>-5165649348</v>
       </c>
-      <c r="D108">
+      <c r="F108">
         <v>-2689408691</v>
       </c>
-      <c r="E108">
+      <c r="G108">
         <v>2692590302</v>
       </c>
-      <c r="F108">
+      <c r="H108">
         <v>-3752658728</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J108"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L108"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:O50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -1968,6 +2210,8 @@
     <col min="11" max="11" customWidth="1" width="20"/>
     <col min="12" max="12" customWidth="1" width="20"/>
     <col min="13" max="13" customWidth="1" width="20"/>
+    <col min="14" max="14" customWidth="1" width="20"/>
+    <col min="15" max="15" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1975,39 +2219,45 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="C1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="D1" t="str">
+      <c r="F1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="E1" t="str">
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2024/3</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>2023/9</v>
       </c>
-      <c r="L1" t="str">
+      <c r="N1" t="str">
         <v>2022/12</v>
       </c>
-      <c r="M1" t="str">
+      <c r="O1" t="str">
         <v>2021/12</v>
       </c>
     </row>
@@ -2021,39 +2271,45 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
+        <v>3183651598</v>
+      </c>
+      <c r="C3">
+        <v>1070726087</v>
+      </c>
+      <c r="D3">
         <v>8121300519</v>
       </c>
-      <c r="C3">
+      <c r="E3">
         <v>6098066741</v>
       </c>
-      <c r="D3">
+      <c r="F3">
         <v>4165559903</v>
       </c>
-      <c r="E3">
+      <c r="G3">
         <v>1812631836</v>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>5839099243</v>
       </c>
-      <c r="G3">
+      <c r="I3">
         <v>4679175920</v>
       </c>
-      <c r="H3">
+      <c r="J3">
         <v>2690612513</v>
       </c>
-      <c r="I3">
+      <c r="K3">
         <v>2155362413</v>
       </c>
-      <c r="J3">
+      <c r="L3">
         <v>10560889333</v>
       </c>
-      <c r="K3">
+      <c r="M3">
         <v>5437984582</v>
       </c>
-      <c r="L3">
+      <c r="N3">
         <v>5445699997</v>
       </c>
-      <c r="M3">
+      <c r="O3">
         <v>1713903324</v>
       </c>
     </row>
@@ -2067,15 +2323,18 @@
         <v xml:space="preserve">    Yurt İçi Satışlar</v>
       </c>
       <c r="C5">
+        <v>1085964250</v>
+      </c>
+      <c r="E5">
         <v>6179091342</v>
       </c>
-      <c r="D5">
+      <c r="F5">
         <v>4152979323</v>
       </c>
-      <c r="E5">
+      <c r="G5">
         <v>1770077332</v>
       </c>
-      <c r="G5">
+      <c r="I5">
         <v>4573657019</v>
       </c>
     </row>
@@ -2083,13 +2342,13 @@
       <c r="A6" t="str">
         <v xml:space="preserve">    Yurt Dışı Satışlar</v>
       </c>
-      <c r="C6">
+      <c r="E6">
         <v>50868484</v>
       </c>
-      <c r="D6">
+      <c r="F6">
         <v>773403</v>
       </c>
-      <c r="G6">
+      <c r="I6">
         <v>52388107</v>
       </c>
     </row>
@@ -2098,39 +2357,45 @@
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
       <c r="B7">
+        <v>-2789443819</v>
+      </c>
+      <c r="C7">
+        <v>-1042905779</v>
+      </c>
+      <c r="D7">
         <v>-6363584108</v>
       </c>
-      <c r="C7">
+      <c r="E7">
         <v>-4845299007</v>
       </c>
-      <c r="D7">
+      <c r="F7">
         <v>-3304324744</v>
       </c>
-      <c r="E7">
+      <c r="G7">
         <v>-1358355061</v>
       </c>
-      <c r="F7">
+      <c r="H7">
         <v>-4978372963</v>
       </c>
-      <c r="G7">
+      <c r="I7">
         <v>-3580706982</v>
       </c>
-      <c r="H7">
+      <c r="J7">
         <v>-2091055746</v>
       </c>
-      <c r="I7">
+      <c r="K7">
         <v>-1598814834</v>
       </c>
-      <c r="J7">
+      <c r="L7">
         <v>-8780724257</v>
       </c>
-      <c r="K7">
+      <c r="M7">
         <v>-4876876107</v>
       </c>
-      <c r="L7">
+      <c r="N7">
         <v>-4897385532</v>
       </c>
-      <c r="M7">
+      <c r="O7">
         <v>-1359284431</v>
       </c>
     </row>
@@ -2139,39 +2404,45 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
+        <v>394207779</v>
+      </c>
+      <c r="C8">
+        <v>27820308</v>
+      </c>
+      <c r="D8">
         <v>1757716411</v>
       </c>
-      <c r="C8">
+      <c r="E8">
         <v>1252767734</v>
       </c>
-      <c r="D8">
+      <c r="F8">
         <v>861235159</v>
       </c>
-      <c r="E8">
+      <c r="G8">
         <v>454276775</v>
       </c>
-      <c r="F8">
+      <c r="H8">
         <v>860726280</v>
       </c>
-      <c r="G8">
+      <c r="I8">
         <v>1098468938</v>
       </c>
-      <c r="H8">
+      <c r="J8">
         <v>599556767</v>
       </c>
-      <c r="I8">
+      <c r="K8">
         <v>556547579</v>
       </c>
-      <c r="J8">
+      <c r="L8">
         <v>1780165076</v>
       </c>
-      <c r="K8">
+      <c r="M8">
         <v>561108475</v>
       </c>
-      <c r="L8">
+      <c r="N8">
         <v>548314465</v>
       </c>
-      <c r="M8">
+      <c r="O8">
         <v>354618893</v>
       </c>
     </row>
@@ -2200,39 +2471,45 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
+        <v>394207779</v>
+      </c>
+      <c r="C13">
+        <v>27820308</v>
+      </c>
+      <c r="D13">
         <v>1757716411</v>
       </c>
-      <c r="C13">
+      <c r="E13">
         <v>1252767734</v>
       </c>
-      <c r="D13">
+      <c r="F13">
         <v>861235159</v>
       </c>
-      <c r="E13">
+      <c r="G13">
         <v>454276775</v>
       </c>
-      <c r="F13">
+      <c r="H13">
         <v>860726280</v>
       </c>
-      <c r="G13">
+      <c r="I13">
         <v>1098468938</v>
       </c>
-      <c r="H13">
+      <c r="J13">
         <v>599556767</v>
       </c>
-      <c r="I13">
+      <c r="K13">
         <v>556547579</v>
       </c>
-      <c r="J13">
+      <c r="L13">
         <v>1780165076</v>
       </c>
-      <c r="K13">
+      <c r="M13">
         <v>561108475</v>
       </c>
-      <c r="L13">
+      <c r="N13">
         <v>548314465</v>
       </c>
-      <c r="M13">
+      <c r="O13">
         <v>354618893</v>
       </c>
     </row>
@@ -2242,39 +2519,45 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
+        <v>-208380813</v>
+      </c>
+      <c r="C15">
+        <v>-98450101</v>
+      </c>
+      <c r="D15">
         <v>-289281106</v>
       </c>
-      <c r="C15">
+      <c r="E15">
         <v>-241002249</v>
       </c>
-      <c r="D15">
+      <c r="F15">
         <v>-166581310</v>
       </c>
-      <c r="E15">
+      <c r="G15">
         <v>-89323077</v>
       </c>
-      <c r="F15">
+      <c r="H15">
         <v>-403063680</v>
       </c>
-      <c r="G15">
+      <c r="I15">
         <v>-295111434</v>
       </c>
-      <c r="H15">
+      <c r="J15">
         <v>-199753904</v>
       </c>
-      <c r="I15">
+      <c r="K15">
         <v>-85459467</v>
       </c>
-      <c r="J15">
+      <c r="L15">
         <v>-184813277</v>
       </c>
-      <c r="K15">
+      <c r="M15">
         <v>-141786567</v>
       </c>
-      <c r="L15">
+      <c r="N15">
         <v>-88998712</v>
       </c>
-      <c r="M15">
+      <c r="O15">
         <v>-38508405</v>
       </c>
     </row>
@@ -2283,39 +2566,45 @@
         <v xml:space="preserve">    Pazarlama, Satış ve Dağıtım Giderleri (-)</v>
       </c>
       <c r="B16">
+        <v>-19689676</v>
+      </c>
+      <c r="C16">
+        <v>-7267124</v>
+      </c>
+      <c r="D16">
         <v>-28098936</v>
       </c>
-      <c r="C16">
+      <c r="E16">
         <v>-51494310</v>
       </c>
-      <c r="D16">
+      <c r="F16">
         <v>-44450136</v>
       </c>
-      <c r="E16">
+      <c r="G16">
         <v>-35460262</v>
       </c>
-      <c r="F16">
+      <c r="H16">
         <v>-80559969</v>
       </c>
-      <c r="G16">
+      <c r="I16">
         <v>-52345012</v>
       </c>
-      <c r="H16">
+      <c r="J16">
         <v>-25606793</v>
       </c>
-      <c r="I16">
+      <c r="K16">
         <v>-9863847</v>
       </c>
-      <c r="J16">
+      <c r="L16">
         <v>-79372583</v>
       </c>
-      <c r="K16">
+      <c r="M16">
         <v>-65845170</v>
       </c>
-      <c r="L16">
+      <c r="N16">
         <v>-55191032</v>
       </c>
-      <c r="M16">
+      <c r="O16">
         <v>-2929335</v>
       </c>
     </row>
@@ -2324,39 +2613,45 @@
         <v xml:space="preserve">    Araştırma ve Geliştirme Giderleri (-)</v>
       </c>
       <c r="B17">
+        <v>-71354735</v>
+      </c>
+      <c r="C17">
+        <v>-42323369</v>
+      </c>
+      <c r="D17">
         <v>-173143073</v>
       </c>
-      <c r="C17">
+      <c r="E17">
         <v>-128415923</v>
       </c>
-      <c r="D17">
+      <c r="F17">
         <v>-81346103</v>
       </c>
-      <c r="E17">
+      <c r="G17">
         <v>-38054493</v>
       </c>
-      <c r="F17">
+      <c r="H17">
         <v>-128386426</v>
       </c>
-      <c r="G17">
+      <c r="I17">
         <v>-101435738</v>
       </c>
-      <c r="H17">
+      <c r="J17">
         <v>-85424727</v>
       </c>
-      <c r="I17">
+      <c r="K17">
         <v>-20951600</v>
       </c>
-      <c r="J17">
+      <c r="L17">
         <v>-66714947</v>
       </c>
-      <c r="K17">
+      <c r="M17">
         <v>-51104393</v>
       </c>
-      <c r="L17">
+      <c r="N17">
         <v>-35451633</v>
       </c>
-      <c r="M17">
+      <c r="O17">
         <v>-2096128</v>
       </c>
     </row>
@@ -2365,39 +2660,45 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
+        <v>195970264</v>
+      </c>
+      <c r="C18">
+        <v>32935530</v>
+      </c>
+      <c r="D18">
         <v>121247358</v>
       </c>
-      <c r="C18">
+      <c r="E18">
         <v>376260015</v>
       </c>
-      <c r="D18">
-        <v>225612241</v>
-      </c>
-      <c r="E18">
-        <v>131693988</v>
-      </c>
       <c r="F18">
+        <v>70192676</v>
+      </c>
+      <c r="G18">
+        <v>56230474</v>
+      </c>
+      <c r="H18">
         <v>874522023</v>
       </c>
-      <c r="G18">
+      <c r="I18">
         <v>509186803</v>
       </c>
-      <c r="H18">
+      <c r="J18">
         <v>515706424</v>
       </c>
-      <c r="I18">
+      <c r="K18">
         <v>191995918</v>
       </c>
-      <c r="J18">
+      <c r="L18">
         <v>217574273</v>
       </c>
-      <c r="K18">
+      <c r="M18">
         <v>174149434</v>
       </c>
-      <c r="L18">
+      <c r="N18">
         <v>366768178</v>
       </c>
-      <c r="M18">
+      <c r="O18">
         <v>173916069</v>
       </c>
     </row>
@@ -2406,39 +2707,45 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
+        <v>-2183790465</v>
+      </c>
+      <c r="C19">
+        <v>-209979584</v>
+      </c>
+      <c r="D19">
         <v>-684985922</v>
       </c>
-      <c r="C19">
+      <c r="E19">
         <v>-306675558</v>
       </c>
-      <c r="D19">
+      <c r="F19">
         <v>-861436527</v>
       </c>
-      <c r="E19">
+      <c r="G19">
         <v>-371200196</v>
       </c>
-      <c r="F19">
+      <c r="H19">
         <v>-35676786</v>
       </c>
-      <c r="G19">
+      <c r="I19">
         <v>-35782802</v>
       </c>
-      <c r="H19">
+      <c r="J19">
         <v>-30600605</v>
       </c>
-      <c r="I19">
+      <c r="K19">
         <v>-19657385</v>
       </c>
-      <c r="J19">
+      <c r="L19">
         <v>-74806561</v>
       </c>
-      <c r="K19">
+      <c r="M19">
         <v>-8204213</v>
       </c>
-      <c r="L19">
+      <c r="N19">
         <v>-13797687</v>
       </c>
-      <c r="M19">
+      <c r="O19">
         <v>-13028332</v>
       </c>
     </row>
@@ -2452,39 +2759,45 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
+        <v>-1893037646</v>
+      </c>
+      <c r="C21">
+        <v>-297264340</v>
+      </c>
+      <c r="D21">
         <v>703454732</v>
       </c>
-      <c r="C21">
+      <c r="E21">
         <v>901439709</v>
       </c>
-      <c r="D21">
-        <v>-66966676</v>
-      </c>
-      <c r="E21">
-        <v>51932735</v>
-      </c>
       <c r="F21">
+        <v>-222386241</v>
+      </c>
+      <c r="G21">
+        <v>-23530779</v>
+      </c>
+      <c r="H21">
         <v>1087561442</v>
       </c>
-      <c r="G21">
+      <c r="I21">
         <v>1122980755</v>
       </c>
-      <c r="H21">
+      <c r="J21">
         <v>773877162</v>
       </c>
-      <c r="I21">
+      <c r="K21">
         <v>612611198</v>
       </c>
-      <c r="J21">
+      <c r="L21">
         <v>1592031981</v>
       </c>
-      <c r="K21">
+      <c r="M21">
         <v>468317566</v>
       </c>
-      <c r="L21">
+      <c r="N21">
         <v>721643579</v>
       </c>
-      <c r="M21">
+      <c r="O21">
         <v>471972762</v>
       </c>
     </row>
@@ -2504,9 +2817,15 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
       <c r="B25">
+        <v>1591641</v>
+      </c>
+      <c r="C25">
+        <v>3145</v>
+      </c>
+      <c r="D25">
         <v>7790504</v>
       </c>
-      <c r="F25">
+      <c r="H25">
         <v>0</v>
       </c>
     </row>
@@ -2514,19 +2833,19 @@
       <c r="A26" t="str">
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Giderler (-)</v>
       </c>
-      <c r="B26">
+      <c r="D26">
         <v>0</v>
       </c>
-      <c r="C26">
+      <c r="E26">
         <v>0</v>
       </c>
-      <c r="F26">
+      <c r="H26">
         <v>-5308857</v>
       </c>
-      <c r="G26">
+      <c r="I26">
         <v>-5308875</v>
       </c>
-      <c r="J26">
+      <c r="L26">
         <v>0</v>
       </c>
     </row>
@@ -2565,39 +2884,45 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
+        <v>-1891446005</v>
+      </c>
+      <c r="C33">
+        <v>-297261195</v>
+      </c>
+      <c r="D33">
         <v>711245236</v>
       </c>
-      <c r="C33">
+      <c r="E33">
         <v>901439709</v>
       </c>
-      <c r="D33">
-        <v>-66966676</v>
-      </c>
-      <c r="E33">
-        <v>51932735</v>
-      </c>
       <c r="F33">
+        <v>-222386241</v>
+      </c>
+      <c r="G33">
+        <v>-23530779</v>
+      </c>
+      <c r="H33">
         <v>1082252585</v>
       </c>
-      <c r="G33">
+      <c r="I33">
         <v>1117671880</v>
       </c>
-      <c r="H33">
+      <c r="J33">
         <v>773877162</v>
       </c>
-      <c r="I33">
+      <c r="K33">
         <v>612611198</v>
       </c>
-      <c r="J33">
+      <c r="L33">
         <v>1592031981</v>
       </c>
-      <c r="K33">
+      <c r="M33">
         <v>468317566</v>
       </c>
-      <c r="L33">
+      <c r="N33">
         <v>721643579</v>
       </c>
-      <c r="M33">
+      <c r="O33">
         <v>471972762</v>
       </c>
     </row>
@@ -2607,9 +2932,21 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
       <c r="B35">
+        <v>45249670</v>
+      </c>
+      <c r="C35">
+        <v>24315263</v>
+      </c>
+      <c r="D35">
         <v>363253994</v>
       </c>
       <c r="F35">
+        <v>155419565</v>
+      </c>
+      <c r="G35">
+        <v>75463514</v>
+      </c>
+      <c r="H35">
         <v>15162214</v>
       </c>
     </row>
@@ -2618,39 +2955,45 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
+        <v>-810843317</v>
+      </c>
+      <c r="C36">
+        <v>-472918475</v>
+      </c>
+      <c r="D36">
         <v>-1480846266</v>
       </c>
-      <c r="C36">
+      <c r="E36">
         <v>-1138422844</v>
       </c>
-      <c r="D36">
+      <c r="F36">
         <v>-632564435</v>
       </c>
-      <c r="E36">
+      <c r="G36">
         <v>-329358629</v>
       </c>
-      <c r="F36">
+      <c r="H36">
         <v>-1410029383</v>
       </c>
-      <c r="G36">
+      <c r="I36">
         <v>-1007904888</v>
       </c>
-      <c r="H36">
+      <c r="J36">
         <v>-694725354</v>
       </c>
-      <c r="I36">
+      <c r="K36">
         <v>-133451278</v>
       </c>
-      <c r="J36">
+      <c r="L36">
         <v>-388417772</v>
       </c>
-      <c r="K36">
+      <c r="M36">
         <v>-223050405</v>
       </c>
-      <c r="L36">
+      <c r="N36">
         <v>-442083381</v>
       </c>
-      <c r="M36">
+      <c r="O36">
         <v>-157548349</v>
       </c>
     </row>
@@ -2664,39 +3007,45 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
+        <v>-2657039652</v>
+      </c>
+      <c r="C38">
+        <v>-745864407</v>
+      </c>
+      <c r="D38">
         <v>-406347036</v>
       </c>
-      <c r="C38">
+      <c r="E38">
         <v>-236983135</v>
       </c>
-      <c r="D38">
+      <c r="F38">
         <v>-699531111</v>
       </c>
-      <c r="E38">
+      <c r="G38">
         <v>-277425894</v>
       </c>
-      <c r="F38">
+      <c r="H38">
         <v>-312614584</v>
       </c>
-      <c r="G38">
+      <c r="I38">
         <v>109766992</v>
       </c>
-      <c r="H38">
+      <c r="J38">
         <v>79151808</v>
       </c>
-      <c r="I38">
+      <c r="K38">
         <v>479159920</v>
       </c>
-      <c r="J38">
+      <c r="L38">
         <v>1203614209</v>
       </c>
-      <c r="K38">
+      <c r="M38">
         <v>245267161</v>
       </c>
-      <c r="L38">
+      <c r="N38">
         <v>279560198</v>
       </c>
-      <c r="M38">
+      <c r="O38">
         <v>314424413</v>
       </c>
     </row>
@@ -2706,39 +3055,45 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
       <c r="B40">
+        <v>2758273158</v>
+      </c>
+      <c r="C40">
+        <v>-277655882</v>
+      </c>
+      <c r="D40">
         <v>-285043384</v>
       </c>
-      <c r="C40">
+      <c r="E40">
         <v>656912112</v>
       </c>
-      <c r="D40">
+      <c r="F40">
         <v>-568343917</v>
       </c>
-      <c r="E40">
+      <c r="G40">
         <v>-319363680</v>
       </c>
-      <c r="F40">
+      <c r="H40">
         <v>-39539872</v>
       </c>
-      <c r="G40">
+      <c r="I40">
         <v>57101886</v>
       </c>
-      <c r="H40">
+      <c r="J40">
         <v>681710574</v>
       </c>
-      <c r="I40">
+      <c r="K40">
         <v>264285801</v>
       </c>
-      <c r="J40">
+      <c r="L40">
         <v>1529187508</v>
       </c>
-      <c r="K40">
+      <c r="M40">
         <v>-168803418</v>
       </c>
-      <c r="L40">
+      <c r="N40">
         <v>-22638186</v>
       </c>
-      <c r="M40">
+      <c r="O40">
         <v>323850347</v>
       </c>
     </row>
@@ -2746,22 +3101,16 @@
       <c r="A41" t="str">
         <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
       </c>
-      <c r="C41">
-        <v>0</v>
-      </c>
-      <c r="D41">
-        <v>0</v>
-      </c>
       <c r="E41">
         <v>0</v>
       </c>
-      <c r="H41">
+      <c r="J41">
         <v>0</v>
       </c>
-      <c r="J41">
+      <c r="L41">
         <v>-50517427</v>
       </c>
-      <c r="K41">
+      <c r="M41">
         <v>-62656456</v>
       </c>
     </row>
@@ -2770,39 +3119,45 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
       <c r="B42">
+        <v>2758273158</v>
+      </c>
+      <c r="C42">
+        <v>-277655882</v>
+      </c>
+      <c r="D42">
         <v>-285043384</v>
       </c>
-      <c r="C42">
+      <c r="E42">
         <v>656912112</v>
       </c>
-      <c r="D42">
+      <c r="F42">
         <v>-568343917</v>
       </c>
-      <c r="E42">
+      <c r="G42">
         <v>-319363680</v>
       </c>
-      <c r="F42">
+      <c r="H42">
         <v>-39539872</v>
       </c>
-      <c r="G42">
+      <c r="I42">
         <v>57101886</v>
       </c>
-      <c r="H42">
+      <c r="J42">
         <v>681710574</v>
       </c>
-      <c r="I42">
+      <c r="K42">
         <v>264285801</v>
       </c>
-      <c r="J42">
+      <c r="L42">
         <v>1579704935</v>
       </c>
-      <c r="K42">
+      <c r="M42">
         <v>-106146962</v>
       </c>
-      <c r="L42">
+      <c r="N42">
         <v>-22638186</v>
       </c>
-      <c r="M42">
+      <c r="O42">
         <v>323850347</v>
       </c>
     </row>
@@ -2811,39 +3166,45 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
+        <v>101233506</v>
+      </c>
+      <c r="C43">
+        <v>-1023520289</v>
+      </c>
+      <c r="D43">
         <v>-691390420</v>
       </c>
-      <c r="C43">
+      <c r="E43">
         <v>419928977</v>
       </c>
-      <c r="D43">
+      <c r="F43">
         <v>-1267875028</v>
       </c>
-      <c r="E43">
+      <c r="G43">
         <v>-596789574</v>
       </c>
-      <c r="F43">
+      <c r="H43">
         <v>-352154456</v>
       </c>
-      <c r="G43">
+      <c r="I43">
         <v>166868878</v>
       </c>
-      <c r="H43">
+      <c r="J43">
         <v>760862382</v>
       </c>
-      <c r="I43">
+      <c r="K43">
         <v>743445721</v>
       </c>
-      <c r="J43">
+      <c r="L43">
         <v>2732801717</v>
       </c>
-      <c r="K43">
+      <c r="M43">
         <v>76463743</v>
       </c>
-      <c r="L43">
+      <c r="N43">
         <v>256922012</v>
       </c>
-      <c r="M43">
+      <c r="O43">
         <v>638274760</v>
       </c>
     </row>
@@ -2851,7 +3212,7 @@
       <c r="A44" t="str">
         <v xml:space="preserve">    Durdurulan Faaliyetler Dönem Karı/Zararı</v>
       </c>
-      <c r="J44">
+      <c r="L44">
         <v>0</v>
       </c>
     </row>
@@ -2861,39 +3222,45 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
+        <v>101233506</v>
+      </c>
+      <c r="C46">
+        <v>-1023520289</v>
+      </c>
+      <c r="D46">
         <v>-691390420</v>
       </c>
-      <c r="C46">
+      <c r="E46">
         <v>419928977</v>
       </c>
-      <c r="D46">
+      <c r="F46">
         <v>-1267875028</v>
       </c>
-      <c r="E46">
+      <c r="G46">
         <v>-596789574</v>
       </c>
-      <c r="F46">
+      <c r="H46">
         <v>-352154456</v>
       </c>
-      <c r="G46">
+      <c r="I46">
         <v>166868878</v>
       </c>
-      <c r="H46">
+      <c r="J46">
         <v>760862382</v>
       </c>
-      <c r="I46">
+      <c r="K46">
         <v>743445721</v>
       </c>
-      <c r="J46">
+      <c r="L46">
         <v>2732801717</v>
       </c>
-      <c r="K46">
+      <c r="M46">
         <v>76463743</v>
       </c>
-      <c r="L46">
+      <c r="N46">
         <v>256922012</v>
       </c>
-      <c r="M46">
+      <c r="O46">
         <v>638274760</v>
       </c>
     </row>
@@ -2928,45 +3295,57 @@
       <c r="J47">
         <v>0</v>
       </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
+        <v>101233506</v>
+      </c>
+      <c r="C48">
+        <v>-1023520289</v>
+      </c>
+      <c r="D48">
         <v>-691390420</v>
       </c>
-      <c r="C48">
+      <c r="E48">
         <v>419928977</v>
       </c>
-      <c r="D48">
+      <c r="F48">
         <v>-1267875028</v>
       </c>
-      <c r="E48">
+      <c r="G48">
         <v>-596789574</v>
       </c>
-      <c r="F48">
+      <c r="H48">
         <v>-352154456</v>
       </c>
-      <c r="G48">
+      <c r="I48">
         <v>166868878</v>
       </c>
-      <c r="H48">
+      <c r="J48">
         <v>760862382</v>
       </c>
-      <c r="I48">
+      <c r="K48">
         <v>743445721</v>
       </c>
-      <c r="J48">
+      <c r="L48">
         <v>2732801717</v>
       </c>
-      <c r="K48">
+      <c r="M48">
         <v>76463743</v>
       </c>
-      <c r="L48">
+      <c r="N48">
         <v>256922012</v>
       </c>
-      <c r="M48">
+      <c r="O48">
         <v>638274760</v>
       </c>
     </row>
@@ -2976,52 +3355,58 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
+        <v>481293772</v>
+      </c>
+      <c r="C50">
+        <v>179108248</v>
+      </c>
+      <c r="D50">
         <v>898156020</v>
       </c>
-      <c r="C50">
+      <c r="E50">
         <v>516520103</v>
       </c>
-      <c r="D50">
+      <c r="F50">
         <v>327193791</v>
       </c>
-      <c r="E50">
+      <c r="G50">
         <v>153064451</v>
       </c>
-      <c r="F50">
+      <c r="H50">
         <v>514126467</v>
       </c>
-      <c r="G50">
+      <c r="I50">
         <v>533555991</v>
       </c>
-      <c r="H50">
+      <c r="J50">
         <v>405934981</v>
       </c>
-      <c r="I50">
+      <c r="K50">
         <v>198657431</v>
       </c>
-      <c r="J50">
+      <c r="L50">
         <v>517711407</v>
       </c>
-      <c r="K50">
+      <c r="M50">
         <v>278996265</v>
       </c>
-      <c r="L50">
+      <c r="N50">
         <v>328056956</v>
       </c>
-      <c r="M50">
+      <c r="O50">
         <v>107953692</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:O50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -3036,6 +3421,8 @@
     <col min="11" max="11" customWidth="1" width="20"/>
     <col min="12" max="12" customWidth="1" width="20"/>
     <col min="13" max="13" customWidth="1" width="20"/>
+    <col min="14" max="14" customWidth="1" width="20"/>
+    <col min="15" max="15" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3043,39 +3430,45 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="C1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="D1" t="str">
+      <c r="F1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="E1" t="str">
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2024/3</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>2023/9</v>
       </c>
-      <c r="L1" t="str">
+      <c r="N1" t="str">
         <v>2022/12</v>
       </c>
-      <c r="M1" t="str">
+      <c r="O1" t="str">
         <v>2021/12</v>
       </c>
     </row>
@@ -3089,30 +3482,36 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
+        <v>2112925511</v>
+      </c>
+      <c r="C3">
+        <v>1070726087</v>
+      </c>
+      <c r="D3">
         <v>2023233778</v>
       </c>
-      <c r="C3">
+      <c r="E3">
         <v>1932506838</v>
       </c>
-      <c r="D3">
+      <c r="F3">
         <v>2352928067</v>
       </c>
-      <c r="E3">
+      <c r="G3">
         <v>1812631836</v>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>1159923323</v>
       </c>
-      <c r="G3">
+      <c r="I3">
         <v>1988563407</v>
       </c>
-      <c r="H3">
+      <c r="J3">
         <v>535250100</v>
       </c>
-      <c r="I3">
+      <c r="K3">
         <v>2155362413</v>
       </c>
-      <c r="J3">
+      <c r="L3">
         <v>5122904751</v>
       </c>
     </row>
@@ -3126,12 +3525,15 @@
         <v xml:space="preserve">    Yurt İçi Satışlar</v>
       </c>
       <c r="C5">
+        <v>1085964250</v>
+      </c>
+      <c r="E5">
         <v>2026112019</v>
       </c>
-      <c r="D5">
+      <c r="F5">
         <v>2382901991</v>
       </c>
-      <c r="E5">
+      <c r="G5">
         <v>1770077332</v>
       </c>
     </row>
@@ -3139,7 +3541,7 @@
       <c r="A6" t="str">
         <v xml:space="preserve">    Yurt Dışı Satışlar</v>
       </c>
-      <c r="C6">
+      <c r="E6">
         <v>50095081</v>
       </c>
     </row>
@@ -3148,30 +3550,36 @@
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
       <c r="B7">
+        <v>-1746538040</v>
+      </c>
+      <c r="C7">
+        <v>-1042905779</v>
+      </c>
+      <c r="D7">
         <v>-1518285101</v>
       </c>
-      <c r="C7">
+      <c r="E7">
         <v>-1540974263</v>
       </c>
-      <c r="D7">
+      <c r="F7">
         <v>-1945969683</v>
       </c>
-      <c r="E7">
+      <c r="G7">
         <v>-1358355061</v>
       </c>
-      <c r="F7">
+      <c r="H7">
         <v>-1397665981</v>
       </c>
-      <c r="G7">
+      <c r="I7">
         <v>-1489651236</v>
       </c>
-      <c r="H7">
+      <c r="J7">
         <v>-492240912</v>
       </c>
-      <c r="I7">
+      <c r="K7">
         <v>-1598814834</v>
       </c>
-      <c r="J7">
+      <c r="L7">
         <v>-3903848150</v>
       </c>
     </row>
@@ -3180,30 +3588,36 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
+        <v>366387471</v>
+      </c>
+      <c r="C8">
+        <v>27820308</v>
+      </c>
+      <c r="D8">
         <v>504948677</v>
       </c>
-      <c r="C8">
+      <c r="E8">
         <v>391532575</v>
       </c>
-      <c r="D8">
+      <c r="F8">
         <v>406958384</v>
       </c>
-      <c r="E8">
+      <c r="G8">
         <v>454276775</v>
       </c>
-      <c r="F8">
+      <c r="H8">
         <v>-237742658</v>
       </c>
-      <c r="G8">
+      <c r="I8">
         <v>498912171</v>
       </c>
-      <c r="H8">
+      <c r="J8">
         <v>43009188</v>
       </c>
-      <c r="I8">
+      <c r="K8">
         <v>556547579</v>
       </c>
-      <c r="J8">
+      <c r="L8">
         <v>1219056601</v>
       </c>
     </row>
@@ -3232,30 +3646,36 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
+        <v>366387471</v>
+      </c>
+      <c r="C13">
+        <v>27820308</v>
+      </c>
+      <c r="D13">
         <v>504948677</v>
       </c>
-      <c r="C13">
+      <c r="E13">
         <v>391532575</v>
       </c>
-      <c r="D13">
+      <c r="F13">
         <v>406958384</v>
       </c>
-      <c r="E13">
+      <c r="G13">
         <v>454276775</v>
       </c>
-      <c r="F13">
+      <c r="H13">
         <v>-237742658</v>
       </c>
-      <c r="G13">
+      <c r="I13">
         <v>498912171</v>
       </c>
-      <c r="H13">
+      <c r="J13">
         <v>43009188</v>
       </c>
-      <c r="I13">
+      <c r="K13">
         <v>556547579</v>
       </c>
-      <c r="J13">
+      <c r="L13">
         <v>1219056601</v>
       </c>
     </row>
@@ -3265,30 +3685,36 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
+        <v>-109930712</v>
+      </c>
+      <c r="C15">
+        <v>-98450101</v>
+      </c>
+      <c r="D15">
         <v>-48278857</v>
       </c>
-      <c r="C15">
+      <c r="E15">
         <v>-74420939</v>
       </c>
-      <c r="D15">
+      <c r="F15">
         <v>-77258233</v>
       </c>
-      <c r="E15">
+      <c r="G15">
         <v>-89323077</v>
       </c>
-      <c r="F15">
+      <c r="H15">
         <v>-107952246</v>
       </c>
-      <c r="G15">
+      <c r="I15">
         <v>-95357530</v>
       </c>
-      <c r="H15">
+      <c r="J15">
         <v>-114294437</v>
       </c>
-      <c r="I15">
+      <c r="K15">
         <v>-85459467</v>
       </c>
-      <c r="J15">
+      <c r="L15">
         <v>-43026710</v>
       </c>
     </row>
@@ -3297,30 +3723,36 @@
         <v xml:space="preserve">    Pazarlama, Satış ve Dağıtım Giderleri (-)</v>
       </c>
       <c r="B16">
+        <v>-12422552</v>
+      </c>
+      <c r="C16">
+        <v>-7267124</v>
+      </c>
+      <c r="D16">
         <v>23395374</v>
       </c>
-      <c r="C16">
+      <c r="E16">
         <v>-7044174</v>
       </c>
-      <c r="D16">
+      <c r="F16">
         <v>-8989874</v>
       </c>
-      <c r="E16">
+      <c r="G16">
         <v>-35460262</v>
       </c>
-      <c r="F16">
+      <c r="H16">
         <v>-28214957</v>
       </c>
-      <c r="G16">
+      <c r="I16">
         <v>-26738219</v>
       </c>
-      <c r="H16">
+      <c r="J16">
         <v>-15742946</v>
       </c>
-      <c r="I16">
+      <c r="K16">
         <v>-9863847</v>
       </c>
-      <c r="J16">
+      <c r="L16">
         <v>-13527413</v>
       </c>
     </row>
@@ -3329,30 +3761,36 @@
         <v xml:space="preserve">    Araştırma ve Geliştirme Giderleri (-)</v>
       </c>
       <c r="B17">
+        <v>-29031366</v>
+      </c>
+      <c r="C17">
+        <v>-42323369</v>
+      </c>
+      <c r="D17">
         <v>-44727150</v>
       </c>
-      <c r="C17">
+      <c r="E17">
         <v>-47069820</v>
       </c>
-      <c r="D17">
+      <c r="F17">
         <v>-43291610</v>
       </c>
-      <c r="E17">
+      <c r="G17">
         <v>-38054493</v>
       </c>
-      <c r="F17">
+      <c r="H17">
         <v>-26950688</v>
       </c>
-      <c r="G17">
+      <c r="I17">
         <v>-16011011</v>
       </c>
-      <c r="H17">
+      <c r="J17">
         <v>-64473127</v>
       </c>
-      <c r="I17">
+      <c r="K17">
         <v>-20951600</v>
       </c>
-      <c r="J17">
+      <c r="L17">
         <v>-15610554</v>
       </c>
     </row>
@@ -3361,30 +3799,36 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
+        <v>163034734</v>
+      </c>
+      <c r="C18">
+        <v>32935530</v>
+      </c>
+      <c r="D18">
         <v>-255012657</v>
       </c>
-      <c r="C18">
-        <v>150647774</v>
-      </c>
-      <c r="D18">
-        <v>93918253</v>
-      </c>
       <c r="E18">
-        <v>131693988</v>
+        <v>306067339</v>
       </c>
       <c r="F18">
+        <v>13962202</v>
+      </c>
+      <c r="G18">
+        <v>56230474</v>
+      </c>
+      <c r="H18">
         <v>365335220</v>
       </c>
-      <c r="G18">
+      <c r="I18">
         <v>-6519621</v>
       </c>
-      <c r="H18">
+      <c r="J18">
         <v>323710506</v>
       </c>
-      <c r="I18">
+      <c r="K18">
         <v>191995918</v>
       </c>
-      <c r="J18">
+      <c r="L18">
         <v>43424839</v>
       </c>
     </row>
@@ -3393,30 +3837,36 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
+        <v>-1973810881</v>
+      </c>
+      <c r="C19">
+        <v>-209979584</v>
+      </c>
+      <c r="D19">
         <v>-378310364</v>
       </c>
-      <c r="C19">
+      <c r="E19">
         <v>554760969</v>
       </c>
-      <c r="D19">
+      <c r="F19">
         <v>-490236331</v>
       </c>
-      <c r="E19">
+      <c r="G19">
         <v>-371200196</v>
       </c>
-      <c r="F19">
+      <c r="H19">
         <v>106016</v>
       </c>
-      <c r="G19">
+      <c r="I19">
         <v>-5182197</v>
       </c>
-      <c r="H19">
+      <c r="J19">
         <v>-10943220</v>
       </c>
-      <c r="I19">
+      <c r="K19">
         <v>-19657385</v>
       </c>
-      <c r="J19">
+      <c r="L19">
         <v>-66602348</v>
       </c>
     </row>
@@ -3430,30 +3880,36 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
+        <v>-1595773306</v>
+      </c>
+      <c r="C21">
+        <v>-297264340</v>
+      </c>
+      <c r="D21">
         <v>-197984977</v>
       </c>
-      <c r="C21">
-        <v>968406385</v>
-      </c>
-      <c r="D21">
-        <v>-118899411</v>
-      </c>
       <c r="E21">
-        <v>51932735</v>
+        <v>1123825950</v>
       </c>
       <c r="F21">
+        <v>-198855462</v>
+      </c>
+      <c r="G21">
+        <v>-23530779</v>
+      </c>
+      <c r="H21">
         <v>-35419313</v>
       </c>
-      <c r="G21">
+      <c r="I21">
         <v>349103593</v>
       </c>
-      <c r="H21">
+      <c r="J21">
         <v>161265964</v>
       </c>
-      <c r="I21">
+      <c r="K21">
         <v>612611198</v>
       </c>
-      <c r="J21">
+      <c r="L21">
         <v>1123714415</v>
       </c>
     </row>
@@ -3472,15 +3928,21 @@
       <c r="A25" t="str">
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
+      <c r="B25">
+        <v>1588496</v>
+      </c>
+      <c r="C25">
+        <v>3145</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Giderler (-)</v>
       </c>
-      <c r="B26">
+      <c r="D26">
         <v>0</v>
       </c>
-      <c r="F26">
+      <c r="H26">
         <v>18</v>
       </c>
     </row>
@@ -3519,30 +3981,36 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
+        <v>-1594184810</v>
+      </c>
+      <c r="C33">
+        <v>-297261195</v>
+      </c>
+      <c r="D33">
         <v>-190194473</v>
       </c>
-      <c r="C33">
-        <v>968406385</v>
-      </c>
-      <c r="D33">
-        <v>-118899411</v>
-      </c>
       <c r="E33">
-        <v>51932735</v>
+        <v>1123825950</v>
       </c>
       <c r="F33">
+        <v>-198855462</v>
+      </c>
+      <c r="G33">
+        <v>-23530779</v>
+      </c>
+      <c r="H33">
         <v>-35419295</v>
       </c>
-      <c r="G33">
+      <c r="I33">
         <v>343794718</v>
       </c>
-      <c r="H33">
+      <c r="J33">
         <v>161265964</v>
       </c>
-      <c r="I33">
+      <c r="K33">
         <v>612611198</v>
       </c>
-      <c r="J33">
+      <c r="L33">
         <v>1123714415</v>
       </c>
     </row>
@@ -3551,36 +4019,54 @@
       <c r="A35" t="str">
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
+      <c r="B35">
+        <v>20934407</v>
+      </c>
+      <c r="C35">
+        <v>24315263</v>
+      </c>
+      <c r="F35">
+        <v>79956051</v>
+      </c>
+      <c r="G35">
+        <v>75463514</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
+        <v>-337924842</v>
+      </c>
+      <c r="C36">
+        <v>-472918475</v>
+      </c>
+      <c r="D36">
         <v>-342423422</v>
       </c>
-      <c r="C36">
+      <c r="E36">
         <v>-505858409</v>
       </c>
-      <c r="D36">
+      <c r="F36">
         <v>-303205806</v>
       </c>
-      <c r="E36">
+      <c r="G36">
         <v>-329358629</v>
       </c>
-      <c r="F36">
+      <c r="H36">
         <v>-402124495</v>
       </c>
-      <c r="G36">
+      <c r="I36">
         <v>-313179534</v>
       </c>
-      <c r="H36">
+      <c r="J36">
         <v>-561274076</v>
       </c>
-      <c r="I36">
+      <c r="K36">
         <v>-133451278</v>
       </c>
-      <c r="J36">
+      <c r="L36">
         <v>-165367367</v>
       </c>
     </row>
@@ -3594,30 +4080,36 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
+        <v>-1911175245</v>
+      </c>
+      <c r="C38">
+        <v>-745864407</v>
+      </c>
+      <c r="D38">
         <v>-169363901</v>
       </c>
-      <c r="C38">
+      <c r="E38">
         <v>462547976</v>
       </c>
-      <c r="D38">
+      <c r="F38">
         <v>-422105217</v>
       </c>
-      <c r="E38">
+      <c r="G38">
         <v>-277425894</v>
       </c>
-      <c r="F38">
+      <c r="H38">
         <v>-422381576</v>
       </c>
-      <c r="G38">
+      <c r="I38">
         <v>30615184</v>
       </c>
-      <c r="H38">
+      <c r="J38">
         <v>-400008112</v>
       </c>
-      <c r="I38">
+      <c r="K38">
         <v>479159920</v>
       </c>
-      <c r="J38">
+      <c r="L38">
         <v>958347048</v>
       </c>
     </row>
@@ -3627,30 +4119,36 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
       <c r="B40">
+        <v>3035929040</v>
+      </c>
+      <c r="C40">
+        <v>-277655882</v>
+      </c>
+      <c r="D40">
         <v>-941955496</v>
       </c>
-      <c r="C40">
+      <c r="E40">
         <v>1225256029</v>
       </c>
-      <c r="D40">
+      <c r="F40">
         <v>-248980237</v>
       </c>
-      <c r="E40">
+      <c r="G40">
         <v>-319363680</v>
       </c>
-      <c r="F40">
+      <c r="H40">
         <v>-96641758</v>
       </c>
-      <c r="G40">
+      <c r="I40">
         <v>-624608688</v>
       </c>
-      <c r="H40">
+      <c r="J40">
         <v>417424773</v>
       </c>
-      <c r="I40">
+      <c r="K40">
         <v>264285801</v>
       </c>
-      <c r="J40">
+      <c r="L40">
         <v>1697990926</v>
       </c>
     </row>
@@ -3658,16 +4156,7 @@
       <c r="A41" t="str">
         <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
       </c>
-      <c r="C41">
-        <v>0</v>
-      </c>
-      <c r="D41">
-        <v>0</v>
-      </c>
-      <c r="E41">
-        <v>0</v>
-      </c>
-      <c r="J41">
+      <c r="L41">
         <v>12139029</v>
       </c>
     </row>
@@ -3676,30 +4165,36 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
       <c r="B42">
+        <v>3035929040</v>
+      </c>
+      <c r="C42">
+        <v>-277655882</v>
+      </c>
+      <c r="D42">
         <v>-941955496</v>
       </c>
-      <c r="C42">
+      <c r="E42">
         <v>1225256029</v>
       </c>
-      <c r="D42">
+      <c r="F42">
         <v>-248980237</v>
       </c>
-      <c r="E42">
+      <c r="G42">
         <v>-319363680</v>
       </c>
-      <c r="F42">
+      <c r="H42">
         <v>-96641758</v>
       </c>
-      <c r="G42">
+      <c r="I42">
         <v>-624608688</v>
       </c>
-      <c r="H42">
+      <c r="J42">
         <v>417424773</v>
       </c>
-      <c r="I42">
+      <c r="K42">
         <v>264285801</v>
       </c>
-      <c r="J42">
+      <c r="L42">
         <v>1685851897</v>
       </c>
     </row>
@@ -3708,30 +4203,36 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
+        <v>1124753795</v>
+      </c>
+      <c r="C43">
+        <v>-1023520289</v>
+      </c>
+      <c r="D43">
         <v>-1111319397</v>
       </c>
-      <c r="C43">
+      <c r="E43">
         <v>1687804005</v>
       </c>
-      <c r="D43">
+      <c r="F43">
         <v>-671085454</v>
       </c>
-      <c r="E43">
+      <c r="G43">
         <v>-596789574</v>
       </c>
-      <c r="F43">
+      <c r="H43">
         <v>-519023334</v>
       </c>
-      <c r="G43">
+      <c r="I43">
         <v>-593993504</v>
       </c>
-      <c r="H43">
+      <c r="J43">
         <v>17416661</v>
       </c>
-      <c r="I43">
+      <c r="K43">
         <v>743445721</v>
       </c>
-      <c r="J43">
+      <c r="L43">
         <v>2656337974</v>
       </c>
     </row>
@@ -3746,30 +4247,36 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
+        <v>1124753795</v>
+      </c>
+      <c r="C46">
+        <v>-1023520289</v>
+      </c>
+      <c r="D46">
         <v>-1111319397</v>
       </c>
-      <c r="C46">
+      <c r="E46">
         <v>1687804005</v>
       </c>
-      <c r="D46">
+      <c r="F46">
         <v>-671085454</v>
       </c>
-      <c r="E46">
+      <c r="G46">
         <v>-596789574</v>
       </c>
-      <c r="F46">
+      <c r="H46">
         <v>-519023334</v>
       </c>
-      <c r="G46">
+      <c r="I46">
         <v>-593993504</v>
       </c>
-      <c r="H46">
+      <c r="J46">
         <v>17416661</v>
       </c>
-      <c r="I46">
+      <c r="K46">
         <v>743445721</v>
       </c>
-      <c r="J46">
+      <c r="L46">
         <v>2656337974</v>
       </c>
     </row>
@@ -3801,36 +4308,48 @@
       <c r="I47">
         <v>0</v>
       </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
+        <v>1124753795</v>
+      </c>
+      <c r="C48">
+        <v>-1023520289</v>
+      </c>
+      <c r="D48">
         <v>-1111319397</v>
       </c>
-      <c r="C48">
+      <c r="E48">
         <v>1687804005</v>
       </c>
-      <c r="D48">
+      <c r="F48">
         <v>-671085454</v>
       </c>
-      <c r="E48">
+      <c r="G48">
         <v>-596789574</v>
       </c>
-      <c r="F48">
+      <c r="H48">
         <v>-519023334</v>
       </c>
-      <c r="G48">
+      <c r="I48">
         <v>-593993504</v>
       </c>
-      <c r="H48">
+      <c r="J48">
         <v>17416661</v>
       </c>
-      <c r="I48">
+      <c r="K48">
         <v>743445721</v>
       </c>
-      <c r="J48">
+      <c r="L48">
         <v>2656337974</v>
       </c>
     </row>
@@ -3840,43 +4359,49 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
+        <v>302185524</v>
+      </c>
+      <c r="C50">
+        <v>179108248</v>
+      </c>
+      <c r="D50">
         <v>381635917</v>
       </c>
-      <c r="C50">
+      <c r="E50">
         <v>189326312</v>
       </c>
-      <c r="D50">
+      <c r="F50">
         <v>174129340</v>
       </c>
-      <c r="E50">
+      <c r="G50">
         <v>153064451</v>
       </c>
-      <c r="F50">
+      <c r="H50">
         <v>-19429524</v>
       </c>
-      <c r="G50">
+      <c r="I50">
         <v>127621010</v>
       </c>
-      <c r="H50">
+      <c r="J50">
         <v>207277550</v>
       </c>
-      <c r="I50">
+      <c r="K50">
         <v>198657431</v>
       </c>
-      <c r="J50">
+      <c r="L50">
         <v>238715142</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:O50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -3891,6 +4416,8 @@
     <col min="11" max="11" customWidth="1" width="20"/>
     <col min="12" max="12" customWidth="1" width="20"/>
     <col min="13" max="13" customWidth="1" width="20"/>
+    <col min="14" max="14" customWidth="1" width="20"/>
+    <col min="15" max="15" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3898,39 +4425,45 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="C1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="D1" t="str">
+      <c r="F1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="E1" t="str">
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2024/3</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>2023/9</v>
       </c>
-      <c r="L1" t="str">
+      <c r="N1" t="str">
         <v>2022/12</v>
       </c>
-      <c r="M1" t="str">
+      <c r="O1" t="str">
         <v>2021/12</v>
       </c>
     </row>
@@ -3944,30 +4477,36 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
+        <v>7139392214</v>
+      </c>
+      <c r="C3">
+        <v>7379394770</v>
+      </c>
+      <c r="D3">
         <v>8121300519</v>
       </c>
-      <c r="C3">
+      <c r="E3">
         <v>7257990064</v>
       </c>
-      <c r="D3">
+      <c r="F3">
         <v>7314046633</v>
       </c>
-      <c r="E3">
+      <c r="G3">
         <v>5496368666</v>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>5839099243</v>
       </c>
-      <c r="G3">
+      <c r="I3">
         <v>9802080671</v>
       </c>
-      <c r="J3">
+      <c r="L3">
         <v>10560889333</v>
       </c>
-      <c r="L3">
+      <c r="N3">
         <v>5445699997</v>
       </c>
-      <c r="M3">
+      <c r="O3">
         <v>1713903324</v>
       </c>
     </row>
@@ -3991,30 +4530,36 @@
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
       <c r="B7">
+        <v>-5848703183</v>
+      </c>
+      <c r="C7">
+        <v>-6048134826</v>
+      </c>
+      <c r="D7">
         <v>-6363584108</v>
       </c>
-      <c r="C7">
+      <c r="E7">
         <v>-6242964988</v>
       </c>
-      <c r="D7">
+      <c r="F7">
         <v>-6191641961</v>
       </c>
-      <c r="E7">
+      <c r="G7">
         <v>-4737913190</v>
       </c>
-      <c r="F7">
+      <c r="H7">
         <v>-4978372963</v>
       </c>
-      <c r="G7">
+      <c r="I7">
         <v>-7484555132</v>
       </c>
-      <c r="J7">
+      <c r="L7">
         <v>-8780724257</v>
       </c>
-      <c r="L7">
+      <c r="N7">
         <v>-4897385532</v>
       </c>
-      <c r="M7">
+      <c r="O7">
         <v>-1359284431</v>
       </c>
     </row>
@@ -4023,30 +4568,36 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
+        <v>1290689031</v>
+      </c>
+      <c r="C8">
+        <v>1331259944</v>
+      </c>
+      <c r="D8">
         <v>1757716411</v>
       </c>
-      <c r="C8">
+      <c r="E8">
         <v>1015025076</v>
       </c>
-      <c r="D8">
+      <c r="F8">
         <v>1122404672</v>
       </c>
-      <c r="E8">
+      <c r="G8">
         <v>758455476</v>
       </c>
-      <c r="F8">
+      <c r="H8">
         <v>860726280</v>
       </c>
-      <c r="G8">
+      <c r="I8">
         <v>2317525539</v>
       </c>
-      <c r="J8">
+      <c r="L8">
         <v>1780165076</v>
       </c>
-      <c r="L8">
+      <c r="N8">
         <v>548314465</v>
       </c>
-      <c r="M8">
+      <c r="O8">
         <v>354618893</v>
       </c>
     </row>
@@ -4075,30 +4626,36 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
+        <v>1290689031</v>
+      </c>
+      <c r="C13">
+        <v>1331259944</v>
+      </c>
+      <c r="D13">
         <v>1757716411</v>
       </c>
-      <c r="C13">
+      <c r="E13">
         <v>1015025076</v>
       </c>
-      <c r="D13">
+      <c r="F13">
         <v>1122404672</v>
       </c>
-      <c r="E13">
+      <c r="G13">
         <v>758455476</v>
       </c>
-      <c r="F13">
+      <c r="H13">
         <v>860726280</v>
       </c>
-      <c r="G13">
+      <c r="I13">
         <v>2317525539</v>
       </c>
-      <c r="J13">
+      <c r="L13">
         <v>1780165076</v>
       </c>
-      <c r="L13">
+      <c r="N13">
         <v>548314465</v>
       </c>
-      <c r="M13">
+      <c r="O13">
         <v>354618893</v>
       </c>
     </row>
@@ -4108,30 +4665,36 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
+        <v>-331080609</v>
+      </c>
+      <c r="C15">
+        <v>-298408130</v>
+      </c>
+      <c r="D15">
         <v>-289281106</v>
       </c>
-      <c r="C15">
+      <c r="E15">
         <v>-348954495</v>
       </c>
-      <c r="D15">
+      <c r="F15">
         <v>-369891086</v>
       </c>
-      <c r="E15">
+      <c r="G15">
         <v>-406927290</v>
       </c>
-      <c r="F15">
+      <c r="H15">
         <v>-403063680</v>
       </c>
-      <c r="G15">
+      <c r="I15">
         <v>-338138144</v>
       </c>
-      <c r="J15">
+      <c r="L15">
         <v>-184813277</v>
       </c>
-      <c r="L15">
+      <c r="N15">
         <v>-88998712</v>
       </c>
-      <c r="M15">
+      <c r="O15">
         <v>-38508405</v>
       </c>
     </row>
@@ -4140,30 +4703,36 @@
         <v xml:space="preserve">    Pazarlama, Satış ve Dağıtım Giderleri (-)</v>
       </c>
       <c r="B16">
+        <v>-3338476</v>
+      </c>
+      <c r="C16">
+        <v>94202</v>
+      </c>
+      <c r="D16">
         <v>-28098936</v>
       </c>
-      <c r="C16">
+      <c r="E16">
         <v>-79709267</v>
       </c>
-      <c r="D16">
+      <c r="F16">
         <v>-99403312</v>
       </c>
-      <c r="E16">
+      <c r="G16">
         <v>-106156384</v>
       </c>
-      <c r="F16">
+      <c r="H16">
         <v>-80559969</v>
       </c>
-      <c r="G16">
+      <c r="I16">
         <v>-65872425</v>
       </c>
-      <c r="J16">
+      <c r="L16">
         <v>-79372583</v>
       </c>
-      <c r="L16">
+      <c r="N16">
         <v>-55191032</v>
       </c>
-      <c r="M16">
+      <c r="O16">
         <v>-2929335</v>
       </c>
     </row>
@@ -4172,30 +4741,36 @@
         <v xml:space="preserve">    Araştırma ve Geliştirme Giderleri (-)</v>
       </c>
       <c r="B17">
+        <v>-163151705</v>
+      </c>
+      <c r="C17">
+        <v>-177411949</v>
+      </c>
+      <c r="D17">
         <v>-173143073</v>
       </c>
-      <c r="C17">
+      <c r="E17">
         <v>-155366611</v>
       </c>
-      <c r="D17">
+      <c r="F17">
         <v>-124307802</v>
       </c>
-      <c r="E17">
+      <c r="G17">
         <v>-145489319</v>
       </c>
-      <c r="F17">
+      <c r="H17">
         <v>-128386426</v>
       </c>
-      <c r="G17">
+      <c r="I17">
         <v>-117046292</v>
       </c>
-      <c r="J17">
+      <c r="L17">
         <v>-66714947</v>
       </c>
-      <c r="L17">
+      <c r="N17">
         <v>-35451633</v>
       </c>
-      <c r="M17">
+      <c r="O17">
         <v>-2096128</v>
       </c>
     </row>
@@ -4204,30 +4779,36 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
+        <v>247024946</v>
+      </c>
+      <c r="C18">
+        <v>97952414</v>
+      </c>
+      <c r="D18">
         <v>121247358</v>
       </c>
-      <c r="C18">
+      <c r="E18">
         <v>741595235</v>
       </c>
-      <c r="D18">
-        <v>584427840</v>
-      </c>
-      <c r="E18">
-        <v>814220093</v>
-      </c>
       <c r="F18">
+        <v>429008275</v>
+      </c>
+      <c r="G18">
+        <v>738756579</v>
+      </c>
+      <c r="H18">
         <v>874522023</v>
       </c>
-      <c r="G18">
+      <c r="I18">
         <v>552611642</v>
       </c>
-      <c r="J18">
+      <c r="L18">
         <v>217574273</v>
       </c>
-      <c r="L18">
+      <c r="N18">
         <v>366768178</v>
       </c>
-      <c r="M18">
+      <c r="O18">
         <v>173916069</v>
       </c>
     </row>
@@ -4236,30 +4817,36 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
+        <v>-2007339860</v>
+      </c>
+      <c r="C19">
+        <v>-523765310</v>
+      </c>
+      <c r="D19">
         <v>-684985922</v>
       </c>
-      <c r="C19">
+      <c r="E19">
         <v>-306569542</v>
       </c>
-      <c r="D19">
+      <c r="F19">
         <v>-866512708</v>
       </c>
-      <c r="E19">
+      <c r="G19">
         <v>-387219597</v>
       </c>
-      <c r="F19">
+      <c r="H19">
         <v>-35676786</v>
       </c>
-      <c r="G19">
+      <c r="I19">
         <v>-102385150</v>
       </c>
-      <c r="J19">
+      <c r="L19">
         <v>-74806561</v>
       </c>
-      <c r="L19">
+      <c r="N19">
         <v>-13797687</v>
       </c>
-      <c r="M19">
+      <c r="O19">
         <v>-13028332</v>
       </c>
     </row>
@@ -4273,30 +4860,36 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
+        <v>-967196673</v>
+      </c>
+      <c r="C21">
+        <v>429721171</v>
+      </c>
+      <c r="D21">
         <v>703454732</v>
       </c>
-      <c r="C21">
+      <c r="E21">
         <v>866020396</v>
       </c>
-      <c r="D21">
-        <v>246717604</v>
-      </c>
-      <c r="E21">
-        <v>526882979</v>
-      </c>
       <c r="F21">
+        <v>91298039</v>
+      </c>
+      <c r="G21">
+        <v>451419465</v>
+      </c>
+      <c r="H21">
         <v>1087561442</v>
       </c>
-      <c r="G21">
+      <c r="I21">
         <v>2246695170</v>
       </c>
-      <c r="J21">
+      <c r="L21">
         <v>1592031981</v>
       </c>
-      <c r="L21">
+      <c r="N21">
         <v>721643579</v>
       </c>
-      <c r="M21">
+      <c r="O21">
         <v>471972762</v>
       </c>
     </row>
@@ -4315,10 +4908,10 @@
       <c r="A25" t="str">
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
-      <c r="B25">
+      <c r="D25">
         <v>7790504</v>
       </c>
-      <c r="F25">
+      <c r="H25">
         <v>0</v>
       </c>
     </row>
@@ -4326,16 +4919,16 @@
       <c r="A26" t="str">
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Giderler (-)</v>
       </c>
-      <c r="B26">
+      <c r="D26">
         <v>0</v>
       </c>
-      <c r="C26">
+      <c r="E26">
         <v>18</v>
       </c>
-      <c r="F26">
+      <c r="H26">
         <v>-5308857</v>
       </c>
-      <c r="J26">
+      <c r="L26">
         <v>0</v>
       </c>
     </row>
@@ -4374,30 +4967,36 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
+        <v>-957814528</v>
+      </c>
+      <c r="C33">
+        <v>437514820</v>
+      </c>
+      <c r="D33">
         <v>711245236</v>
       </c>
-      <c r="C33">
+      <c r="E33">
         <v>866020414</v>
       </c>
-      <c r="D33">
-        <v>241408747</v>
-      </c>
-      <c r="E33">
-        <v>521574122</v>
-      </c>
       <c r="F33">
+        <v>85989182</v>
+      </c>
+      <c r="G33">
+        <v>446110608</v>
+      </c>
+      <c r="H33">
         <v>1082252585</v>
       </c>
-      <c r="G33">
+      <c r="I33">
         <v>2241386295</v>
       </c>
-      <c r="J33">
+      <c r="L33">
         <v>1592031981</v>
       </c>
-      <c r="L33">
+      <c r="N33">
         <v>721643579</v>
       </c>
-      <c r="M33">
+      <c r="O33">
         <v>471972762</v>
       </c>
     </row>
@@ -4407,9 +5006,15 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
       <c r="B35">
+        <v>253084099</v>
+      </c>
+      <c r="C35">
+        <v>312105743</v>
+      </c>
+      <c r="D35">
         <v>363253994</v>
       </c>
-      <c r="F35">
+      <c r="H35">
         <v>15162214</v>
       </c>
     </row>
@@ -4418,30 +5023,36 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
+        <v>-1659125148</v>
+      </c>
+      <c r="C36">
+        <v>-1624406112</v>
+      </c>
+      <c r="D36">
         <v>-1480846266</v>
       </c>
-      <c r="C36">
+      <c r="E36">
         <v>-1540547339</v>
       </c>
-      <c r="D36">
+      <c r="F36">
         <v>-1347868464</v>
       </c>
-      <c r="E36">
+      <c r="G36">
         <v>-1605936734</v>
       </c>
-      <c r="F36">
+      <c r="H36">
         <v>-1410029383</v>
       </c>
-      <c r="G36">
+      <c r="I36">
         <v>-1173272255</v>
       </c>
-      <c r="J36">
+      <c r="L36">
         <v>-388417772</v>
       </c>
-      <c r="L36">
+      <c r="N36">
         <v>-442083381</v>
       </c>
-      <c r="M36">
+      <c r="O36">
         <v>-157548349</v>
       </c>
     </row>
@@ -4455,30 +5066,36 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
+        <v>-2363855577</v>
+      </c>
+      <c r="C38">
+        <v>-874785549</v>
+      </c>
+      <c r="D38">
         <v>-406347036</v>
       </c>
-      <c r="C38">
+      <c r="E38">
         <v>-659364711</v>
       </c>
-      <c r="D38">
+      <c r="F38">
         <v>-1091297503</v>
       </c>
-      <c r="E38">
+      <c r="G38">
         <v>-1069200398</v>
       </c>
-      <c r="F38">
+      <c r="H38">
         <v>-312614584</v>
       </c>
-      <c r="G38">
+      <c r="I38">
         <v>1068114040</v>
       </c>
-      <c r="J38">
+      <c r="L38">
         <v>1203614209</v>
       </c>
-      <c r="L38">
+      <c r="N38">
         <v>279560198</v>
       </c>
-      <c r="M38">
+      <c r="O38">
         <v>314424413</v>
       </c>
     </row>
@@ -4488,30 +5105,36 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
       <c r="B40">
+        <v>3041573691</v>
+      </c>
+      <c r="C40">
+        <v>-243335586</v>
+      </c>
+      <c r="D40">
         <v>-285043384</v>
       </c>
-      <c r="C40">
+      <c r="E40">
         <v>560270354</v>
       </c>
-      <c r="D40">
+      <c r="F40">
         <v>-1289594363</v>
       </c>
-      <c r="E40">
+      <c r="G40">
         <v>-623189353</v>
       </c>
-      <c r="F40">
+      <c r="H40">
         <v>-39539872</v>
       </c>
-      <c r="G40">
+      <c r="I40">
         <v>1755092812</v>
       </c>
-      <c r="J40">
+      <c r="L40">
         <v>1529187508</v>
       </c>
-      <c r="L40">
+      <c r="N40">
         <v>-22638186</v>
       </c>
-      <c r="M40">
+      <c r="O40">
         <v>323850347</v>
       </c>
     </row>
@@ -4519,7 +5142,7 @@
       <c r="A41" t="str">
         <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
       </c>
-      <c r="J41">
+      <c r="L41">
         <v>-50517427</v>
       </c>
     </row>
@@ -4528,30 +5151,36 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
       <c r="B42">
+        <v>3041573691</v>
+      </c>
+      <c r="C42">
+        <v>-243335586</v>
+      </c>
+      <c r="D42">
         <v>-285043384</v>
       </c>
-      <c r="C42">
+      <c r="E42">
         <v>560270354</v>
       </c>
-      <c r="D42">
+      <c r="F42">
         <v>-1289594363</v>
       </c>
-      <c r="E42">
+      <c r="G42">
         <v>-623189353</v>
       </c>
-      <c r="F42">
+      <c r="H42">
         <v>-39539872</v>
       </c>
-      <c r="G42">
+      <c r="I42">
         <v>1742953783</v>
       </c>
-      <c r="J42">
+      <c r="L42">
         <v>1579704935</v>
       </c>
-      <c r="L42">
+      <c r="N42">
         <v>-22638186</v>
       </c>
-      <c r="M42">
+      <c r="O42">
         <v>323850347</v>
       </c>
     </row>
@@ -4560,30 +5189,36 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
+        <v>677718114</v>
+      </c>
+      <c r="C43">
+        <v>-1118121135</v>
+      </c>
+      <c r="D43">
         <v>-691390420</v>
       </c>
-      <c r="C43">
+      <c r="E43">
         <v>-99094357</v>
       </c>
-      <c r="D43">
+      <c r="F43">
         <v>-2380891866</v>
       </c>
-      <c r="E43">
+      <c r="G43">
         <v>-1692389751</v>
       </c>
-      <c r="F43">
+      <c r="H43">
         <v>-352154456</v>
       </c>
-      <c r="G43">
+      <c r="I43">
         <v>2823206852</v>
       </c>
-      <c r="J43">
+      <c r="L43">
         <v>2732801717</v>
       </c>
-      <c r="L43">
+      <c r="N43">
         <v>256922012</v>
       </c>
-      <c r="M43">
+      <c r="O43">
         <v>638274760</v>
       </c>
     </row>
@@ -4591,7 +5226,7 @@
       <c r="A44" t="str">
         <v xml:space="preserve">    Durdurulan Faaliyetler Dönem Karı/Zararı</v>
       </c>
-      <c r="J44">
+      <c r="L44">
         <v>0</v>
       </c>
     </row>
@@ -4601,30 +5236,36 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
+        <v>677718114</v>
+      </c>
+      <c r="C46">
+        <v>-1118121135</v>
+      </c>
+      <c r="D46">
         <v>-691390420</v>
       </c>
-      <c r="C46">
+      <c r="E46">
         <v>-99094357</v>
       </c>
-      <c r="D46">
+      <c r="F46">
         <v>-2380891866</v>
       </c>
-      <c r="E46">
+      <c r="G46">
         <v>-1692389751</v>
       </c>
-      <c r="F46">
+      <c r="H46">
         <v>-352154456</v>
       </c>
-      <c r="G46">
+      <c r="I46">
         <v>2823206852</v>
       </c>
-      <c r="J46">
+      <c r="L46">
         <v>2732801717</v>
       </c>
-      <c r="L46">
+      <c r="N46">
         <v>256922012</v>
       </c>
-      <c r="M46">
+      <c r="O46">
         <v>638274760</v>
       </c>
     </row>
@@ -4647,7 +5288,13 @@
       <c r="F47">
         <v>0</v>
       </c>
-      <c r="J47">
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="L47">
         <v>0</v>
       </c>
     </row>
@@ -4656,30 +5303,36 @@
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
+        <v>677718114</v>
+      </c>
+      <c r="C48">
+        <v>-1118121135</v>
+      </c>
+      <c r="D48">
         <v>-691390420</v>
       </c>
-      <c r="C48">
+      <c r="E48">
         <v>-99094357</v>
       </c>
-      <c r="D48">
+      <c r="F48">
         <v>-2380891866</v>
       </c>
-      <c r="E48">
+      <c r="G48">
         <v>-1692389751</v>
       </c>
-      <c r="F48">
+      <c r="H48">
         <v>-352154456</v>
       </c>
-      <c r="G48">
+      <c r="I48">
         <v>2823206852</v>
       </c>
-      <c r="J48">
+      <c r="L48">
         <v>2732801717</v>
       </c>
-      <c r="L48">
+      <c r="N48">
         <v>256922012</v>
       </c>
-      <c r="M48">
+      <c r="O48">
         <v>638274760</v>
       </c>
     </row>
@@ -4689,43 +5342,49 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
+        <v>1052256001</v>
+      </c>
+      <c r="C50">
+        <v>924199817</v>
+      </c>
+      <c r="D50">
         <v>898156020</v>
       </c>
-      <c r="C50">
+      <c r="E50">
         <v>497090579</v>
       </c>
-      <c r="D50">
+      <c r="F50">
         <v>435385277</v>
       </c>
-      <c r="E50">
+      <c r="G50">
         <v>468533487</v>
       </c>
-      <c r="F50">
+      <c r="H50">
         <v>514126467</v>
       </c>
-      <c r="G50">
+      <c r="I50">
         <v>772271133</v>
       </c>
-      <c r="J50">
+      <c r="L50">
         <v>517711407</v>
       </c>
-      <c r="L50">
+      <c r="N50">
         <v>328056956</v>
       </c>
-      <c r="M50">
+      <c r="O50">
         <v>107953692</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M129"/>
+  <dimension ref="A1:O129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -4740,6 +5399,8 @@
     <col min="11" max="11" customWidth="1" width="20"/>
     <col min="12" max="12" customWidth="1" width="20"/>
     <col min="13" max="13" customWidth="1" width="20"/>
+    <col min="14" max="14" customWidth="1" width="20"/>
+    <col min="15" max="15" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4747,39 +5408,45 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="C1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="D1" t="str">
+      <c r="F1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="E1" t="str">
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2024/3</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>2023/9</v>
       </c>
-      <c r="L1" t="str">
+      <c r="N1" t="str">
         <v>2022/12</v>
       </c>
-      <c r="M1" t="str">
+      <c r="O1" t="str">
         <v>2021/12</v>
       </c>
     </row>
@@ -4793,40 +5460,46 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
+        <v>886843374</v>
+      </c>
+      <c r="C3">
+        <v>-315968239</v>
+      </c>
+      <c r="D3">
         <v>2290405959</v>
       </c>
-      <c r="C3">
+      <c r="E3">
         <v>-1556187215</v>
       </c>
-      <c r="D3">
+      <c r="F3">
         <v>-1181696846</v>
       </c>
-      <c r="E3">
+      <c r="G3">
         <v>1093232974</v>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>144316070</v>
       </c>
-      <c r="G3">
+      <c r="I3">
         <v>-986947759</v>
       </c>
-      <c r="H3">
+      <c r="J3">
         <v>-666552135</v>
       </c>
-      <c r="I3">
+      <c r="K3">
         <v>815288653</v>
       </c>
-      <c r="J3">
+      <c r="L3">
         <v>2623252238</v>
       </c>
-      <c r="K3">
+      <c r="M3">
         <v>979161613</v>
       </c>
-      <c r="L3">
+      <c r="N3">
         <v>418423509</v>
       </c>
-      <c r="M3">
-        <v>2321186332</v>
+      <c r="O3">
+        <v>-12814</v>
       </c>
     </row>
     <row r="4">
@@ -4834,39 +5507,45 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
+        <v>101233506</v>
+      </c>
+      <c r="C4">
+        <v>-1023520289</v>
+      </c>
+      <c r="D4">
         <v>-691390420</v>
       </c>
-      <c r="C4">
+      <c r="E4">
         <v>419928977</v>
       </c>
-      <c r="D4">
+      <c r="F4">
         <v>-1267875028</v>
       </c>
-      <c r="E4">
+      <c r="G4">
         <v>-596789574</v>
       </c>
-      <c r="F4">
+      <c r="H4">
         <v>-352154456</v>
       </c>
-      <c r="G4">
+      <c r="I4">
         <v>166868878</v>
       </c>
-      <c r="H4">
+      <c r="J4">
         <v>760862382</v>
       </c>
-      <c r="I4">
+      <c r="K4">
         <v>743445721</v>
       </c>
-      <c r="J4">
+      <c r="L4">
         <v>2732801717</v>
       </c>
-      <c r="K4">
+      <c r="M4">
         <v>76463743</v>
       </c>
-      <c r="L4">
+      <c r="N4">
         <v>256922012</v>
       </c>
-      <c r="M4">
+      <c r="O4">
         <v>638274760</v>
       </c>
     </row>
@@ -4875,30 +5554,36 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
+        <v>-231130630</v>
+      </c>
+      <c r="C5">
+        <v>1677284973</v>
+      </c>
+      <c r="D5">
         <v>2178914162</v>
       </c>
-      <c r="C5">
+      <c r="E5">
         <v>-510628869</v>
       </c>
-      <c r="D5">
+      <c r="F5">
         <v>1931751221</v>
       </c>
-      <c r="E5">
+      <c r="G5">
         <v>2690383636</v>
       </c>
-      <c r="F5">
+      <c r="H5">
         <v>1711372135</v>
       </c>
-      <c r="G5">
+      <c r="I5">
         <v>1958423233</v>
       </c>
-      <c r="H5">
+      <c r="J5">
         <v>197271896</v>
       </c>
-      <c r="I5">
+      <c r="K5">
         <v>1355394754</v>
       </c>
-      <c r="J5">
+      <c r="L5">
         <v>204229425</v>
       </c>
     </row>
@@ -4907,39 +5592,45 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
+        <v>481293772</v>
+      </c>
+      <c r="C6">
+        <v>179108248</v>
+      </c>
+      <c r="D6">
         <v>898156020</v>
       </c>
-      <c r="C6">
+      <c r="E6">
         <v>516520103</v>
       </c>
-      <c r="D6">
+      <c r="F6">
         <v>327193791</v>
       </c>
-      <c r="E6">
+      <c r="G6">
         <v>153064451</v>
       </c>
-      <c r="F6">
+      <c r="H6">
         <v>514126467</v>
       </c>
-      <c r="G6">
+      <c r="I6">
         <v>533555991</v>
       </c>
-      <c r="H6">
+      <c r="J6">
         <v>405934981</v>
       </c>
-      <c r="I6">
+      <c r="K6">
         <v>198657431</v>
       </c>
-      <c r="J6">
+      <c r="L6">
         <v>517711407</v>
       </c>
-      <c r="K6">
+      <c r="M6">
         <v>278996265</v>
       </c>
-      <c r="L6">
+      <c r="N6">
         <v>328056956</v>
       </c>
-      <c r="M6">
+      <c r="O6">
         <v>107953692</v>
       </c>
     </row>
@@ -4953,39 +5644,45 @@
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
+        <v>614042610</v>
+      </c>
+      <c r="C8">
+        <v>5959578</v>
+      </c>
+      <c r="D8">
         <v>24910968</v>
       </c>
-      <c r="C8">
+      <c r="E8">
         <v>27599679</v>
       </c>
-      <c r="D8">
+      <c r="F8">
         <v>28430573</v>
       </c>
-      <c r="E8">
+      <c r="G8">
         <v>20560094</v>
       </c>
-      <c r="F8">
+      <c r="H8">
         <v>14475332</v>
       </c>
-      <c r="G8">
+      <c r="I8">
         <v>10394690</v>
       </c>
-      <c r="H8">
+      <c r="J8">
         <v>12961648</v>
       </c>
-      <c r="I8">
+      <c r="K8">
         <v>32241170</v>
       </c>
-      <c r="J8">
+      <c r="L8">
         <v>510069</v>
       </c>
-      <c r="K8">
+      <c r="M8">
         <v>18002033</v>
       </c>
-      <c r="L8">
+      <c r="N8">
         <v>12475321</v>
       </c>
-      <c r="M8">
+      <c r="O8">
         <v>2755552</v>
       </c>
     </row>
@@ -5009,39 +5706,45 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
+        <v>686219813</v>
+      </c>
+      <c r="C12">
+        <v>413525053</v>
+      </c>
+      <c r="D12">
         <v>948883371</v>
       </c>
-      <c r="C12">
+      <c r="E12">
         <v>710262543</v>
       </c>
-      <c r="D12">
+      <c r="F12">
         <v>373059499</v>
       </c>
-      <c r="E12">
+      <c r="G12">
         <v>219470350</v>
       </c>
-      <c r="F12">
+      <c r="H12">
         <v>1305853682</v>
       </c>
-      <c r="G12">
+      <c r="I12">
         <v>953536370</v>
       </c>
-      <c r="H12">
+      <c r="J12">
         <v>654998279</v>
       </c>
-      <c r="I12">
+      <c r="K12">
         <v>119295259</v>
       </c>
-      <c r="J12">
+      <c r="L12">
         <v>323105223</v>
       </c>
-      <c r="K12">
+      <c r="M12">
         <v>28998654</v>
       </c>
-      <c r="L12">
+      <c r="N12">
         <v>76809646</v>
       </c>
-      <c r="M12">
+      <c r="O12">
         <v>150457138</v>
       </c>
     </row>
@@ -5060,39 +5763,45 @@
         <v xml:space="preserve">    Gerçekleşmemiş Yabancı Para Çevrim Farkları İle İlgili Düzeltmeler</v>
       </c>
       <c r="B15">
+        <v>745586333</v>
+      </c>
+      <c r="C15">
+        <v>801036212</v>
+      </c>
+      <c r="D15">
         <v>21920419</v>
       </c>
-      <c r="C15">
+      <c r="E15">
         <v>-1108099082</v>
       </c>
-      <c r="D15">
+      <c r="F15">
         <v>634723441</v>
       </c>
-      <c r="E15">
+      <c r="G15">
         <v>1977925061</v>
       </c>
-      <c r="F15">
+      <c r="H15">
         <v>-162623218</v>
       </c>
-      <c r="G15">
+      <c r="I15">
         <v>518038068</v>
       </c>
-      <c r="H15">
+      <c r="J15">
         <v>-194912438</v>
       </c>
-      <c r="I15">
+      <c r="K15">
         <v>1269486695</v>
       </c>
-      <c r="J15">
+      <c r="L15">
         <v>892090234</v>
       </c>
-      <c r="K15">
+      <c r="M15">
         <v>282204221</v>
       </c>
-      <c r="L15">
+      <c r="N15">
         <v>360148302</v>
       </c>
-      <c r="M15">
+      <c r="O15">
         <v>2114653074</v>
       </c>
     </row>
@@ -5121,39 +5830,45 @@
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B20">
+        <v>-2758273158</v>
+      </c>
+      <c r="C20">
+        <v>277655882</v>
+      </c>
+      <c r="D20">
         <v>285043384</v>
       </c>
-      <c r="C20">
+      <c r="E20">
         <v>-656912112</v>
       </c>
-      <c r="D20">
+      <c r="F20">
         <v>568343917</v>
       </c>
-      <c r="E20">
+      <c r="G20">
         <v>319363680</v>
       </c>
-      <c r="F20">
+      <c r="H20">
         <v>39539872</v>
       </c>
-      <c r="G20">
+      <c r="I20">
         <v>-57101886</v>
       </c>
-      <c r="H20">
+      <c r="J20">
         <v>-681710574</v>
       </c>
-      <c r="I20">
+      <c r="K20">
         <v>-264285801</v>
       </c>
-      <c r="J20">
+      <c r="L20">
         <v>-1529187508</v>
       </c>
-      <c r="K20">
+      <c r="M20">
         <v>168803418</v>
       </c>
-      <c r="L20">
+      <c r="N20">
         <v>22638186</v>
       </c>
-      <c r="M20">
+      <c r="O20">
         <v>-323850347</v>
       </c>
     </row>
@@ -5197,30 +5912,36 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
+        <v>984098602</v>
+      </c>
+      <c r="C28">
+        <v>-990397035</v>
+      </c>
+      <c r="D28">
         <v>811878005</v>
       </c>
-      <c r="C28">
+      <c r="E28">
         <v>-1758887852</v>
       </c>
-      <c r="D28">
+      <c r="F28">
         <v>-1997523895</v>
       </c>
-      <c r="E28">
+      <c r="G28">
         <v>-1074729841</v>
       </c>
-      <c r="F28">
+      <c r="H28">
         <v>-1136458924</v>
       </c>
-      <c r="G28">
+      <c r="I28">
         <v>-3050018903</v>
       </c>
-      <c r="H28">
+      <c r="J28">
         <v>-1608290288</v>
       </c>
-      <c r="I28">
+      <c r="K28">
         <v>-1277337930</v>
       </c>
-      <c r="J28">
+      <c r="L28">
         <v>-257267813</v>
       </c>
     </row>
@@ -5239,39 +5960,45 @@
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B31">
+        <v>522631951</v>
+      </c>
+      <c r="C31">
+        <v>227602084</v>
+      </c>
+      <c r="D31">
         <v>-33279380</v>
       </c>
-      <c r="C31">
+      <c r="E31">
         <v>-364261373</v>
       </c>
-      <c r="D31">
+      <c r="F31">
         <v>-2675350901</v>
       </c>
-      <c r="E31">
+      <c r="G31">
         <v>-551861501</v>
       </c>
-      <c r="F31">
+      <c r="H31">
         <v>-372698912</v>
       </c>
-      <c r="G31">
+      <c r="I31">
         <v>-489313245</v>
       </c>
-      <c r="H31">
+      <c r="J31">
         <v>-563743735</v>
       </c>
-      <c r="I31">
+      <c r="K31">
         <v>-619264837</v>
       </c>
-      <c r="J31">
+      <c r="L31">
         <v>70447537</v>
       </c>
-      <c r="K31">
+      <c r="M31">
         <v>-297340829</v>
       </c>
-      <c r="L31">
+      <c r="N31">
         <v>-617605418</v>
       </c>
-      <c r="M31">
+      <c r="O31">
         <v>-24397814</v>
       </c>
     </row>
@@ -5285,39 +6012,45 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
+        <v>-789284940</v>
+      </c>
+      <c r="C33">
+        <v>-493117823</v>
+      </c>
+      <c r="D33">
         <v>-562351888</v>
       </c>
-      <c r="C33">
+      <c r="E33">
         <v>-245076248</v>
       </c>
-      <c r="D33">
+      <c r="F33">
         <v>302322194</v>
       </c>
-      <c r="E33">
+      <c r="G33">
         <v>23393293</v>
       </c>
-      <c r="F33">
+      <c r="H33">
         <v>-116582892</v>
       </c>
-      <c r="G33">
+      <c r="I33">
         <v>-239410666</v>
       </c>
-      <c r="H33">
+      <c r="J33">
         <v>-137760414</v>
       </c>
-      <c r="I33">
+      <c r="K33">
         <v>-78658655</v>
       </c>
-      <c r="J33">
+      <c r="L33">
         <v>-76896512</v>
       </c>
-      <c r="K33">
+      <c r="M33">
         <v>-173419806</v>
       </c>
-      <c r="L33">
+      <c r="N33">
         <v>-140470867</v>
       </c>
-      <c r="M33">
+      <c r="O33">
         <v>-55760823</v>
       </c>
     </row>
@@ -5341,39 +6074,45 @@
         <v xml:space="preserve">    Stoklardaki Azalışlar (Artışlar) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B37">
+        <v>-971208641</v>
+      </c>
+      <c r="C37">
+        <v>-919447151</v>
+      </c>
+      <c r="D37">
         <v>294636618</v>
       </c>
-      <c r="C37">
+      <c r="E37">
         <v>107502567</v>
       </c>
-      <c r="D37">
+      <c r="F37">
         <v>1036484962</v>
       </c>
-      <c r="E37">
+      <c r="G37">
         <v>379717100</v>
       </c>
-      <c r="F37">
+      <c r="H37">
         <v>-1485435559</v>
       </c>
-      <c r="G37">
+      <c r="I37">
         <v>-2215852510</v>
       </c>
-      <c r="H37">
+      <c r="J37">
         <v>-1966797011</v>
       </c>
-      <c r="I37">
+      <c r="K37">
         <v>-824306629</v>
       </c>
-      <c r="J37">
+      <c r="L37">
         <v>-673256660</v>
       </c>
-      <c r="K37">
+      <c r="M37">
         <v>-2023479383</v>
       </c>
-      <c r="L37">
+      <c r="N37">
         <v>-1495286351</v>
       </c>
-      <c r="M37">
+      <c r="O37">
         <v>-197870741</v>
       </c>
     </row>
@@ -5387,39 +6126,45 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
+        <v>1546028484</v>
+      </c>
+      <c r="C39">
+        <v>885886994</v>
+      </c>
+      <c r="D39">
         <v>-735063828</v>
       </c>
-      <c r="C39">
+      <c r="E39">
         <v>-1244356218</v>
       </c>
-      <c r="D39">
+      <c r="F39">
         <v>-1871400412</v>
       </c>
-      <c r="E39">
+      <c r="G39">
         <v>-450463540</v>
       </c>
-      <c r="F39">
+      <c r="H39">
         <v>-935865199</v>
       </c>
-      <c r="G39">
+      <c r="I39">
         <v>-770052378</v>
       </c>
-      <c r="H39">
+      <c r="J39">
         <v>-1024849916</v>
       </c>
-      <c r="I39">
+      <c r="K39">
         <v>-511925967</v>
       </c>
-      <c r="J39">
+      <c r="L39">
         <v>-142408032</v>
       </c>
-      <c r="K39">
+      <c r="M39">
         <v>-223862073</v>
       </c>
-      <c r="L39">
+      <c r="N39">
         <v>-465642006</v>
       </c>
-      <c r="M39">
+      <c r="O39">
         <v>-197870741</v>
       </c>
     </row>
@@ -5428,39 +6173,45 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
+        <v>-564966161</v>
+      </c>
+      <c r="C40">
+        <v>-1242537241</v>
+      </c>
+      <c r="D40">
         <v>606511329</v>
       </c>
-      <c r="C40">
+      <c r="E40">
         <v>686969134</v>
       </c>
-      <c r="D40">
+      <c r="F40">
         <v>658691054</v>
       </c>
-      <c r="E40">
+      <c r="G40">
         <v>-11052005</v>
       </c>
-      <c r="F40">
+      <c r="H40">
         <v>593100433</v>
       </c>
-      <c r="G40">
+      <c r="I40">
         <v>-27906145</v>
       </c>
-      <c r="H40">
+      <c r="J40">
         <v>-177331452</v>
       </c>
-      <c r="I40">
+      <c r="K40">
         <v>-114738516</v>
       </c>
-      <c r="J40">
+      <c r="L40">
         <v>567400901</v>
       </c>
-      <c r="K40">
+      <c r="M40">
         <v>2135332071</v>
       </c>
-      <c r="L40">
+      <c r="N40">
         <v>385399204</v>
       </c>
-      <c r="M40">
+      <c r="O40">
         <v>486081546</v>
       </c>
     </row>
@@ -5479,30 +6230,36 @@
         <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Yükümlülüklerdeki Artış (Azalış) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B43">
+        <v>-93585111</v>
+      </c>
+      <c r="C43">
+        <v>-8013295</v>
+      </c>
+      <c r="D43">
         <v>-245128</v>
       </c>
-      <c r="C43">
+      <c r="E43">
         <v>-245131</v>
       </c>
-      <c r="D43">
+      <c r="F43">
         <v>-245102</v>
       </c>
-      <c r="E43">
+      <c r="G43">
         <v>-7963</v>
       </c>
-      <c r="F43">
+      <c r="H43">
         <v>42983010</v>
       </c>
-      <c r="G43">
+      <c r="I43">
         <v>-28021325</v>
       </c>
-      <c r="H43">
+      <c r="J43">
         <v>-19412396</v>
       </c>
-      <c r="I43">
+      <c r="K43">
         <v>5762878</v>
       </c>
-      <c r="J43">
+      <c r="L43">
         <v>-65563672</v>
       </c>
     </row>
@@ -5511,39 +6268,45 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
+        <v>958043936</v>
+      </c>
+      <c r="C44">
+        <v>-911389617</v>
+      </c>
+      <c r="D44">
         <v>867407476</v>
       </c>
-      <c r="C44">
+      <c r="E44">
         <v>-794133252</v>
       </c>
-      <c r="D44">
+      <c r="F44">
         <v>325290288</v>
       </c>
-      <c r="E44">
+      <c r="G44">
         <v>-61520659</v>
       </c>
-      <c r="F44">
+      <c r="H44">
         <v>918142713</v>
       </c>
-      <c r="G44">
+      <c r="I44">
         <v>645659181</v>
       </c>
-      <c r="H44">
+      <c r="J44">
         <v>643742840</v>
       </c>
-      <c r="I44">
+      <c r="K44">
         <v>53848819</v>
       </c>
-      <c r="J44">
+      <c r="L44">
         <v>63008625</v>
       </c>
-      <c r="K44">
+      <c r="M44">
         <v>39503997</v>
       </c>
-      <c r="L44">
+      <c r="N44">
         <v>33291945</v>
       </c>
-      <c r="M44">
+      <c r="O44">
         <v>3804761</v>
       </c>
     </row>
@@ -5562,39 +6325,45 @@
         <v xml:space="preserve">    Ertelenmiş Gelirlerdeki Artış (Azalış)</v>
       </c>
       <c r="B47">
+        <v>376439084</v>
+      </c>
+      <c r="C47">
+        <v>1470619014</v>
+      </c>
+      <c r="D47">
         <v>374262806</v>
       </c>
-      <c r="C47">
+      <c r="E47">
         <v>94712669</v>
       </c>
-      <c r="D47">
+      <c r="F47">
         <v>226684022</v>
       </c>
-      <c r="E47">
+      <c r="G47">
         <v>-402934566</v>
       </c>
-      <c r="F47">
+      <c r="H47">
         <v>219897482</v>
       </c>
-      <c r="G47">
+      <c r="I47">
         <v>74878185</v>
       </c>
-      <c r="H47">
+      <c r="J47">
         <v>1637861796</v>
       </c>
-      <c r="I47">
+      <c r="K47">
         <v>811944977</v>
       </c>
-      <c r="J47">
+      <c r="L47">
         <v>0</v>
       </c>
-      <c r="K47">
+      <c r="M47">
         <v>728898226</v>
       </c>
-      <c r="L47">
+      <c r="N47">
         <v>1660652575</v>
       </c>
-      <c r="M47">
+      <c r="O47">
         <v>51012108</v>
       </c>
     </row>
@@ -5602,13 +6371,13 @@
       <c r="A48" t="str">
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
-      <c r="K48">
+      <c r="M48">
         <v>-1002624</v>
       </c>
-      <c r="L48">
+      <c r="N48">
         <v>-2636188</v>
       </c>
-      <c r="M48">
+      <c r="O48">
         <v>-204094</v>
       </c>
     </row>
@@ -5617,30 +6386,36 @@
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
       <c r="B49">
+        <v>854201478</v>
+      </c>
+      <c r="C49">
+        <v>-336632351</v>
+      </c>
+      <c r="D49">
         <v>2299401747</v>
       </c>
-      <c r="C49">
+      <c r="E49">
         <v>-1849587744</v>
       </c>
-      <c r="D49">
+      <c r="F49">
         <v>-1333647702</v>
       </c>
-      <c r="E49">
+      <c r="G49">
         <v>1018864221</v>
       </c>
-      <c r="F49">
+      <c r="H49">
         <v>222758755</v>
       </c>
-      <c r="G49">
+      <c r="I49">
         <v>-924726792</v>
       </c>
-      <c r="H49">
+      <c r="J49">
         <v>-650156010</v>
       </c>
-      <c r="I49">
+      <c r="K49">
         <v>821502545</v>
       </c>
-      <c r="J49">
+      <c r="L49">
         <v>2679763329</v>
       </c>
     </row>
@@ -5663,34 +6438,40 @@
       <c r="A53" t="str">
         <v xml:space="preserve">    Alınan Faiz</v>
       </c>
+      <c r="B53">
+        <v>45249670</v>
+      </c>
       <c r="C53">
+        <v>24315263</v>
+      </c>
+      <c r="E53">
         <v>299957676</v>
       </c>
-      <c r="D53">
+      <c r="F53">
         <v>155419565</v>
       </c>
-      <c r="E53">
+      <c r="G53">
         <v>75463514</v>
       </c>
-      <c r="G53">
+      <c r="I53">
         <v>9511720</v>
       </c>
-      <c r="H53">
+      <c r="J53">
         <v>5930965</v>
       </c>
-      <c r="I53">
+      <c r="K53">
         <v>2570296</v>
       </c>
-      <c r="J53">
+      <c r="L53">
         <v>6032736</v>
       </c>
-      <c r="K53">
+      <c r="M53">
         <v>3607527</v>
       </c>
-      <c r="L53">
+      <c r="N53">
         <v>3670192</v>
       </c>
-      <c r="M53">
+      <c r="O53">
         <v>191280</v>
       </c>
     </row>
@@ -5698,16 +6479,13 @@
       <c r="A54" t="str">
         <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
-      <c r="E54">
+      <c r="K54">
         <v>0</v>
       </c>
-      <c r="I54">
-        <v>0</v>
-      </c>
-      <c r="J54">
+      <c r="L54">
         <v>-62543827</v>
       </c>
-      <c r="K54">
+      <c r="M54">
         <v>-62543827</v>
       </c>
     </row>
@@ -5751,30 +6529,36 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalara İlişkin Karşılıklar Kapsamında Yapılan Ödemeler</v>
       </c>
       <c r="B62">
+        <v>-12607774</v>
+      </c>
+      <c r="C62">
+        <v>-3651151</v>
+      </c>
+      <c r="D62">
         <v>-8995788</v>
       </c>
-      <c r="C62">
+      <c r="E62">
         <v>-6557147</v>
       </c>
-      <c r="D62">
+      <c r="F62">
         <v>-3468709</v>
       </c>
-      <c r="E62">
+      <c r="G62">
         <v>-1094761</v>
       </c>
-      <c r="F62">
+      <c r="H62">
         <v>-78442685</v>
       </c>
-      <c r="G62">
+      <c r="I62">
         <v>-71732687</v>
       </c>
-      <c r="H62">
+      <c r="J62">
         <v>-22327090</v>
       </c>
-      <c r="I62">
+      <c r="K62">
         <v>-8784188</v>
       </c>
-      <c r="J62">
+      <c r="L62">
         <v>0</v>
       </c>
     </row>
@@ -5799,39 +6583,45 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
       <c r="B67">
+        <v>-1994340251</v>
+      </c>
+      <c r="C67">
+        <v>-953294039</v>
+      </c>
+      <c r="D67">
         <v>-6721761747</v>
       </c>
-      <c r="C67">
+      <c r="E67">
         <v>-3818232833</v>
       </c>
-      <c r="D67">
+      <c r="F67">
         <v>-839865200</v>
       </c>
-      <c r="E67">
+      <c r="G67">
         <v>-289209706</v>
       </c>
-      <c r="F67">
+      <c r="H67">
         <v>-1574717568</v>
       </c>
-      <c r="G67">
+      <c r="I67">
         <v>-625830473</v>
       </c>
-      <c r="H67">
+      <c r="J67">
         <v>-408217776</v>
       </c>
-      <c r="I67">
+      <c r="K67">
         <v>-84575918</v>
       </c>
-      <c r="J67">
+      <c r="L67">
         <v>-1222250017</v>
       </c>
-      <c r="K67">
+      <c r="M67">
         <v>-637812546</v>
       </c>
-      <c r="L67">
+      <c r="N67">
         <v>-347125737</v>
       </c>
-      <c r="M67">
+      <c r="O67">
         <v>-684934184</v>
       </c>
     </row>
@@ -5885,33 +6675,39 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B77">
+        <v>611348</v>
+      </c>
+      <c r="C77">
+        <v>0</v>
+      </c>
+      <c r="D77">
         <v>2703529</v>
       </c>
-      <c r="C77">
+      <c r="E77">
         <v>3325470</v>
       </c>
-      <c r="D77">
+      <c r="F77">
         <v>1245038</v>
       </c>
-      <c r="E77">
+      <c r="G77">
         <v>20379</v>
       </c>
-      <c r="F77">
+      <c r="H77">
         <v>1001562</v>
-      </c>
-      <c r="G77">
-        <v>0</v>
-      </c>
-      <c r="H77">
-        <v>0</v>
       </c>
       <c r="I77">
         <v>0</v>
       </c>
       <c r="J77">
+        <v>0</v>
+      </c>
+      <c r="K77">
+        <v>0</v>
+      </c>
+      <c r="L77">
         <v>28754</v>
       </c>
-      <c r="L77">
+      <c r="N77">
         <v>8395</v>
       </c>
     </row>
@@ -5920,39 +6716,45 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
       <c r="B78">
+        <v>-1994951599</v>
+      </c>
+      <c r="C78">
+        <v>-953294039</v>
+      </c>
+      <c r="D78">
         <v>-6724465276</v>
       </c>
-      <c r="C78">
+      <c r="E78">
         <v>-3821558303</v>
       </c>
-      <c r="D78">
+      <c r="F78">
         <v>-841110238</v>
       </c>
-      <c r="E78">
+      <c r="G78">
         <v>-289230085</v>
       </c>
-      <c r="F78">
+      <c r="H78">
         <v>-1575719130</v>
       </c>
-      <c r="G78">
+      <c r="I78">
         <v>-625830473</v>
       </c>
-      <c r="H78">
+      <c r="J78">
         <v>-408217776</v>
       </c>
-      <c r="I78">
+      <c r="K78">
         <v>-84575918</v>
       </c>
-      <c r="J78">
+      <c r="L78">
         <v>-1222278771</v>
       </c>
-      <c r="K78">
+      <c r="M78">
         <v>-637812546</v>
       </c>
-      <c r="L78">
+      <c r="N78">
         <v>-347134132</v>
       </c>
-      <c r="M78">
+      <c r="O78">
         <v>-684934184</v>
       </c>
     </row>
@@ -6067,39 +6869,45 @@
         <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B101">
+        <v>-888125708</v>
+      </c>
+      <c r="C101">
+        <v>308746634</v>
+      </c>
+      <c r="D101">
         <v>6361425579</v>
       </c>
-      <c r="C101">
+      <c r="E101">
         <v>7794303360</v>
       </c>
-      <c r="D101">
+      <c r="F101">
         <v>6392878969</v>
       </c>
-      <c r="E101">
+      <c r="G101">
         <v>-73752764</v>
       </c>
-      <c r="F101">
+      <c r="H101">
         <v>1516126212</v>
       </c>
-      <c r="G101">
+      <c r="I101">
         <v>1658802728</v>
       </c>
-      <c r="H101">
+      <c r="J101">
         <v>1186789401</v>
       </c>
-      <c r="I101">
+      <c r="K101">
         <v>-721715969</v>
       </c>
-      <c r="J101">
+      <c r="L101">
         <v>-1423875054</v>
       </c>
-      <c r="K101">
+      <c r="M101">
         <v>-396090990</v>
       </c>
-      <c r="L101">
+      <c r="N101">
         <v>-22316949</v>
       </c>
-      <c r="M101">
+      <c r="O101">
         <v>-1639059524</v>
       </c>
     </row>
@@ -6118,24 +6926,30 @@
         <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B104">
+        <v>0</v>
+      </c>
+      <c r="C104">
+        <v>0</v>
+      </c>
+      <c r="D104">
         <v>2408368625</v>
-      </c>
-      <c r="C104">
-        <v>2449618562</v>
-      </c>
-      <c r="D104">
-        <v>2449618562</v>
       </c>
       <c r="E104">
         <v>2449618562</v>
       </c>
       <c r="F104">
+        <v>2449618562</v>
+      </c>
+      <c r="G104">
+        <v>2449618562</v>
+      </c>
+      <c r="H104">
         <v>0</v>
       </c>
-      <c r="G104">
+      <c r="I104">
         <v>0</v>
       </c>
-      <c r="H104">
+      <c r="J104">
         <v>0</v>
       </c>
     </row>
@@ -6143,15 +6957,39 @@
       <c r="A105" t="str">
         <v xml:space="preserve">    Sermaye Avanslarından Nakit Girişleri</v>
       </c>
+      <c r="B105">
+        <v>3419205837</v>
+      </c>
+      <c r="C105">
+        <v>3419205837</v>
+      </c>
+      <c r="F105">
+        <v>0</v>
+      </c>
+      <c r="G105">
+        <v>0</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
         <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
       </c>
       <c r="B106">
+        <v>-144546282</v>
+      </c>
+      <c r="C106">
+        <v>-144546282</v>
+      </c>
+      <c r="D106">
         <v>-80382359</v>
       </c>
       <c r="F106">
+        <v>0</v>
+      </c>
+      <c r="G106">
+        <v>0</v>
+      </c>
+      <c r="H106">
         <v>0</v>
       </c>
     </row>
@@ -6170,39 +7008,45 @@
         <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B109">
+        <v>0</v>
+      </c>
+      <c r="C109">
+        <v>0</v>
+      </c>
+      <c r="D109">
         <v>9238509781</v>
       </c>
-      <c r="C109">
+      <c r="E109">
         <v>9225012663</v>
       </c>
-      <c r="D109">
+      <c r="F109">
         <v>8495294163</v>
       </c>
-      <c r="E109">
+      <c r="G109">
         <v>1279639236</v>
       </c>
-      <c r="F109">
+      <c r="H109">
         <v>5501567775</v>
       </c>
-      <c r="G109">
+      <c r="I109">
         <v>4421799752</v>
       </c>
-      <c r="H109">
+      <c r="J109">
         <v>2378292787</v>
-      </c>
-      <c r="I109">
-        <v>280000000</v>
-      </c>
-      <c r="J109">
-        <v>500000000</v>
       </c>
       <c r="K109">
         <v>280000000</v>
       </c>
       <c r="L109">
+        <v>500000000</v>
+      </c>
+      <c r="M109">
+        <v>280000000</v>
+      </c>
+      <c r="N109">
         <v>3648635908</v>
       </c>
-      <c r="M109">
+      <c r="O109">
         <v>2372844974</v>
       </c>
     </row>
@@ -6211,39 +7055,45 @@
         <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
       <c r="B110">
+        <v>-3167305124</v>
+      </c>
+      <c r="C110">
+        <v>-2032008432</v>
+      </c>
+      <c r="D110">
         <v>-4533496701</v>
       </c>
-      <c r="C110">
+      <c r="E110">
         <v>-4363710965</v>
       </c>
-      <c r="D110">
+      <c r="F110">
         <v>-4163604563</v>
       </c>
-      <c r="E110">
+      <c r="G110">
         <v>-2649462302</v>
       </c>
-      <c r="F110">
+      <c r="H110">
         <v>-2649462302</v>
       </c>
-      <c r="G110">
+      <c r="I110">
         <v>-1583454766</v>
       </c>
-      <c r="H110">
+      <c r="J110">
         <v>-428275649</v>
-      </c>
-      <c r="I110">
-        <v>-654071874</v>
-      </c>
-      <c r="J110">
-        <v>-1868624392</v>
       </c>
       <c r="K110">
         <v>-654071874</v>
       </c>
       <c r="L110">
+        <v>-1868624392</v>
+      </c>
+      <c r="M110">
+        <v>-654071874</v>
+      </c>
+      <c r="N110">
         <v>-3523971759</v>
       </c>
-      <c r="M110">
+      <c r="O110">
         <v>-3827111278</v>
       </c>
     </row>
@@ -6287,39 +7137,45 @@
         <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
       <c r="B118">
+        <v>-995480139</v>
+      </c>
+      <c r="C118">
+        <v>-933904489</v>
+      </c>
+      <c r="D118">
         <v>-1034827761</v>
       </c>
-      <c r="C118">
+      <c r="E118">
         <v>483383100</v>
       </c>
-      <c r="D118">
+      <c r="F118">
         <v>-388429193</v>
       </c>
-      <c r="E118">
+      <c r="G118">
         <v>-1153548260</v>
       </c>
-      <c r="F118">
+      <c r="H118">
         <v>-1351141475</v>
       </c>
-      <c r="G118">
+      <c r="I118">
         <v>-1179542258</v>
       </c>
-      <c r="H118">
+      <c r="J118">
         <v>-763227737</v>
       </c>
-      <c r="I118">
+      <c r="K118">
         <v>-347644095</v>
       </c>
-      <c r="J118">
+      <c r="L118">
         <v>-55250662</v>
       </c>
-      <c r="K118">
+      <c r="M118">
         <v>-22019116</v>
       </c>
-      <c r="L118">
+      <c r="N118">
         <v>-146981098</v>
       </c>
-      <c r="M118">
+      <c r="O118">
         <v>-184793220</v>
       </c>
     </row>
@@ -6327,10 +7183,10 @@
       <c r="A119" t="str">
         <v xml:space="preserve">    Alınan Faiz</v>
       </c>
-      <c r="B119">
+      <c r="D119">
         <v>363253994</v>
       </c>
-      <c r="F119">
+      <c r="H119">
         <v>15162214</v>
       </c>
     </row>
@@ -6364,30 +7220,36 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B125">
+        <v>-1995622585</v>
+      </c>
+      <c r="C125">
+        <v>-960515644</v>
+      </c>
+      <c r="D125">
         <v>1930069791</v>
       </c>
-      <c r="C125">
+      <c r="E125">
         <v>2419883312</v>
       </c>
-      <c r="D125">
+      <c r="F125">
         <v>4371316923</v>
       </c>
-      <c r="E125">
+      <c r="G125">
         <v>730270504</v>
       </c>
-      <c r="F125">
+      <c r="H125">
         <v>85724714</v>
       </c>
-      <c r="G125">
+      <c r="I125">
         <v>46024496</v>
       </c>
-      <c r="H125">
+      <c r="J125">
         <v>112019490</v>
       </c>
-      <c r="I125">
+      <c r="K125">
         <v>8996766</v>
       </c>
-      <c r="J125">
+      <c r="L125">
         <v>-22872833</v>
       </c>
     </row>
@@ -6401,39 +7263,45 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
+        <v>-1995622585</v>
+      </c>
+      <c r="C127">
+        <v>-960515644</v>
+      </c>
+      <c r="D127">
         <v>1930069791</v>
       </c>
-      <c r="C127">
+      <c r="E127">
         <v>2419883312</v>
       </c>
-      <c r="D127">
+      <c r="F127">
         <v>4371316923</v>
       </c>
-      <c r="E127">
+      <c r="G127">
         <v>730270504</v>
       </c>
-      <c r="F127">
+      <c r="H127">
         <v>85724714</v>
       </c>
-      <c r="G127">
+      <c r="I127">
         <v>46024496</v>
       </c>
-      <c r="H127">
+      <c r="J127">
         <v>112019490</v>
       </c>
-      <c r="I127">
+      <c r="K127">
         <v>8996766</v>
       </c>
-      <c r="J127">
+      <c r="L127">
         <v>-22872833</v>
       </c>
-      <c r="K127">
+      <c r="M127">
         <v>-54741924</v>
       </c>
-      <c r="L127">
+      <c r="N127">
         <v>48980823</v>
       </c>
-      <c r="M127">
+      <c r="O127">
         <v>-2807376</v>
       </c>
     </row>
@@ -6442,10 +7310,10 @@
         <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B128">
-        <v>119454439</v>
+        <v>2049524230</v>
       </c>
       <c r="C128">
-        <v>119454439</v>
+        <v>2049524230</v>
       </c>
       <c r="D128">
         <v>119454439</v>
@@ -6454,10 +7322,10 @@
         <v>119454439</v>
       </c>
       <c r="F128">
-        <v>33729725</v>
+        <v>119454439</v>
       </c>
       <c r="G128">
-        <v>33729725</v>
+        <v>119454439</v>
       </c>
       <c r="H128">
         <v>33729725</v>
@@ -6466,6 +7334,12 @@
         <v>33729725</v>
       </c>
       <c r="J128">
+        <v>33729725</v>
+      </c>
+      <c r="K128">
+        <v>33729725</v>
+      </c>
+      <c r="L128">
         <v>56602558</v>
       </c>
     </row>
@@ -6474,43 +7348,49 @@
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B129">
+        <v>53901645</v>
+      </c>
+      <c r="C129">
+        <v>1089008586</v>
+      </c>
+      <c r="D129">
         <v>2049524230</v>
       </c>
-      <c r="C129">
+      <c r="E129">
         <v>2539337751</v>
       </c>
-      <c r="D129">
+      <c r="F129">
         <v>4490771362</v>
       </c>
-      <c r="E129">
+      <c r="G129">
         <v>849724943</v>
       </c>
-      <c r="F129">
+      <c r="H129">
         <v>119454439</v>
       </c>
-      <c r="G129">
+      <c r="I129">
         <v>79754221</v>
       </c>
-      <c r="H129">
+      <c r="J129">
         <v>145749215</v>
       </c>
-      <c r="I129">
+      <c r="K129">
         <v>42726491</v>
       </c>
-      <c r="J129">
+      <c r="L129">
         <v>33729725</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O129"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M129"/>
+  <dimension ref="A1:O129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -6525,6 +7405,8 @@
     <col min="11" max="11" customWidth="1" width="20"/>
     <col min="12" max="12" customWidth="1" width="20"/>
     <col min="13" max="13" customWidth="1" width="20"/>
+    <col min="14" max="14" customWidth="1" width="20"/>
+    <col min="15" max="15" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6532,39 +7414,45 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="C1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="D1" t="str">
+      <c r="F1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="E1" t="str">
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2024/3</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>2023/9</v>
       </c>
-      <c r="L1" t="str">
+      <c r="N1" t="str">
         <v>2022/12</v>
       </c>
-      <c r="M1" t="str">
+      <c r="O1" t="str">
         <v>2021/12</v>
       </c>
     </row>
@@ -6578,30 +7466,36 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
+        <v>1202811613</v>
+      </c>
+      <c r="C3">
+        <v>-315968239</v>
+      </c>
+      <c r="D3">
         <v>3846593174</v>
       </c>
-      <c r="C3">
+      <c r="E3">
         <v>-374490369</v>
       </c>
-      <c r="D3">
+      <c r="F3">
         <v>-2274929820</v>
       </c>
-      <c r="E3">
+      <c r="G3">
         <v>1093232974</v>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>1131263829</v>
       </c>
-      <c r="G3">
+      <c r="I3">
         <v>-320395624</v>
       </c>
-      <c r="H3">
+      <c r="J3">
         <v>-1481840788</v>
       </c>
-      <c r="I3">
+      <c r="K3">
         <v>815288653</v>
       </c>
-      <c r="J3">
+      <c r="L3">
         <v>1644090625</v>
       </c>
     </row>
@@ -6610,30 +7504,36 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
+        <v>1124753795</v>
+      </c>
+      <c r="C4">
+        <v>-1023520289</v>
+      </c>
+      <c r="D4">
         <v>-1111319397</v>
       </c>
-      <c r="C4">
+      <c r="E4">
         <v>1687804005</v>
       </c>
-      <c r="D4">
+      <c r="F4">
         <v>-671085454</v>
       </c>
-      <c r="E4">
+      <c r="G4">
         <v>-596789574</v>
       </c>
-      <c r="F4">
+      <c r="H4">
         <v>-519023334</v>
       </c>
-      <c r="G4">
+      <c r="I4">
         <v>-593993504</v>
       </c>
-      <c r="H4">
+      <c r="J4">
         <v>17416661</v>
       </c>
-      <c r="I4">
+      <c r="K4">
         <v>743445721</v>
       </c>
-      <c r="J4">
+      <c r="L4">
         <v>2656337974</v>
       </c>
     </row>
@@ -6642,27 +7542,33 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
+        <v>-1908415603</v>
+      </c>
+      <c r="C5">
+        <v>1677284973</v>
+      </c>
+      <c r="D5">
         <v>2689543031</v>
       </c>
-      <c r="C5">
+      <c r="E5">
         <v>-2442380090</v>
       </c>
-      <c r="D5">
+      <c r="F5">
         <v>-758632415</v>
       </c>
-      <c r="E5">
+      <c r="G5">
         <v>2690383636</v>
       </c>
-      <c r="F5">
+      <c r="H5">
         <v>-247051098</v>
       </c>
-      <c r="G5">
+      <c r="I5">
         <v>1761151337</v>
       </c>
-      <c r="H5">
+      <c r="J5">
         <v>-1158122858</v>
       </c>
-      <c r="I5">
+      <c r="K5">
         <v>1355394754</v>
       </c>
     </row>
@@ -6671,30 +7577,36 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
+        <v>302185524</v>
+      </c>
+      <c r="C6">
+        <v>179108248</v>
+      </c>
+      <c r="D6">
         <v>381635917</v>
       </c>
-      <c r="C6">
+      <c r="E6">
         <v>189326312</v>
       </c>
-      <c r="D6">
+      <c r="F6">
         <v>174129340</v>
       </c>
-      <c r="E6">
+      <c r="G6">
         <v>153064451</v>
       </c>
-      <c r="F6">
+      <c r="H6">
         <v>-19429524</v>
       </c>
-      <c r="G6">
+      <c r="I6">
         <v>127621010</v>
       </c>
-      <c r="H6">
+      <c r="J6">
         <v>207277550</v>
       </c>
-      <c r="I6">
+      <c r="K6">
         <v>198657431</v>
       </c>
-      <c r="J6">
+      <c r="L6">
         <v>238715142</v>
       </c>
     </row>
@@ -6708,30 +7620,36 @@
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
+        <v>608083032</v>
+      </c>
+      <c r="C8">
+        <v>5959578</v>
+      </c>
+      <c r="D8">
         <v>-2688711</v>
       </c>
-      <c r="C8">
+      <c r="E8">
         <v>-830894</v>
       </c>
-      <c r="D8">
+      <c r="F8">
         <v>7870479</v>
       </c>
-      <c r="E8">
+      <c r="G8">
         <v>20560094</v>
       </c>
-      <c r="F8">
+      <c r="H8">
         <v>4080642</v>
       </c>
-      <c r="G8">
+      <c r="I8">
         <v>-2566958</v>
       </c>
-      <c r="H8">
+      <c r="J8">
         <v>-19279522</v>
       </c>
-      <c r="I8">
+      <c r="K8">
         <v>32241170</v>
       </c>
-      <c r="J8">
+      <c r="L8">
         <v>-17491964</v>
       </c>
     </row>
@@ -6755,30 +7673,36 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
+        <v>272694760</v>
+      </c>
+      <c r="C12">
+        <v>413525053</v>
+      </c>
+      <c r="D12">
         <v>238620828</v>
       </c>
-      <c r="C12">
+      <c r="E12">
         <v>337203044</v>
       </c>
-      <c r="D12">
+      <c r="F12">
         <v>153589149</v>
       </c>
-      <c r="E12">
+      <c r="G12">
         <v>219470350</v>
       </c>
-      <c r="F12">
+      <c r="H12">
         <v>352317312</v>
       </c>
-      <c r="G12">
+      <c r="I12">
         <v>298538091</v>
       </c>
-      <c r="H12">
+      <c r="J12">
         <v>535703020</v>
       </c>
-      <c r="I12">
+      <c r="K12">
         <v>119295259</v>
       </c>
-      <c r="J12">
+      <c r="L12">
         <v>294106569</v>
       </c>
     </row>
@@ -6797,30 +7721,36 @@
         <v xml:space="preserve">    Gerçekleşmemiş Yabancı Para Çevrim Farkları İle İlgili Düzeltmeler</v>
       </c>
       <c r="B15">
+        <v>-55449879</v>
+      </c>
+      <c r="C15">
+        <v>801036212</v>
+      </c>
+      <c r="D15">
         <v>1130019501</v>
       </c>
-      <c r="C15">
+      <c r="E15">
         <v>-1742822523</v>
       </c>
-      <c r="D15">
+      <c r="F15">
         <v>-1343201620</v>
       </c>
-      <c r="E15">
+      <c r="G15">
         <v>1977925061</v>
       </c>
-      <c r="F15">
+      <c r="H15">
         <v>-680661286</v>
       </c>
-      <c r="G15">
+      <c r="I15">
         <v>712950506</v>
       </c>
-      <c r="H15">
+      <c r="J15">
         <v>-1464399133</v>
       </c>
-      <c r="I15">
+      <c r="K15">
         <v>1269486695</v>
       </c>
-      <c r="J15">
+      <c r="L15">
         <v>609886013</v>
       </c>
     </row>
@@ -6849,30 +7779,36 @@
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B20">
+        <v>-3035929040</v>
+      </c>
+      <c r="C20">
+        <v>277655882</v>
+      </c>
+      <c r="D20">
         <v>941955496</v>
       </c>
-      <c r="C20">
+      <c r="E20">
         <v>-1225256029</v>
       </c>
-      <c r="D20">
+      <c r="F20">
         <v>248980237</v>
       </c>
-      <c r="E20">
+      <c r="G20">
         <v>319363680</v>
       </c>
-      <c r="F20">
+      <c r="H20">
         <v>96641758</v>
       </c>
-      <c r="G20">
+      <c r="I20">
         <v>624608688</v>
       </c>
-      <c r="H20">
+      <c r="J20">
         <v>-417424773</v>
       </c>
-      <c r="I20">
+      <c r="K20">
         <v>-264285801</v>
       </c>
-      <c r="J20">
+      <c r="L20">
         <v>-1697990926</v>
       </c>
     </row>
@@ -6916,27 +7852,33 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
+        <v>1974495637</v>
+      </c>
+      <c r="C28">
+        <v>-990397035</v>
+      </c>
+      <c r="D28">
         <v>2570765857</v>
       </c>
-      <c r="C28">
+      <c r="E28">
         <v>238636043</v>
       </c>
-      <c r="D28">
+      <c r="F28">
         <v>-922794054</v>
       </c>
-      <c r="E28">
+      <c r="G28">
         <v>-1074729841</v>
       </c>
-      <c r="F28">
+      <c r="H28">
         <v>1913559979</v>
       </c>
-      <c r="G28">
+      <c r="I28">
         <v>-1441728615</v>
       </c>
-      <c r="H28">
+      <c r="J28">
         <v>-330952358</v>
       </c>
-      <c r="I28">
+      <c r="K28">
         <v>-1277337930</v>
       </c>
     </row>
@@ -6955,30 +7897,36 @@
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B31">
+        <v>295029867</v>
+      </c>
+      <c r="C31">
+        <v>227602084</v>
+      </c>
+      <c r="D31">
         <v>330981993</v>
       </c>
-      <c r="C31">
+      <c r="E31">
         <v>2311089528</v>
       </c>
-      <c r="D31">
+      <c r="F31">
         <v>-2123489400</v>
       </c>
-      <c r="E31">
+      <c r="G31">
         <v>-551861501</v>
       </c>
-      <c r="F31">
+      <c r="H31">
         <v>116614333</v>
       </c>
-      <c r="G31">
+      <c r="I31">
         <v>74430490</v>
       </c>
-      <c r="H31">
+      <c r="J31">
         <v>55521102</v>
       </c>
-      <c r="I31">
+      <c r="K31">
         <v>-619264837</v>
       </c>
-      <c r="J31">
+      <c r="L31">
         <v>367788366</v>
       </c>
     </row>
@@ -6992,30 +7940,36 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
+        <v>-296167117</v>
+      </c>
+      <c r="C33">
+        <v>-493117823</v>
+      </c>
+      <c r="D33">
         <v>-317275640</v>
       </c>
-      <c r="C33">
+      <c r="E33">
         <v>-547398442</v>
       </c>
-      <c r="D33">
+      <c r="F33">
         <v>278928901</v>
       </c>
-      <c r="E33">
+      <c r="G33">
         <v>23393293</v>
       </c>
-      <c r="F33">
+      <c r="H33">
         <v>122827774</v>
       </c>
-      <c r="G33">
+      <c r="I33">
         <v>-101650252</v>
       </c>
-      <c r="H33">
+      <c r="J33">
         <v>-59101759</v>
       </c>
-      <c r="I33">
+      <c r="K33">
         <v>-78658655</v>
       </c>
-      <c r="J33">
+      <c r="L33">
         <v>96523294</v>
       </c>
     </row>
@@ -7039,30 +7993,36 @@
         <v xml:space="preserve">    Stoklardaki Azalışlar (Artışlar) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B37">
+        <v>-51761490</v>
+      </c>
+      <c r="C37">
+        <v>-919447151</v>
+      </c>
+      <c r="D37">
         <v>187134051</v>
       </c>
-      <c r="C37">
+      <c r="E37">
         <v>-928982395</v>
       </c>
-      <c r="D37">
+      <c r="F37">
         <v>656767862</v>
       </c>
-      <c r="E37">
+      <c r="G37">
         <v>379717100</v>
       </c>
-      <c r="F37">
+      <c r="H37">
         <v>730416951</v>
       </c>
-      <c r="G37">
+      <c r="I37">
         <v>-249055499</v>
       </c>
-      <c r="H37">
+      <c r="J37">
         <v>-1142490382</v>
       </c>
-      <c r="I37">
+      <c r="K37">
         <v>-824306629</v>
       </c>
-      <c r="J37">
+      <c r="L37">
         <v>1350222723</v>
       </c>
     </row>
@@ -7076,30 +8036,36 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
+        <v>660141490</v>
+      </c>
+      <c r="C39">
+        <v>885886994</v>
+      </c>
+      <c r="D39">
         <v>509292390</v>
       </c>
-      <c r="C39">
+      <c r="E39">
         <v>627044194</v>
       </c>
-      <c r="D39">
+      <c r="F39">
         <v>-1420936872</v>
       </c>
-      <c r="E39">
+      <c r="G39">
         <v>-450463540</v>
       </c>
-      <c r="F39">
+      <c r="H39">
         <v>-165812821</v>
       </c>
-      <c r="G39">
+      <c r="I39">
         <v>254797538</v>
       </c>
-      <c r="H39">
+      <c r="J39">
         <v>-512923949</v>
       </c>
-      <c r="I39">
+      <c r="K39">
         <v>-511925967</v>
       </c>
-      <c r="J39">
+      <c r="L39">
         <v>81454041</v>
       </c>
     </row>
@@ -7108,30 +8074,36 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
+        <v>677571080</v>
+      </c>
+      <c r="C40">
+        <v>-1242537241</v>
+      </c>
+      <c r="D40">
         <v>-80457805</v>
       </c>
-      <c r="C40">
+      <c r="E40">
         <v>28278080</v>
       </c>
-      <c r="D40">
+      <c r="F40">
         <v>669743059</v>
       </c>
-      <c r="E40">
+      <c r="G40">
         <v>-11052005</v>
       </c>
-      <c r="F40">
+      <c r="H40">
         <v>621006578</v>
       </c>
-      <c r="G40">
+      <c r="I40">
         <v>149425307</v>
       </c>
-      <c r="H40">
+      <c r="J40">
         <v>-62592936</v>
       </c>
-      <c r="I40">
+      <c r="K40">
         <v>-114738516</v>
       </c>
-      <c r="J40">
+      <c r="L40">
         <v>-1567931170</v>
       </c>
     </row>
@@ -7150,27 +8122,33 @@
         <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Yükümlülüklerdeki Artış (Azalış) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B43">
+        <v>-85571816</v>
+      </c>
+      <c r="C43">
+        <v>-8013295</v>
+      </c>
+      <c r="D43">
         <v>3</v>
       </c>
-      <c r="C43">
+      <c r="E43">
         <v>-29</v>
       </c>
-      <c r="D43">
+      <c r="F43">
         <v>-237139</v>
       </c>
-      <c r="E43">
+      <c r="G43">
         <v>-7963</v>
       </c>
-      <c r="F43">
+      <c r="H43">
         <v>71004335</v>
       </c>
-      <c r="G43">
+      <c r="I43">
         <v>-8608929</v>
       </c>
-      <c r="H43">
+      <c r="J43">
         <v>-25175274</v>
       </c>
-      <c r="I43">
+      <c r="K43">
         <v>5762878</v>
       </c>
     </row>
@@ -7179,30 +8157,36 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
+        <v>1869433553</v>
+      </c>
+      <c r="C44">
+        <v>-911389617</v>
+      </c>
+      <c r="D44">
         <v>1661540728</v>
       </c>
-      <c r="C44">
+      <c r="E44">
         <v>-1119423540</v>
       </c>
-      <c r="D44">
+      <c r="F44">
         <v>386810947</v>
       </c>
-      <c r="E44">
+      <c r="G44">
         <v>-61520659</v>
       </c>
-      <c r="F44">
+      <c r="H44">
         <v>272483532</v>
       </c>
-      <c r="G44">
+      <c r="I44">
         <v>1916341</v>
       </c>
-      <c r="H44">
+      <c r="J44">
         <v>589894021</v>
       </c>
-      <c r="I44">
+      <c r="K44">
         <v>53848819</v>
       </c>
-      <c r="J44">
+      <c r="L44">
         <v>23504628</v>
       </c>
     </row>
@@ -7221,30 +8205,36 @@
         <v xml:space="preserve">    Ertelenmiş Gelirlerdeki Artış (Azalış)</v>
       </c>
       <c r="B47">
+        <v>-1094179930</v>
+      </c>
+      <c r="C47">
+        <v>1470619014</v>
+      </c>
+      <c r="D47">
         <v>279550137</v>
       </c>
-      <c r="C47">
+      <c r="E47">
         <v>-131971353</v>
       </c>
-      <c r="D47">
+      <c r="F47">
         <v>629618588</v>
       </c>
-      <c r="E47">
+      <c r="G47">
         <v>-402934566</v>
       </c>
-      <c r="F47">
+      <c r="H47">
         <v>145019297</v>
       </c>
-      <c r="G47">
+      <c r="I47">
         <v>-1562983611</v>
       </c>
-      <c r="H47">
+      <c r="J47">
         <v>825916819</v>
       </c>
-      <c r="I47">
+      <c r="K47">
         <v>811944977</v>
       </c>
-      <c r="J47">
+      <c r="L47">
         <v>-728898226</v>
       </c>
     </row>
@@ -7258,27 +8248,33 @@
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
       <c r="B49">
+        <v>1190833829</v>
+      </c>
+      <c r="C49">
+        <v>-336632351</v>
+      </c>
+      <c r="D49">
         <v>4148989491</v>
       </c>
-      <c r="C49">
+      <c r="E49">
         <v>-515940042</v>
       </c>
-      <c r="D49">
+      <c r="F49">
         <v>-2352511923</v>
       </c>
-      <c r="E49">
+      <c r="G49">
         <v>1018864221</v>
       </c>
-      <c r="F49">
+      <c r="H49">
         <v>1147485547</v>
       </c>
-      <c r="G49">
+      <c r="I49">
         <v>-274570782</v>
       </c>
-      <c r="H49">
+      <c r="J49">
         <v>-1471658555</v>
       </c>
-      <c r="I49">
+      <c r="K49">
         <v>821502545</v>
       </c>
     </row>
@@ -7301,25 +8297,31 @@
       <c r="A53" t="str">
         <v xml:space="preserve">    Alınan Faiz</v>
       </c>
+      <c r="B53">
+        <v>20934407</v>
+      </c>
       <c r="C53">
+        <v>24315263</v>
+      </c>
+      <c r="E53">
         <v>144538111</v>
       </c>
-      <c r="D53">
+      <c r="F53">
         <v>79956051</v>
       </c>
-      <c r="E53">
+      <c r="G53">
         <v>75463514</v>
       </c>
-      <c r="G53">
+      <c r="I53">
         <v>3580755</v>
       </c>
-      <c r="H53">
+      <c r="J53">
         <v>3360669</v>
       </c>
-      <c r="I53">
+      <c r="K53">
         <v>2570296</v>
       </c>
-      <c r="J53">
+      <c r="L53">
         <v>2425209</v>
       </c>
     </row>
@@ -7327,13 +8329,10 @@
       <c r="A54" t="str">
         <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
-      <c r="E54">
+      <c r="K54">
         <v>0</v>
       </c>
-      <c r="I54">
-        <v>0</v>
-      </c>
-      <c r="J54">
+      <c r="L54">
         <v>0</v>
       </c>
     </row>
@@ -7377,27 +8376,33 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalara İlişkin Karşılıklar Kapsamında Yapılan Ödemeler</v>
       </c>
       <c r="B62">
+        <v>-8956623</v>
+      </c>
+      <c r="C62">
+        <v>-3651151</v>
+      </c>
+      <c r="D62">
         <v>-2438641</v>
       </c>
-      <c r="C62">
+      <c r="E62">
         <v>-3088438</v>
       </c>
-      <c r="D62">
+      <c r="F62">
         <v>-2373948</v>
       </c>
-      <c r="E62">
+      <c r="G62">
         <v>-1094761</v>
       </c>
-      <c r="F62">
+      <c r="H62">
         <v>-6709998</v>
       </c>
-      <c r="G62">
+      <c r="I62">
         <v>-49405597</v>
       </c>
-      <c r="H62">
+      <c r="J62">
         <v>-13542902</v>
       </c>
-      <c r="I62">
+      <c r="K62">
         <v>-8784188</v>
       </c>
     </row>
@@ -7422,30 +8427,36 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
       <c r="B67">
+        <v>-1041046212</v>
+      </c>
+      <c r="C67">
+        <v>-953294039</v>
+      </c>
+      <c r="D67">
         <v>-2903528914</v>
       </c>
-      <c r="C67">
+      <c r="E67">
         <v>-2978367633</v>
       </c>
-      <c r="D67">
+      <c r="F67">
         <v>-550655494</v>
       </c>
-      <c r="E67">
+      <c r="G67">
         <v>-289209706</v>
       </c>
-      <c r="F67">
+      <c r="H67">
         <v>-948887095</v>
       </c>
-      <c r="G67">
+      <c r="I67">
         <v>-217612697</v>
       </c>
-      <c r="H67">
+      <c r="J67">
         <v>-323641858</v>
       </c>
-      <c r="I67">
+      <c r="K67">
         <v>-84575918</v>
       </c>
-      <c r="J67">
+      <c r="L67">
         <v>-584437471</v>
       </c>
     </row>
@@ -7499,27 +8510,33 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B77">
+        <v>611348</v>
+      </c>
+      <c r="C77">
+        <v>0</v>
+      </c>
+      <c r="D77">
         <v>-621941</v>
       </c>
-      <c r="C77">
+      <c r="E77">
         <v>2080432</v>
       </c>
-      <c r="D77">
+      <c r="F77">
         <v>1224659</v>
       </c>
-      <c r="E77">
+      <c r="G77">
         <v>20379</v>
       </c>
-      <c r="F77">
+      <c r="H77">
         <v>1001562</v>
       </c>
-      <c r="G77">
+      <c r="I77">
         <v>0</v>
       </c>
-      <c r="H77">
+      <c r="J77">
         <v>0</v>
       </c>
-      <c r="I77">
+      <c r="K77">
         <v>0</v>
       </c>
     </row>
@@ -7528,30 +8545,36 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
       <c r="B78">
+        <v>-1041657560</v>
+      </c>
+      <c r="C78">
+        <v>-953294039</v>
+      </c>
+      <c r="D78">
         <v>-2902906973</v>
       </c>
-      <c r="C78">
+      <c r="E78">
         <v>-2980448065</v>
       </c>
-      <c r="D78">
+      <c r="F78">
         <v>-551880153</v>
       </c>
-      <c r="E78">
+      <c r="G78">
         <v>-289230085</v>
       </c>
-      <c r="F78">
+      <c r="H78">
         <v>-949888657</v>
       </c>
-      <c r="G78">
+      <c r="I78">
         <v>-217612697</v>
       </c>
-      <c r="H78">
+      <c r="J78">
         <v>-323641858</v>
       </c>
-      <c r="I78">
+      <c r="K78">
         <v>-84575918</v>
       </c>
-      <c r="J78">
+      <c r="L78">
         <v>-584466225</v>
       </c>
     </row>
@@ -7666,30 +8689,36 @@
         <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B101">
+        <v>-1196872342</v>
+      </c>
+      <c r="C101">
+        <v>308746634</v>
+      </c>
+      <c r="D101">
         <v>-1432877781</v>
       </c>
-      <c r="C101">
+      <c r="E101">
         <v>1401424391</v>
       </c>
-      <c r="D101">
+      <c r="F101">
         <v>6466631733</v>
       </c>
-      <c r="E101">
+      <c r="G101">
         <v>-73752764</v>
       </c>
-      <c r="F101">
+      <c r="H101">
         <v>-142676516</v>
       </c>
-      <c r="G101">
+      <c r="I101">
         <v>472013327</v>
       </c>
-      <c r="H101">
+      <c r="J101">
         <v>1908505370</v>
       </c>
-      <c r="I101">
+      <c r="K101">
         <v>-721715969</v>
       </c>
-      <c r="J101">
+      <c r="L101">
         <v>-1027784064</v>
       </c>
     </row>
@@ -7708,21 +8737,27 @@
         <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B104">
-        <v>-41249937</v>
+        <v>0</v>
       </c>
       <c r="C104">
         <v>0</v>
       </c>
       <c r="D104">
+        <v>-41249937</v>
+      </c>
+      <c r="E104">
         <v>0</v>
-      </c>
-      <c r="E104">
-        <v>2449618562</v>
       </c>
       <c r="F104">
         <v>0</v>
       </c>
       <c r="G104">
+        <v>2449618562</v>
+      </c>
+      <c r="H104">
+        <v>0</v>
+      </c>
+      <c r="I104">
         <v>0</v>
       </c>
     </row>
@@ -7730,11 +8765,35 @@
       <c r="A105" t="str">
         <v xml:space="preserve">    Sermaye Avanslarından Nakit Girişleri</v>
       </c>
+      <c r="B105">
+        <v>0</v>
+      </c>
+      <c r="C105">
+        <v>3419205837</v>
+      </c>
+      <c r="F105">
+        <v>0</v>
+      </c>
+      <c r="G105">
+        <v>0</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
         <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
       </c>
+      <c r="B106">
+        <v>0</v>
+      </c>
+      <c r="C106">
+        <v>-144546282</v>
+      </c>
+      <c r="F106">
+        <v>0</v>
+      </c>
+      <c r="G106">
+        <v>0</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
@@ -7751,30 +8810,36 @@
         <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B109">
+        <v>0</v>
+      </c>
+      <c r="C109">
+        <v>0</v>
+      </c>
+      <c r="D109">
         <v>13497118</v>
       </c>
-      <c r="C109">
+      <c r="E109">
         <v>729718500</v>
       </c>
-      <c r="D109">
+      <c r="F109">
         <v>7215654927</v>
       </c>
-      <c r="E109">
+      <c r="G109">
         <v>1279639236</v>
       </c>
-      <c r="F109">
+      <c r="H109">
         <v>1079768023</v>
       </c>
-      <c r="G109">
+      <c r="I109">
         <v>2043506965</v>
       </c>
-      <c r="H109">
+      <c r="J109">
         <v>2098292787</v>
       </c>
-      <c r="I109">
+      <c r="K109">
         <v>280000000</v>
       </c>
-      <c r="J109">
+      <c r="L109">
         <v>220000000</v>
       </c>
     </row>
@@ -7783,30 +8848,36 @@
         <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
       <c r="B110">
+        <v>-1135296692</v>
+      </c>
+      <c r="C110">
+        <v>-2032008432</v>
+      </c>
+      <c r="D110">
         <v>-169785736</v>
       </c>
-      <c r="C110">
+      <c r="E110">
         <v>-200106402</v>
       </c>
-      <c r="D110">
+      <c r="F110">
         <v>-1514142261</v>
       </c>
-      <c r="E110">
+      <c r="G110">
         <v>-2649462302</v>
       </c>
-      <c r="F110">
+      <c r="H110">
         <v>-1066007536</v>
       </c>
-      <c r="G110">
+      <c r="I110">
         <v>-1155179117</v>
       </c>
-      <c r="H110">
+      <c r="J110">
         <v>225796225</v>
       </c>
-      <c r="I110">
+      <c r="K110">
         <v>-654071874</v>
       </c>
-      <c r="J110">
+      <c r="L110">
         <v>-1214552518</v>
       </c>
     </row>
@@ -7850,30 +8921,36 @@
         <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
       <c r="B118">
+        <v>-61575650</v>
+      </c>
+      <c r="C118">
+        <v>-933904489</v>
+      </c>
+      <c r="D118">
         <v>-1518210861</v>
       </c>
-      <c r="C118">
+      <c r="E118">
         <v>871812293</v>
       </c>
-      <c r="D118">
+      <c r="F118">
         <v>765119067</v>
       </c>
-      <c r="E118">
+      <c r="G118">
         <v>-1153548260</v>
       </c>
-      <c r="F118">
+      <c r="H118">
         <v>-171599217</v>
       </c>
-      <c r="G118">
+      <c r="I118">
         <v>-416314521</v>
       </c>
-      <c r="H118">
+      <c r="J118">
         <v>-415583642</v>
       </c>
-      <c r="I118">
+      <c r="K118">
         <v>-347644095</v>
       </c>
-      <c r="J118">
+      <c r="L118">
         <v>-33231546</v>
       </c>
     </row>
@@ -7912,27 +8989,33 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B125">
+        <v>-1035106941</v>
+      </c>
+      <c r="C125">
+        <v>-960515644</v>
+      </c>
+      <c r="D125">
         <v>-489813521</v>
       </c>
-      <c r="C125">
+      <c r="E125">
         <v>-1951433611</v>
       </c>
-      <c r="D125">
+      <c r="F125">
         <v>3641046419</v>
       </c>
-      <c r="E125">
+      <c r="G125">
         <v>730270504</v>
       </c>
-      <c r="F125">
+      <c r="H125">
         <v>39700218</v>
       </c>
-      <c r="G125">
+      <c r="I125">
         <v>-65994994</v>
       </c>
-      <c r="H125">
+      <c r="J125">
         <v>103022724</v>
       </c>
-      <c r="I125">
+      <c r="K125">
         <v>8996766</v>
       </c>
     </row>
@@ -7946,30 +9029,36 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
+        <v>-1035106941</v>
+      </c>
+      <c r="C127">
+        <v>-960515644</v>
+      </c>
+      <c r="D127">
         <v>-489813521</v>
       </c>
-      <c r="C127">
+      <c r="E127">
         <v>-1951433611</v>
       </c>
-      <c r="D127">
+      <c r="F127">
         <v>3641046419</v>
       </c>
-      <c r="E127">
+      <c r="G127">
         <v>730270504</v>
       </c>
-      <c r="F127">
+      <c r="H127">
         <v>39700218</v>
       </c>
-      <c r="G127">
+      <c r="I127">
         <v>-65994994</v>
       </c>
-      <c r="H127">
+      <c r="J127">
         <v>103022724</v>
       </c>
-      <c r="I127">
+      <c r="K127">
         <v>8996766</v>
       </c>
-      <c r="J127">
+      <c r="L127">
         <v>31869091</v>
       </c>
     </row>
@@ -7981,24 +9070,30 @@
         <v>0</v>
       </c>
       <c r="C128">
-        <v>0</v>
+        <v>2049524230</v>
       </c>
       <c r="D128">
         <v>0</v>
       </c>
       <c r="E128">
-        <v>119454439</v>
+        <v>0</v>
       </c>
       <c r="F128">
         <v>0</v>
       </c>
       <c r="G128">
-        <v>0</v>
+        <v>119454439</v>
       </c>
       <c r="H128">
         <v>0</v>
       </c>
       <c r="I128">
+        <v>0</v>
+      </c>
+      <c r="J128">
+        <v>0</v>
+      </c>
+      <c r="K128">
         <v>33729725</v>
       </c>
     </row>
@@ -8007,40 +9102,46 @@
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B129">
+        <v>-1035106941</v>
+      </c>
+      <c r="C129">
+        <v>1089008586</v>
+      </c>
+      <c r="D129">
         <v>-489813521</v>
       </c>
-      <c r="C129">
+      <c r="E129">
         <v>-1951433611</v>
       </c>
-      <c r="D129">
+      <c r="F129">
         <v>3641046419</v>
       </c>
-      <c r="E129">
+      <c r="G129">
         <v>849724943</v>
       </c>
-      <c r="F129">
+      <c r="H129">
         <v>39700218</v>
       </c>
-      <c r="G129">
+      <c r="I129">
         <v>-65994994</v>
       </c>
-      <c r="H129">
+      <c r="J129">
         <v>103022724</v>
       </c>
-      <c r="I129">
+      <c r="K129">
         <v>42726491</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O129"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M129"/>
+  <dimension ref="A1:O129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -8055,6 +9156,8 @@
     <col min="11" max="11" customWidth="1" width="20"/>
     <col min="12" max="12" customWidth="1" width="20"/>
     <col min="13" max="13" customWidth="1" width="20"/>
+    <col min="14" max="14" customWidth="1" width="20"/>
+    <col min="15" max="15" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8062,39 +9165,45 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="C1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="D1" t="str">
+      <c r="F1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="E1" t="str">
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2024/3</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>2023/9</v>
       </c>
-      <c r="L1" t="str">
+      <c r="N1" t="str">
         <v>2022/12</v>
       </c>
-      <c r="M1" t="str">
+      <c r="O1" t="str">
         <v>2021/12</v>
       </c>
     </row>
@@ -8108,31 +9217,37 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
+        <v>4358946179</v>
+      </c>
+      <c r="C3">
+        <v>881204746</v>
+      </c>
+      <c r="D3">
         <v>2290405959</v>
       </c>
-      <c r="C3">
+      <c r="E3">
         <v>-424923386</v>
       </c>
-      <c r="D3">
+      <c r="F3">
         <v>-370828641</v>
       </c>
-      <c r="E3">
+      <c r="G3">
         <v>422260391</v>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>144316070</v>
       </c>
-      <c r="G3">
+      <c r="I3">
         <v>657142866</v>
       </c>
-      <c r="J3">
+      <c r="L3">
         <v>2623252238</v>
       </c>
-      <c r="L3">
+      <c r="N3">
         <v>418423509</v>
       </c>
-      <c r="M3">
-        <v>2321186332</v>
+      <c r="O3">
+        <v>-12814</v>
       </c>
     </row>
     <row r="4">
@@ -8140,30 +9255,36 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
+        <v>677718114</v>
+      </c>
+      <c r="C4">
+        <v>-1118121135</v>
+      </c>
+      <c r="D4">
         <v>-691390420</v>
       </c>
-      <c r="C4">
+      <c r="E4">
         <v>-99094357</v>
       </c>
-      <c r="D4">
+      <c r="F4">
         <v>-2380891866</v>
       </c>
-      <c r="E4">
+      <c r="G4">
         <v>-1692389751</v>
       </c>
-      <c r="F4">
+      <c r="H4">
         <v>-352154456</v>
       </c>
-      <c r="G4">
+      <c r="I4">
         <v>2823206852</v>
       </c>
-      <c r="J4">
+      <c r="L4">
         <v>2732801717</v>
       </c>
-      <c r="L4">
+      <c r="N4">
         <v>256922012</v>
       </c>
-      <c r="M4">
+      <c r="O4">
         <v>638274760</v>
       </c>
     </row>
@@ -8172,21 +9293,27 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
+        <v>16032311</v>
+      </c>
+      <c r="C5">
+        <v>1165815499</v>
+      </c>
+      <c r="D5">
         <v>2178914162</v>
       </c>
-      <c r="C5">
+      <c r="E5">
         <v>-757679967</v>
       </c>
-      <c r="D5">
+      <c r="F5">
         <v>3445851460</v>
       </c>
-      <c r="E5">
+      <c r="G5">
         <v>3046361017</v>
       </c>
-      <c r="F5">
+      <c r="H5">
         <v>1711372135</v>
       </c>
-      <c r="J5">
+      <c r="L5">
         <v>204229425</v>
       </c>
     </row>
@@ -8195,30 +9322,36 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
+        <v>1052256001</v>
+      </c>
+      <c r="C6">
+        <v>924199817</v>
+      </c>
+      <c r="D6">
         <v>898156020</v>
       </c>
-      <c r="C6">
+      <c r="E6">
         <v>497090579</v>
       </c>
-      <c r="D6">
+      <c r="F6">
         <v>435385277</v>
       </c>
-      <c r="E6">
+      <c r="G6">
         <v>468533487</v>
       </c>
-      <c r="F6">
+      <c r="H6">
         <v>514126467</v>
       </c>
-      <c r="G6">
+      <c r="I6">
         <v>772271133</v>
       </c>
-      <c r="J6">
+      <c r="L6">
         <v>517711407</v>
       </c>
-      <c r="L6">
+      <c r="N6">
         <v>328056956</v>
       </c>
-      <c r="M6">
+      <c r="O6">
         <v>107953692</v>
       </c>
     </row>
@@ -8232,30 +9365,36 @@
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
+        <v>610523005</v>
+      </c>
+      <c r="C8">
+        <v>10310452</v>
+      </c>
+      <c r="D8">
         <v>24910968</v>
       </c>
-      <c r="C8">
+      <c r="E8">
         <v>31680321</v>
       </c>
-      <c r="D8">
+      <c r="F8">
         <v>29944257</v>
       </c>
-      <c r="E8">
+      <c r="G8">
         <v>2794256</v>
       </c>
-      <c r="F8">
+      <c r="H8">
         <v>14475332</v>
       </c>
-      <c r="G8">
+      <c r="I8">
         <v>-7097274</v>
       </c>
-      <c r="J8">
+      <c r="L8">
         <v>510069</v>
       </c>
-      <c r="L8">
+      <c r="N8">
         <v>12475321</v>
       </c>
-      <c r="M8">
+      <c r="O8">
         <v>2755552</v>
       </c>
     </row>
@@ -8279,30 +9418,36 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
+        <v>1262043685</v>
+      </c>
+      <c r="C12">
+        <v>1142938074</v>
+      </c>
+      <c r="D12">
         <v>948883371</v>
       </c>
-      <c r="C12">
+      <c r="E12">
         <v>1062579855</v>
       </c>
-      <c r="D12">
+      <c r="F12">
         <v>1023914902</v>
       </c>
-      <c r="E12">
+      <c r="G12">
         <v>1406028773</v>
       </c>
-      <c r="F12">
+      <c r="H12">
         <v>1305853682</v>
       </c>
-      <c r="G12">
+      <c r="I12">
         <v>1247642939</v>
       </c>
-      <c r="J12">
+      <c r="L12">
         <v>323105223</v>
       </c>
-      <c r="L12">
+      <c r="N12">
         <v>76809646</v>
       </c>
-      <c r="M12">
+      <c r="O12">
         <v>150457138</v>
       </c>
     </row>
@@ -8321,30 +9466,36 @@
         <v xml:space="preserve">    Gerçekleşmemiş Yabancı Para Çevrim Farkları İle İlgili Düzeltmeler</v>
       </c>
       <c r="B15">
+        <v>132783311</v>
+      </c>
+      <c r="C15">
+        <v>-1154968430</v>
+      </c>
+      <c r="D15">
         <v>21920419</v>
       </c>
-      <c r="C15">
+      <c r="E15">
         <v>-1788760368</v>
       </c>
-      <c r="D15">
+      <c r="F15">
         <v>667012661</v>
       </c>
-      <c r="E15">
+      <c r="G15">
         <v>545815148</v>
       </c>
-      <c r="F15">
+      <c r="H15">
         <v>-162623218</v>
       </c>
-      <c r="G15">
+      <c r="I15">
         <v>1127924081</v>
       </c>
-      <c r="J15">
+      <c r="L15">
         <v>892090234</v>
       </c>
-      <c r="L15">
+      <c r="N15">
         <v>360148302</v>
       </c>
-      <c r="M15">
+      <c r="O15">
         <v>2114653074</v>
       </c>
     </row>
@@ -8373,30 +9524,36 @@
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B20">
+        <v>-3041573691</v>
+      </c>
+      <c r="C20">
+        <v>243335586</v>
+      </c>
+      <c r="D20">
         <v>285043384</v>
       </c>
-      <c r="C20">
+      <c r="E20">
         <v>-560270354</v>
       </c>
-      <c r="D20">
+      <c r="F20">
         <v>1289594363</v>
       </c>
-      <c r="E20">
+      <c r="G20">
         <v>623189353</v>
       </c>
-      <c r="F20">
+      <c r="H20">
         <v>39539872</v>
       </c>
-      <c r="G20">
+      <c r="I20">
         <v>-1755092812</v>
       </c>
-      <c r="J20">
+      <c r="L20">
         <v>-1529187508</v>
       </c>
-      <c r="L20">
+      <c r="N20">
         <v>22638186</v>
       </c>
-      <c r="M20">
+      <c r="O20">
         <v>-323850347</v>
       </c>
     </row>
@@ -8440,21 +9597,27 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
+        <v>3793500502</v>
+      </c>
+      <c r="C28">
+        <v>896210811</v>
+      </c>
+      <c r="D28">
         <v>811878005</v>
       </c>
-      <c r="C28">
+      <c r="E28">
         <v>154672127</v>
       </c>
-      <c r="D28">
+      <c r="F28">
         <v>-1525692531</v>
       </c>
-      <c r="E28">
+      <c r="G28">
         <v>-933850835</v>
       </c>
-      <c r="F28">
+      <c r="H28">
         <v>-1136458924</v>
       </c>
-      <c r="J28">
+      <c r="L28">
         <v>-257267813</v>
       </c>
     </row>
@@ -8473,30 +9636,36 @@
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B31">
+        <v>3164703472</v>
+      </c>
+      <c r="C31">
+        <v>746184205</v>
+      </c>
+      <c r="D31">
         <v>-33279380</v>
       </c>
-      <c r="C31">
+      <c r="E31">
         <v>-247647040</v>
       </c>
-      <c r="D31">
+      <c r="F31">
         <v>-2484306078</v>
       </c>
-      <c r="E31">
+      <c r="G31">
         <v>-305295576</v>
       </c>
-      <c r="F31">
+      <c r="H31">
         <v>-372698912</v>
       </c>
-      <c r="G31">
+      <c r="I31">
         <v>-121524879</v>
       </c>
-      <c r="J31">
+      <c r="L31">
         <v>70447537</v>
       </c>
-      <c r="L31">
+      <c r="N31">
         <v>-617605418</v>
       </c>
-      <c r="M31">
+      <c r="O31">
         <v>-24397814</v>
       </c>
     </row>
@@ -8510,30 +9679,36 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
+        <v>-1653959022</v>
+      </c>
+      <c r="C33">
+        <v>-1078863004</v>
+      </c>
+      <c r="D33">
         <v>-562351888</v>
       </c>
-      <c r="C33">
+      <c r="E33">
         <v>-122248474</v>
       </c>
-      <c r="D33">
+      <c r="F33">
         <v>323499716</v>
       </c>
-      <c r="E33">
+      <c r="G33">
         <v>-14530944</v>
       </c>
-      <c r="F33">
+      <c r="H33">
         <v>-116582892</v>
       </c>
-      <c r="G33">
+      <c r="I33">
         <v>-142887372</v>
       </c>
-      <c r="J33">
+      <c r="L33">
         <v>-76896512</v>
       </c>
-      <c r="L33">
+      <c r="N33">
         <v>-140470867</v>
       </c>
-      <c r="M33">
+      <c r="O33">
         <v>-55760823</v>
       </c>
     </row>
@@ -8557,30 +9732,36 @@
         <v xml:space="preserve">    Stoklardaki Azalışlar (Artışlar) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B37">
+        <v>-1713056985</v>
+      </c>
+      <c r="C37">
+        <v>-1004527633</v>
+      </c>
+      <c r="D37">
         <v>294636618</v>
       </c>
-      <c r="C37">
+      <c r="E37">
         <v>837919518</v>
       </c>
-      <c r="D37">
+      <c r="F37">
         <v>1517846414</v>
       </c>
-      <c r="E37">
+      <c r="G37">
         <v>-281411830</v>
       </c>
-      <c r="F37">
+      <c r="H37">
         <v>-1485435559</v>
       </c>
-      <c r="G37">
+      <c r="I37">
         <v>-865629787</v>
       </c>
-      <c r="J37">
+      <c r="L37">
         <v>-673256660</v>
       </c>
-      <c r="L37">
+      <c r="N37">
         <v>-1495286351</v>
       </c>
-      <c r="M37">
+      <c r="O37">
         <v>-197870741</v>
       </c>
     </row>
@@ -8594,30 +9775,36 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
+        <v>2682365068</v>
+      </c>
+      <c r="C39">
+        <v>601286706</v>
+      </c>
+      <c r="D39">
         <v>-735063828</v>
       </c>
-      <c r="C39">
+      <c r="E39">
         <v>-1410169039</v>
       </c>
-      <c r="D39">
+      <c r="F39">
         <v>-1782415695</v>
       </c>
-      <c r="E39">
+      <c r="G39">
         <v>-874402772</v>
       </c>
-      <c r="F39">
+      <c r="H39">
         <v>-935865199</v>
       </c>
-      <c r="G39">
+      <c r="I39">
         <v>-688598337</v>
       </c>
-      <c r="J39">
+      <c r="L39">
         <v>-142408032</v>
       </c>
-      <c r="L39">
+      <c r="N39">
         <v>-465642006</v>
       </c>
-      <c r="M39">
+      <c r="O39">
         <v>-197870741</v>
       </c>
     </row>
@@ -8626,30 +9813,36 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
+        <v>-617145886</v>
+      </c>
+      <c r="C40">
+        <v>-624973907</v>
+      </c>
+      <c r="D40">
         <v>606511329</v>
       </c>
-      <c r="C40">
+      <c r="E40">
         <v>1307975712</v>
       </c>
-      <c r="D40">
+      <c r="F40">
         <v>1429122939</v>
       </c>
-      <c r="E40">
+      <c r="G40">
         <v>696786944</v>
       </c>
-      <c r="F40">
+      <c r="H40">
         <v>593100433</v>
       </c>
-      <c r="G40">
+      <c r="I40">
         <v>-1595837315</v>
       </c>
-      <c r="J40">
+      <c r="L40">
         <v>567400901</v>
       </c>
-      <c r="L40">
+      <c r="N40">
         <v>385399204</v>
       </c>
-      <c r="M40">
+      <c r="O40">
         <v>486081546</v>
       </c>
     </row>
@@ -8668,21 +9861,27 @@
         <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Yükümlülüklerdeki Artış (Azalış) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B43">
+        <v>-93585137</v>
+      </c>
+      <c r="C43">
+        <v>-8250460</v>
+      </c>
+      <c r="D43">
         <v>-245128</v>
       </c>
-      <c r="C43">
+      <c r="E43">
         <v>70759204</v>
       </c>
-      <c r="D43">
+      <c r="F43">
         <v>62150304</v>
       </c>
-      <c r="E43">
+      <c r="G43">
         <v>37212169</v>
       </c>
-      <c r="F43">
+      <c r="H43">
         <v>42983010</v>
       </c>
-      <c r="J43">
+      <c r="L43">
         <v>-65563672</v>
       </c>
     </row>
@@ -8691,30 +9890,36 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
+        <v>1500161124</v>
+      </c>
+      <c r="C44">
+        <v>17538518</v>
+      </c>
+      <c r="D44">
         <v>867407476</v>
       </c>
-      <c r="C44">
+      <c r="E44">
         <v>-521649720</v>
       </c>
-      <c r="D44">
+      <c r="F44">
         <v>599690161</v>
       </c>
-      <c r="E44">
+      <c r="G44">
         <v>802773235</v>
       </c>
-      <c r="F44">
+      <c r="H44">
         <v>918142713</v>
       </c>
-      <c r="G44">
+      <c r="I44">
         <v>669163809</v>
       </c>
-      <c r="J44">
+      <c r="L44">
         <v>63008625</v>
       </c>
-      <c r="L44">
+      <c r="N44">
         <v>33291945</v>
       </c>
-      <c r="M44">
+      <c r="O44">
         <v>3804761</v>
       </c>
     </row>
@@ -8733,30 +9938,36 @@
         <v xml:space="preserve">    Ertelenmiş Gelirlerdeki Artış (Azalış)</v>
       </c>
       <c r="B47">
+        <v>524017868</v>
+      </c>
+      <c r="C47">
+        <v>2247816386</v>
+      </c>
+      <c r="D47">
         <v>374262806</v>
       </c>
-      <c r="C47">
+      <c r="E47">
         <v>239731966</v>
       </c>
-      <c r="D47">
+      <c r="F47">
         <v>-1191280292</v>
       </c>
-      <c r="E47">
+      <c r="G47">
         <v>-994982061</v>
       </c>
-      <c r="F47">
+      <c r="H47">
         <v>219897482</v>
       </c>
-      <c r="G47">
+      <c r="I47">
         <v>-654020041</v>
       </c>
-      <c r="J47">
+      <c r="L47">
         <v>0</v>
       </c>
-      <c r="L47">
+      <c r="N47">
         <v>1660652575</v>
       </c>
-      <c r="M47">
+      <c r="O47">
         <v>51012108</v>
       </c>
     </row>
@@ -8764,10 +9975,10 @@
       <c r="A48" t="str">
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
-      <c r="L48">
+      <c r="N48">
         <v>-2636188</v>
       </c>
-      <c r="M48">
+      <c r="O48">
         <v>-204094</v>
       </c>
     </row>
@@ -8776,21 +9987,27 @@
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
       <c r="B49">
+        <v>4487250927</v>
+      </c>
+      <c r="C49">
+        <v>943905175</v>
+      </c>
+      <c r="D49">
         <v>2299401747</v>
       </c>
-      <c r="C49">
+      <c r="E49">
         <v>-702102197</v>
       </c>
-      <c r="D49">
+      <c r="F49">
         <v>-460732937</v>
       </c>
-      <c r="E49">
+      <c r="G49">
         <v>420120431</v>
       </c>
-      <c r="F49">
+      <c r="H49">
         <v>222758755</v>
       </c>
-      <c r="J49">
+      <c r="L49">
         <v>2679763329</v>
       </c>
     </row>
@@ -8813,16 +10030,16 @@
       <c r="A53" t="str">
         <v xml:space="preserve">    Alınan Faiz</v>
       </c>
-      <c r="G53">
+      <c r="I53">
         <v>11936929</v>
       </c>
-      <c r="J53">
+      <c r="L53">
         <v>6032736</v>
       </c>
-      <c r="L53">
+      <c r="N53">
         <v>3670192</v>
       </c>
-      <c r="M53">
+      <c r="O53">
         <v>191280</v>
       </c>
     </row>
@@ -8830,7 +10047,7 @@
       <c r="A54" t="str">
         <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
-      <c r="J54">
+      <c r="L54">
         <v>-62543827</v>
       </c>
     </row>
@@ -8874,21 +10091,27 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalara İlişkin Karşılıklar Kapsamında Yapılan Ödemeler</v>
       </c>
       <c r="B62">
+        <v>-18134853</v>
+      </c>
+      <c r="C62">
+        <v>-11552178</v>
+      </c>
+      <c r="D62">
         <v>-8995788</v>
       </c>
-      <c r="C62">
+      <c r="E62">
         <v>-13267145</v>
       </c>
-      <c r="D62">
+      <c r="F62">
         <v>-59584304</v>
       </c>
-      <c r="E62">
+      <c r="G62">
         <v>-70753258</v>
       </c>
-      <c r="F62">
+      <c r="H62">
         <v>-78442685</v>
       </c>
-      <c r="J62">
+      <c r="L62">
         <v>0</v>
       </c>
     </row>
@@ -8913,30 +10136,36 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
       <c r="B67">
+        <v>-7876236798</v>
+      </c>
+      <c r="C67">
+        <v>-7385846080</v>
+      </c>
+      <c r="D67">
         <v>-6721761747</v>
       </c>
-      <c r="C67">
+      <c r="E67">
         <v>-4767119928</v>
       </c>
-      <c r="D67">
+      <c r="F67">
         <v>-2006364992</v>
       </c>
-      <c r="E67">
+      <c r="G67">
         <v>-1779351356</v>
       </c>
-      <c r="F67">
+      <c r="H67">
         <v>-1574717568</v>
       </c>
-      <c r="G67">
+      <c r="I67">
         <v>-1210267944</v>
       </c>
-      <c r="J67">
+      <c r="L67">
         <v>-1222250017</v>
       </c>
-      <c r="L67">
+      <c r="N67">
         <v>-347125737</v>
       </c>
-      <c r="M67">
+      <c r="O67">
         <v>-684934184</v>
       </c>
     </row>
@@ -8990,24 +10219,30 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B77">
+        <v>2069839</v>
+      </c>
+      <c r="C77">
+        <v>2683150</v>
+      </c>
+      <c r="D77">
         <v>2703529</v>
       </c>
-      <c r="C77">
+      <c r="E77">
         <v>4327032</v>
       </c>
-      <c r="D77">
+      <c r="F77">
         <v>2246600</v>
       </c>
-      <c r="E77">
+      <c r="G77">
         <v>1021941</v>
       </c>
-      <c r="F77">
+      <c r="H77">
         <v>1001562</v>
       </c>
-      <c r="J77">
+      <c r="L77">
         <v>28754</v>
       </c>
-      <c r="L77">
+      <c r="N77">
         <v>8395</v>
       </c>
     </row>
@@ -9016,30 +10251,36 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
       <c r="B78">
+        <v>-7878306637</v>
+      </c>
+      <c r="C78">
+        <v>-7388529230</v>
+      </c>
+      <c r="D78">
         <v>-6724465276</v>
       </c>
-      <c r="C78">
+      <c r="E78">
         <v>-4771446960</v>
       </c>
-      <c r="D78">
+      <c r="F78">
         <v>-2008611592</v>
       </c>
-      <c r="E78">
+      <c r="G78">
         <v>-1780373297</v>
       </c>
-      <c r="F78">
+      <c r="H78">
         <v>-1575719130</v>
       </c>
-      <c r="G78">
+      <c r="I78">
         <v>-1210296698</v>
       </c>
-      <c r="J78">
+      <c r="L78">
         <v>-1222278771</v>
       </c>
-      <c r="L78">
+      <c r="N78">
         <v>-347134132</v>
       </c>
-      <c r="M78">
+      <c r="O78">
         <v>-684934184</v>
       </c>
     </row>
@@ -9154,30 +10395,36 @@
         <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B101">
+        <v>-919579098</v>
+      </c>
+      <c r="C101">
+        <v>6743924977</v>
+      </c>
+      <c r="D101">
         <v>6361425579</v>
       </c>
-      <c r="C101">
+      <c r="E101">
         <v>7651626844</v>
       </c>
-      <c r="D101">
+      <c r="F101">
         <v>6722215780</v>
       </c>
-      <c r="E101">
+      <c r="G101">
         <v>2164089417</v>
       </c>
-      <c r="F101">
+      <c r="H101">
         <v>1516126212</v>
       </c>
-      <c r="G101">
+      <c r="I101">
         <v>631018664</v>
       </c>
-      <c r="J101">
+      <c r="L101">
         <v>-1423875054</v>
       </c>
-      <c r="L101">
+      <c r="N101">
         <v>-22316949</v>
       </c>
-      <c r="M101">
+      <c r="O101">
         <v>-1639059524</v>
       </c>
     </row>
@@ -9196,15 +10443,21 @@
         <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B104">
+        <v>-41249937</v>
+      </c>
+      <c r="C104">
+        <v>-41249937</v>
+      </c>
+      <c r="D104">
         <v>2408368625</v>
       </c>
-      <c r="C104">
+      <c r="E104">
         <v>2449618562</v>
       </c>
-      <c r="D104">
+      <c r="F104">
         <v>2449618562</v>
       </c>
-      <c r="F104">
+      <c r="H104">
         <v>0</v>
       </c>
     </row>
@@ -9218,9 +10471,15 @@
         <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
       </c>
       <c r="B106">
+        <v>-224928641</v>
+      </c>
+      <c r="C106">
+        <v>-224928641</v>
+      </c>
+      <c r="D106">
         <v>-80382359</v>
       </c>
-      <c r="F106">
+      <c r="H106">
         <v>0</v>
       </c>
     </row>
@@ -9239,30 +10498,36 @@
         <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B109">
+        <v>743215618</v>
+      </c>
+      <c r="C109">
+        <v>7958870545</v>
+      </c>
+      <c r="D109">
         <v>9238509781</v>
       </c>
-      <c r="C109">
+      <c r="E109">
         <v>10304780686</v>
       </c>
-      <c r="D109">
+      <c r="F109">
         <v>11618569151</v>
       </c>
-      <c r="E109">
+      <c r="G109">
         <v>6501207011</v>
       </c>
-      <c r="F109">
+      <c r="H109">
         <v>5501567775</v>
       </c>
-      <c r="G109">
+      <c r="I109">
         <v>4641799752</v>
       </c>
-      <c r="J109">
+      <c r="L109">
         <v>500000000</v>
       </c>
-      <c r="L109">
+      <c r="N109">
         <v>3648635908</v>
       </c>
-      <c r="M109">
+      <c r="O109">
         <v>2372844974</v>
       </c>
     </row>
@@ -9271,30 +10536,36 @@
         <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
       <c r="B110">
+        <v>-3537197262</v>
+      </c>
+      <c r="C110">
+        <v>-3916042831</v>
+      </c>
+      <c r="D110">
         <v>-4533496701</v>
       </c>
-      <c r="C110">
+      <c r="E110">
         <v>-5429718501</v>
       </c>
-      <c r="D110">
+      <c r="F110">
         <v>-6384791216</v>
       </c>
-      <c r="E110">
+      <c r="G110">
         <v>-4644852730</v>
       </c>
-      <c r="F110">
+      <c r="H110">
         <v>-2649462302</v>
       </c>
-      <c r="G110">
+      <c r="I110">
         <v>-2798007284</v>
       </c>
-      <c r="J110">
+      <c r="L110">
         <v>-1868624392</v>
       </c>
-      <c r="L110">
+      <c r="N110">
         <v>-3523971759</v>
       </c>
-      <c r="M110">
+      <c r="O110">
         <v>-3827111278</v>
       </c>
     </row>
@@ -9338,30 +10609,36 @@
         <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
       <c r="B118">
+        <v>-1641878707</v>
+      </c>
+      <c r="C118">
+        <v>-815183990</v>
+      </c>
+      <c r="D118">
         <v>-1034827761</v>
       </c>
-      <c r="C118">
+      <c r="E118">
         <v>311783883</v>
       </c>
-      <c r="D118">
+      <c r="F118">
         <v>-976342931</v>
       </c>
-      <c r="E118">
+      <c r="G118">
         <v>-2157045640</v>
       </c>
-      <c r="F118">
+      <c r="H118">
         <v>-1351141475</v>
       </c>
-      <c r="G118">
+      <c r="I118">
         <v>-1212773804</v>
       </c>
-      <c r="J118">
+      <c r="L118">
         <v>-55250662</v>
       </c>
-      <c r="L118">
+      <c r="N118">
         <v>-146981098</v>
       </c>
-      <c r="M118">
+      <c r="O118">
         <v>-184793220</v>
       </c>
     </row>
@@ -9369,10 +10646,10 @@
       <c r="A119" t="str">
         <v xml:space="preserve">    Alınan Faiz</v>
       </c>
-      <c r="B119">
+      <c r="D119">
         <v>363253994</v>
       </c>
-      <c r="F119">
+      <c r="H119">
         <v>15162214</v>
       </c>
     </row>
@@ -9406,21 +10683,27 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B125">
+        <v>-4436869717</v>
+      </c>
+      <c r="C125">
+        <v>239283643</v>
+      </c>
+      <c r="D125">
         <v>1930069791</v>
       </c>
-      <c r="C125">
+      <c r="E125">
         <v>2459583530</v>
       </c>
-      <c r="D125">
+      <c r="F125">
         <v>4345022147</v>
       </c>
-      <c r="E125">
+      <c r="G125">
         <v>806998452</v>
       </c>
-      <c r="F125">
+      <c r="H125">
         <v>85724714</v>
       </c>
-      <c r="J125">
+      <c r="L125">
         <v>-22872833</v>
       </c>
     </row>
@@ -9434,30 +10717,36 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
+        <v>-4436869717</v>
+      </c>
+      <c r="C127">
+        <v>239283643</v>
+      </c>
+      <c r="D127">
         <v>1930069791</v>
       </c>
-      <c r="C127">
+      <c r="E127">
         <v>2459583530</v>
       </c>
-      <c r="D127">
+      <c r="F127">
         <v>4345022147</v>
       </c>
-      <c r="E127">
+      <c r="G127">
         <v>806998452</v>
       </c>
-      <c r="F127">
+      <c r="H127">
         <v>85724714</v>
       </c>
-      <c r="G127">
+      <c r="I127">
         <v>77893587</v>
       </c>
-      <c r="J127">
+      <c r="L127">
         <v>-22872833</v>
       </c>
-      <c r="L127">
+      <c r="N127">
         <v>48980823</v>
       </c>
-      <c r="M127">
+      <c r="O127">
         <v>-2807376</v>
       </c>
     </row>
@@ -9466,10 +10755,10 @@
         <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B128">
-        <v>119454439</v>
+        <v>2049524230</v>
       </c>
       <c r="C128">
-        <v>119454439</v>
+        <v>2049524230</v>
       </c>
       <c r="D128">
         <v>119454439</v>
@@ -9478,9 +10767,15 @@
         <v>119454439</v>
       </c>
       <c r="F128">
+        <v>119454439</v>
+      </c>
+      <c r="G128">
+        <v>119454439</v>
+      </c>
+      <c r="H128">
         <v>33729725</v>
       </c>
-      <c r="J128">
+      <c r="L128">
         <v>56602558</v>
       </c>
     </row>
@@ -9489,27 +10784,33 @@
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B129">
+        <v>-2387345487</v>
+      </c>
+      <c r="C129">
+        <v>2288807873</v>
+      </c>
+      <c r="D129">
         <v>2049524230</v>
       </c>
-      <c r="C129">
+      <c r="E129">
         <v>2579037969</v>
       </c>
-      <c r="D129">
+      <c r="F129">
         <v>4464476586</v>
       </c>
-      <c r="E129">
+      <c r="G129">
         <v>926452891</v>
       </c>
-      <c r="F129">
+      <c r="H129">
         <v>119454439</v>
       </c>
-      <c r="J129">
+      <c r="L129">
         <v>33729725</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O129"/>
   </ignoredErrors>
 </worksheet>
 </file>